--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,11 +115,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,66 +644,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24826.19</v>
+        <v>24495.85</v>
       </c>
       <c r="C2" t="n">
-        <v>24844.98</v>
+        <v>24560.19</v>
       </c>
       <c r="D2" t="n">
-        <v>24378.69</v>
+        <v>24254.07</v>
       </c>
       <c r="E2" t="n">
-        <v>24493.95</v>
+        <v>24312.16</v>
       </c>
       <c r="F2" t="n">
-        <v>-348.72</v>
+        <v>-181.79</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0074</v>
       </c>
       <c r="H2" t="n">
-        <v>466.29</v>
+        <v>306.12</v>
       </c>
       <c r="I2" t="n">
-        <v>24544.7</v>
+        <v>23912.4</v>
       </c>
       <c r="J2" t="n">
-        <v>24551.35</v>
+        <v>23968.72</v>
       </c>
       <c r="K2" t="n">
-        <v>24716.87</v>
+        <v>24260.8</v>
       </c>
       <c r="L2" t="n">
-        <v>24882.39</v>
+        <v>24552.89</v>
       </c>
       <c r="M2" t="n">
-        <v>24968.47</v>
+        <v>24727.09</v>
       </c>
       <c r="N2" t="n">
-        <v>25054.55</v>
+        <v>24901.3</v>
       </c>
       <c r="O2" t="n">
-        <v>25299.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>25311.27</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -717,68 +716,76 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24495.85</v>
+        <v>24145.19</v>
       </c>
       <c r="C3" t="n">
-        <v>24560.19</v>
+        <v>24163.25</v>
       </c>
       <c r="D3" t="n">
-        <v>24254.07</v>
+        <v>23749.99</v>
       </c>
       <c r="E3" t="n">
-        <v>24312.16</v>
+        <v>23924.81</v>
       </c>
       <c r="F3" t="n">
-        <v>-181.79</v>
+        <v>-387.35</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0159</v>
       </c>
       <c r="H3" t="n">
-        <v>306.12</v>
+        <v>413.26</v>
       </c>
       <c r="I3" t="n">
-        <v>23912.4</v>
+        <v>23947.95</v>
       </c>
       <c r="J3" t="n">
-        <v>23968.72</v>
+        <v>23958.56</v>
       </c>
       <c r="K3" t="n">
-        <v>24260.8</v>
+        <v>24159.1</v>
       </c>
       <c r="L3" t="n">
-        <v>24552.89</v>
+        <v>24359.65</v>
       </c>
       <c r="M3" t="n">
-        <v>24727.09</v>
+        <v>24465.22</v>
       </c>
       <c r="N3" t="n">
-        <v>24901.3</v>
+        <v>24570.79</v>
       </c>
       <c r="O3" t="n">
-        <v>25311.27</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+        <v>24866.31</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
@@ -795,7 +802,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -805,66 +812,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24145.19</v>
+        <v>23811.76</v>
       </c>
       <c r="C4" t="n">
-        <v>24163.25</v>
+        <v>23863.71</v>
       </c>
       <c r="D4" t="n">
-        <v>23749.99</v>
+        <v>23444.86</v>
       </c>
       <c r="E4" t="n">
-        <v>23924.81</v>
+        <v>23768.52</v>
       </c>
       <c r="F4" t="n">
-        <v>-387.35</v>
+        <v>-156.29</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0159</v>
+        <v>-0.0065</v>
       </c>
       <c r="H4" t="n">
-        <v>413.26</v>
+        <v>418.85</v>
       </c>
       <c r="I4" t="n">
-        <v>23947.95</v>
+        <v>23336.73</v>
       </c>
       <c r="J4" t="n">
-        <v>23958.56</v>
+        <v>23495.65</v>
       </c>
       <c r="K4" t="n">
-        <v>24159.1</v>
+        <v>23718.18</v>
       </c>
       <c r="L4" t="n">
-        <v>24359.65</v>
+        <v>23940.72</v>
       </c>
       <c r="M4" t="n">
-        <v>24465.22</v>
+        <v>24131.44</v>
       </c>
       <c r="N4" t="n">
-        <v>24570.79</v>
+        <v>24322.17</v>
       </c>
       <c r="O4" t="n">
-        <v>24866.31</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>24576.51</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -879,7 +884,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -889,62 +894,62 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23811.76</v>
+        <v>23800.02</v>
       </c>
       <c r="C5" t="n">
-        <v>23863.71</v>
+        <v>23825.81</v>
       </c>
       <c r="D5" t="n">
-        <v>23444.86</v>
+        <v>23252.13</v>
       </c>
       <c r="E5" t="n">
-        <v>23768.52</v>
+        <v>23336.28</v>
       </c>
       <c r="F5" t="n">
-        <v>-156.29</v>
+        <v>-432.24</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0182</v>
       </c>
       <c r="H5" t="n">
-        <v>418.85</v>
+        <v>573.6799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>23336.73</v>
+        <v>23026.01</v>
       </c>
       <c r="J5" t="n">
-        <v>23495.65</v>
+        <v>23406.79</v>
       </c>
       <c r="K5" t="n">
-        <v>23718.18</v>
+        <v>23559.09</v>
       </c>
       <c r="L5" t="n">
-        <v>23940.72</v>
+        <v>23711.4</v>
       </c>
       <c r="M5" t="n">
-        <v>24131.44</v>
+        <v>23977.95</v>
       </c>
       <c r="N5" t="n">
-        <v>24322.17</v>
+        <v>24244.49</v>
       </c>
       <c r="O5" t="n">
-        <v>24576.51</v>
+        <v>24282.56</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
@@ -961,7 +966,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -971,67 +976,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23800.02</v>
+        <v>23420.7</v>
       </c>
       <c r="C6" t="n">
-        <v>23825.81</v>
+        <v>23565.65</v>
       </c>
       <c r="D6" t="n">
-        <v>23252.13</v>
+        <v>23248.87</v>
       </c>
       <c r="E6" t="n">
-        <v>23336.28</v>
+        <v>23412.18</v>
       </c>
       <c r="F6" t="n">
-        <v>-432.24</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0033</v>
       </c>
       <c r="H6" t="n">
-        <v>573.6799999999999</v>
+        <v>316.78</v>
       </c>
       <c r="I6" t="n">
-        <v>23026.01</v>
+        <v>22678.45</v>
       </c>
       <c r="J6" t="n">
-        <v>23406.79</v>
+        <v>22661.25</v>
       </c>
       <c r="K6" t="n">
-        <v>23559.09</v>
+        <v>23049.44</v>
       </c>
       <c r="L6" t="n">
-        <v>23711.4</v>
+        <v>23437.62</v>
       </c>
       <c r="M6" t="n">
-        <v>23977.95</v>
+        <v>23623.12</v>
       </c>
       <c r="N6" t="n">
-        <v>24244.49</v>
+        <v>23808.61</v>
       </c>
       <c r="O6" t="n">
-        <v>24282.56</v>
+        <v>24399.49</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1043,73 +1044,81 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23420.7</v>
+        <v>23388.5</v>
       </c>
       <c r="C7" t="n">
-        <v>23565.65</v>
+        <v>23388.5</v>
       </c>
       <c r="D7" t="n">
-        <v>23248.87</v>
+        <v>22978.59</v>
       </c>
       <c r="E7" t="n">
-        <v>23412.18</v>
+        <v>23076.91</v>
       </c>
       <c r="F7" t="n">
-        <v>75.90000000000001</v>
+        <v>-335.27</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.0143</v>
       </c>
       <c r="H7" t="n">
-        <v>316.78</v>
+        <v>409.91</v>
       </c>
       <c r="I7" t="n">
-        <v>22678.45</v>
+        <v>22932.09</v>
       </c>
       <c r="J7" t="n">
-        <v>22661.25</v>
+        <v>23097.86</v>
       </c>
       <c r="K7" t="n">
-        <v>23049.44</v>
+        <v>23253.79</v>
       </c>
       <c r="L7" t="n">
-        <v>23437.62</v>
+        <v>23409.72</v>
       </c>
       <c r="M7" t="n">
-        <v>23623.12</v>
+        <v>23570.57</v>
       </c>
       <c r="N7" t="n">
-        <v>23808.61</v>
+        <v>23731.42</v>
       </c>
       <c r="O7" t="n">
-        <v>24399.49</v>
+        <v>23882.43</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1121,67 +1130,65 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23388.5</v>
+        <v>22952.09</v>
       </c>
       <c r="C8" t="n">
-        <v>23388.5</v>
+        <v>22962.46</v>
       </c>
       <c r="D8" t="n">
-        <v>22978.59</v>
+        <v>22518</v>
       </c>
       <c r="E8" t="n">
-        <v>23076.91</v>
+        <v>22671.86</v>
       </c>
       <c r="F8" t="n">
-        <v>-335.27</v>
+        <v>-405.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0176</v>
       </c>
       <c r="H8" t="n">
-        <v>409.91</v>
+        <v>444.46</v>
       </c>
       <c r="I8" t="n">
-        <v>22932.09</v>
+        <v>22568.68</v>
       </c>
       <c r="J8" t="n">
-        <v>23097.86</v>
+        <v>22613.68</v>
       </c>
       <c r="K8" t="n">
-        <v>23253.79</v>
+        <v>22871.96</v>
       </c>
       <c r="L8" t="n">
-        <v>23409.72</v>
+        <v>23130.23</v>
       </c>
       <c r="M8" t="n">
-        <v>23570.57</v>
+        <v>23281.87</v>
       </c>
       <c r="N8" t="n">
-        <v>23731.42</v>
+        <v>23433.5</v>
       </c>
       <c r="O8" t="n">
-        <v>23882.43</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
+        <v>23798.41</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
@@ -1207,7 +1214,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1217,134 +1224,136 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C9" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D9" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E9" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F9" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H9" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I9" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J9" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K9" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L9" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M9" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N9" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O9" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C10" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D10" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E10" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F10" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H10" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I10" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J10" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K10" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L10" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M10" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N10" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O10" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,85 +1361,79 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C11" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D11" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E11" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F11" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H11" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I11" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J11" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K11" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L11" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M11" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N11" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O11" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,79 +1441,85 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C12" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D12" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E12" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F12" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H12" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I12" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J12" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K12" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L12" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M12" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N12" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O12" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,25 +1530,25 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1553,50 +1562,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C13" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D13" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E13" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F13" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H13" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I13" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J13" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K13" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L13" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M13" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N13" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O13" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1607,7 +1616,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1625,7 +1634,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1639,50 +1648,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C14" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D14" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E14" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F14" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H14" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I14" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J14" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K14" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L14" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M14" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N14" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O14" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,82 +1702,78 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C15" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D15" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E15" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F15" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H15" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I15" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J15" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K15" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L15" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M15" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N15" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O15" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1779,78 +1784,80 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C16" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D16" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E16" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F16" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H16" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I16" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J16" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K16" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L16" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M16" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N16" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O16" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,80 +1868,78 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C17" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D17" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E17" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F17" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H17" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I17" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J17" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K17" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L17" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M17" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N17" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O17" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,78 +1950,78 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C18" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D18" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E18" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F18" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H18" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I18" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J18" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K18" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L18" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M18" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N18" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O18" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2027,78 +2032,80 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C19" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D19" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E19" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F19" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H19" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I19" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J19" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K19" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L19" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M19" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N19" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O19" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,17 +2113,19 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2125,64 +2134,64 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C20" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D20" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E20" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F20" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H20" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I20" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J20" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K20" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L20" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M20" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N20" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O20" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,12 +2199,10 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2211,64 +2218,60 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C21" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D21" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E21" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F21" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H21" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I21" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J21" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K21" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L21" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M21" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N21" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O21" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,23 +2282,27 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2305,83 +2312,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C22" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D22" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E22" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F22" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H22" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I22" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J22" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K22" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L22" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M22" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N22" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O22" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2389,134 +2396,136 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C23" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D23" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E23" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F23" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H23" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I23" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J23" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K23" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L23" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M23" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N23" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O23" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C24" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D24" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E24" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F24" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H24" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I24" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J24" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K24" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L24" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M24" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N24" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O24" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2527,25 +2536,21 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2559,63 +2564,67 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C25" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D25" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E25" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H25" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I25" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J25" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K25" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L25" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N25" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O25" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2627,95 +2636,93 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C26" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D26" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E26" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F26" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H26" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I26" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J26" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K26" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L26" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M26" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N26" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O26" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2723,220 +2730,220 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C27" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D27" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E27" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F27" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H27" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I27" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J27" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K27" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L27" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M27" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N27" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O27" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C28" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D28" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E28" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F28" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H28" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I28" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J28" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K28" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L28" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M28" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N28" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O28" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C29" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D29" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E29" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F29" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H29" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I29" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J29" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K29" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L29" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M29" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N29" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O29" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,27 +2954,23 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2977,50 +2980,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C30" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D30" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E30" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F30" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H30" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I30" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J30" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K30" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L30" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M30" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N30" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O30" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3031,23 +3034,27 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3057,50 +3064,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C31" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D31" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E31" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F31" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H31" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I31" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J31" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K31" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L31" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M31" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N31" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O31" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3111,27 +3118,23 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3141,50 +3144,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C32" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D32" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E32" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F32" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I32" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J32" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K32" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L32" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M32" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N32" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O32" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3192,18 +3195,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3211,60 +3214,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C33" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D33" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E33" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F33" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H33" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I33" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J33" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K33" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L33" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M33" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N33" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O33" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3272,18 +3279,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3291,64 +3298,60 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C34" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D34" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E34" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F34" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H34" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I34" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J34" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K34" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L34" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M34" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N34" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O34" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3356,17 +3359,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
@@ -3375,60 +3380,64 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C35" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D35" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E35" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F35" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H35" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I35" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J35" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K35" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L35" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M35" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N35" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O35" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3436,20 +3445,16 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3457,7 +3462,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3471,63 +3476,69 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C36" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D36" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E36" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F36" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H36" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I36" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J36" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K36" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L36" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M36" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N36" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O36" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3539,148 +3550,144 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W36" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C37" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D37" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E37" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F37" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H37" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I37" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J37" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K37" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L37" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M37" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N37" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O37" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C38" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D38" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E38" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F38" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H38" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I38" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J38" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K38" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L38" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M38" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N38" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O38" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3691,23 +3698,25 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3721,63 +3730,67 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C39" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D39" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E39" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F39" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H39" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I39" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J39" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K39" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L39" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M39" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N39" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O39" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3788,92 +3801,86 @@
       <c r="U39" s="8" t="n">
         <v/>
       </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C40" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D40" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E40" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F40" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H40" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I40" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J40" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K40" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L40" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M40" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N40" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O40" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3881,64 +3888,60 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C41" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D41" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E41" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F41" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H41" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I41" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J41" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K41" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L41" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M41" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N41" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O41" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3948,12 +3951,12 @@
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3965,66 +3968,72 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C42" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D42" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E42" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F42" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H42" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I42" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J42" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K42" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L42" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M42" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N42" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O42" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4033,7 +4042,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4045,95 +4054,93 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C43" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D43" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E43" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F43" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H43" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I43" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J43" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K43" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L43" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M43" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N43" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O43" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4141,50 +4148,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C44" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D44" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E44" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F44" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I44" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J44" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K44" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L44" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M44" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N44" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O44" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4192,83 +4199,83 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C45" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D45" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E45" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F45" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H45" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I45" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J45" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K45" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L45" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M45" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N45" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O45" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4281,7 +4288,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4295,64 +4302,60 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C46" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D46" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E46" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F46" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H46" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I46" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J46" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K46" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L46" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M46" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N46" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O46" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4360,26 +4363,30 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4389,50 +4396,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C47" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D47" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E47" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F47" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H47" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I47" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J47" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K47" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L47" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M47" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N47" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O47" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4443,7 +4450,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4455,15 +4462,15 @@
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4473,83 +4480,83 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C48" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D48" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E48" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F48" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H48" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I48" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J48" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K48" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L48" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M48" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N48" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O48" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr"/>
@@ -4557,69 +4564,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C49" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D49" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E49" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F49" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H49" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I49" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J49" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K49" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L49" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M49" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N49" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O49" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4631,7 +4632,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4641,50 +4642,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C50" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D50" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E50" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H50" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I50" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J50" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K50" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L50" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M50" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N50" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O50" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4695,74 +4696,82 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="S50" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C51" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D51" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E51" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F51" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H51" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I51" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J51" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K51" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L51" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M51" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N51" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O51" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4770,85 +4779,81 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C52" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D52" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E52" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F52" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I52" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J52" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K52" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L52" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M52" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N52" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O52" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4858,18 +4863,16 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4877,66 +4880,72 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C53" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D53" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E53" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F53" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H53" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I53" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J53" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K53" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L53" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M53" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N53" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O53" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4957,71 +4966,67 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C54" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D54" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E54" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F54" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I54" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J54" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K54" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L54" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M54" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N54" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O54" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5031,7 +5036,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5043,7 +5048,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5053,57 +5058,57 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C55" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D55" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E55" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F55" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H55" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I55" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J55" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K55" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L55" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M55" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N55" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O55" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -5113,7 +5118,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5125,7 +5130,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5135,71 +5140,69 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C56" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D56" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E56" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F56" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H56" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I56" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J56" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K56" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L56" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M56" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N56" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O56" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5207,60 +5210,64 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C57" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D57" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E57" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F57" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H57" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I57" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J57" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K57" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L57" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M57" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N57" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O57" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5271,9 +5278,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S57" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5281,166 +5288,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C58" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D58" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E58" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F58" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I58" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J58" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K58" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L58" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M58" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N58" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O58" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="Q58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C59" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D59" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E59" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F59" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H59" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I59" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J59" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K59" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L59" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M59" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N59" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O59" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5455,7 +5462,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5469,50 +5476,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C60" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D60" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E60" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F60" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H60" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I60" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J60" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K60" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L60" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M60" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N60" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O60" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5522,12 +5529,12 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5539,7 +5546,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5553,56 +5560,60 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C61" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D61" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E61" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F61" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H61" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I61" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J61" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K61" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L61" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M61" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N61" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O61" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
@@ -5611,7 +5622,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5623,75 +5634,71 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C62" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D62" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E62" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F62" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H62" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I62" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J62" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K62" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L62" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M62" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N62" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O62" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5711,7 +5718,7 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5721,69 +5728,67 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C63" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D63" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E63" t="n">
-        <v>24805.63</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>-148.84</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.006</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I63" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J63" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K63" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L63" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M63" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N63" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O63" t="n">
-        <v>25153.98</v>
+        <v>25132.12</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5795,39 +5800,43 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="W63" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
-        <v>24289.3</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>24572.15</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>24665.16</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>24758.17</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>24946.1</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>25134.03</v>
-      </c>
-      <c r="O64" s="13" t="n">
-        <v>25132.12</v>
+      <c r="I64" s="14" t="n">
+        <v>24397.98</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>25190.37</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,14 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -490,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,60 +641,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24495.85</v>
+        <v>24145.19</v>
       </c>
       <c r="C2" t="n">
-        <v>24560.19</v>
+        <v>24163.25</v>
       </c>
       <c r="D2" t="n">
-        <v>24254.07</v>
+        <v>23749.99</v>
       </c>
       <c r="E2" t="n">
-        <v>24312.16</v>
+        <v>23924.81</v>
       </c>
       <c r="F2" t="n">
-        <v>-181.79</v>
+        <v>-387.35</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.0159</v>
       </c>
       <c r="H2" t="n">
-        <v>306.12</v>
+        <v>413.26</v>
       </c>
       <c r="I2" t="n">
-        <v>23912.4</v>
+        <v>23947.95</v>
       </c>
       <c r="J2" t="n">
-        <v>23968.72</v>
+        <v>23958.56</v>
       </c>
       <c r="K2" t="n">
-        <v>24260.8</v>
+        <v>24159.1</v>
       </c>
       <c r="L2" t="n">
-        <v>24552.89</v>
+        <v>24359.65</v>
       </c>
       <c r="M2" t="n">
-        <v>24727.09</v>
+        <v>24465.22</v>
       </c>
       <c r="N2" t="n">
-        <v>24901.3</v>
+        <v>24570.79</v>
       </c>
       <c r="O2" t="n">
-        <v>25311.27</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>24866.31</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -716,78 +717,72 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24145.19</v>
+        <v>23811.76</v>
       </c>
       <c r="C3" t="n">
-        <v>24163.25</v>
+        <v>23863.71</v>
       </c>
       <c r="D3" t="n">
-        <v>23749.99</v>
+        <v>23444.86</v>
       </c>
       <c r="E3" t="n">
-        <v>23924.81</v>
+        <v>23768.52</v>
       </c>
       <c r="F3" t="n">
-        <v>-387.35</v>
+        <v>-156.29</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0159</v>
+        <v>-0.0065</v>
       </c>
       <c r="H3" t="n">
-        <v>413.26</v>
+        <v>418.85</v>
       </c>
       <c r="I3" t="n">
-        <v>23947.95</v>
+        <v>23336.73</v>
       </c>
       <c r="J3" t="n">
-        <v>23958.56</v>
+        <v>23495.65</v>
       </c>
       <c r="K3" t="n">
-        <v>24159.1</v>
+        <v>23718.18</v>
       </c>
       <c r="L3" t="n">
-        <v>24359.65</v>
+        <v>23940.72</v>
       </c>
       <c r="M3" t="n">
-        <v>24465.22</v>
+        <v>24131.44</v>
       </c>
       <c r="N3" t="n">
-        <v>24570.79</v>
+        <v>24322.17</v>
       </c>
       <c r="O3" t="n">
-        <v>24866.31</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>24576.51</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -802,7 +797,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -812,62 +807,62 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23811.76</v>
+        <v>23800.02</v>
       </c>
       <c r="C4" t="n">
-        <v>23863.71</v>
+        <v>23825.81</v>
       </c>
       <c r="D4" t="n">
-        <v>23444.86</v>
+        <v>23252.13</v>
       </c>
       <c r="E4" t="n">
-        <v>23768.52</v>
+        <v>23336.28</v>
       </c>
       <c r="F4" t="n">
-        <v>-156.29</v>
+        <v>-432.24</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0182</v>
       </c>
       <c r="H4" t="n">
-        <v>418.85</v>
+        <v>573.6799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>23336.73</v>
+        <v>23026.01</v>
       </c>
       <c r="J4" t="n">
-        <v>23495.65</v>
+        <v>23406.79</v>
       </c>
       <c r="K4" t="n">
-        <v>23718.18</v>
+        <v>23559.09</v>
       </c>
       <c r="L4" t="n">
-        <v>23940.72</v>
+        <v>23711.4</v>
       </c>
       <c r="M4" t="n">
-        <v>24131.44</v>
+        <v>23977.95</v>
       </c>
       <c r="N4" t="n">
-        <v>24322.17</v>
+        <v>24244.49</v>
       </c>
       <c r="O4" t="n">
-        <v>24576.51</v>
+        <v>24282.56</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
@@ -884,7 +879,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -894,67 +889,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23800.02</v>
+        <v>23420.7</v>
       </c>
       <c r="C5" t="n">
-        <v>23825.81</v>
+        <v>23565.65</v>
       </c>
       <c r="D5" t="n">
-        <v>23252.13</v>
+        <v>23248.87</v>
       </c>
       <c r="E5" t="n">
-        <v>23336.28</v>
+        <v>23412.18</v>
       </c>
       <c r="F5" t="n">
-        <v>-432.24</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0033</v>
       </c>
       <c r="H5" t="n">
-        <v>573.6799999999999</v>
+        <v>316.78</v>
       </c>
       <c r="I5" t="n">
-        <v>23026.01</v>
+        <v>22678.45</v>
       </c>
       <c r="J5" t="n">
-        <v>23406.79</v>
+        <v>22661.25</v>
       </c>
       <c r="K5" t="n">
-        <v>23559.09</v>
+        <v>23049.44</v>
       </c>
       <c r="L5" t="n">
-        <v>23711.4</v>
+        <v>23437.62</v>
       </c>
       <c r="M5" t="n">
-        <v>23977.95</v>
+        <v>23623.12</v>
       </c>
       <c r="N5" t="n">
-        <v>24244.49</v>
+        <v>23808.61</v>
       </c>
       <c r="O5" t="n">
-        <v>24282.56</v>
+        <v>24399.49</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -966,73 +957,81 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23420.7</v>
+        <v>23388.5</v>
       </c>
       <c r="C6" t="n">
-        <v>23565.65</v>
+        <v>23388.5</v>
       </c>
       <c r="D6" t="n">
-        <v>23248.87</v>
+        <v>22978.59</v>
       </c>
       <c r="E6" t="n">
-        <v>23412.18</v>
+        <v>23076.91</v>
       </c>
       <c r="F6" t="n">
-        <v>75.90000000000001</v>
+        <v>-335.27</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.0143</v>
       </c>
       <c r="H6" t="n">
-        <v>316.78</v>
+        <v>409.91</v>
       </c>
       <c r="I6" t="n">
-        <v>22678.45</v>
+        <v>22932.09</v>
       </c>
       <c r="J6" t="n">
-        <v>22661.25</v>
+        <v>23097.86</v>
       </c>
       <c r="K6" t="n">
-        <v>23049.44</v>
+        <v>23253.79</v>
       </c>
       <c r="L6" t="n">
-        <v>23437.62</v>
+        <v>23409.72</v>
       </c>
       <c r="M6" t="n">
-        <v>23623.12</v>
+        <v>23570.57</v>
       </c>
       <c r="N6" t="n">
-        <v>23808.61</v>
+        <v>23731.42</v>
       </c>
       <c r="O6" t="n">
-        <v>24399.49</v>
+        <v>23882.43</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1044,67 +1043,65 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23388.5</v>
+        <v>22952.09</v>
       </c>
       <c r="C7" t="n">
-        <v>23388.5</v>
+        <v>22962.46</v>
       </c>
       <c r="D7" t="n">
-        <v>22978.59</v>
+        <v>22518</v>
       </c>
       <c r="E7" t="n">
-        <v>23076.91</v>
+        <v>22671.86</v>
       </c>
       <c r="F7" t="n">
-        <v>-335.27</v>
+        <v>-405.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0176</v>
       </c>
       <c r="H7" t="n">
-        <v>409.91</v>
+        <v>444.46</v>
       </c>
       <c r="I7" t="n">
-        <v>22932.09</v>
+        <v>22568.68</v>
       </c>
       <c r="J7" t="n">
-        <v>23097.86</v>
+        <v>22613.68</v>
       </c>
       <c r="K7" t="n">
-        <v>23253.79</v>
+        <v>22871.96</v>
       </c>
       <c r="L7" t="n">
-        <v>23409.72</v>
+        <v>23130.23</v>
       </c>
       <c r="M7" t="n">
-        <v>23570.57</v>
+        <v>23281.87</v>
       </c>
       <c r="N7" t="n">
-        <v>23731.42</v>
+        <v>23433.5</v>
       </c>
       <c r="O7" t="n">
-        <v>23882.43</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
+        <v>23798.41</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
@@ -1130,7 +1127,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1140,134 +1137,136 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C8" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D8" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E8" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F8" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H8" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I8" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J8" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K8" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L8" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M8" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N8" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O8" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C9" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D9" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E9" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F9" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H9" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I9" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J9" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K9" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L9" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M9" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N9" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O9" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,85 +1274,79 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C10" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D10" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E10" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F10" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H10" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I10" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J10" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K10" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L10" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M10" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N10" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O10" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1361,79 +1354,85 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C11" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D11" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E11" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F11" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H11" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I11" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J11" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K11" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L11" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M11" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N11" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O11" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,25 +1443,25 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1476,50 +1475,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C12" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D12" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E12" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F12" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H12" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I12" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J12" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K12" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L12" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M12" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N12" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O12" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,7 +1529,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1548,7 +1547,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1562,50 +1561,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C13" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D13" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E13" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F13" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H13" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I13" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J13" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K13" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L13" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M13" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N13" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O13" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1616,82 +1615,78 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C14" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D14" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E14" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F14" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H14" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I14" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J14" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K14" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L14" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M14" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N14" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O14" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1702,78 +1697,80 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C15" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D15" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E15" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F15" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H15" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I15" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J15" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K15" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L15" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M15" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N15" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O15" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1784,80 +1781,78 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C16" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D16" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E16" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F16" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H16" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I16" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J16" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K16" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L16" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M16" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N16" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O16" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1868,78 +1863,78 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C17" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D17" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E17" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F17" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H17" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I17" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J17" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K17" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L17" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M17" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N17" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O17" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1950,78 +1945,80 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C18" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D18" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E18" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F18" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H18" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I18" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J18" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K18" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L18" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M18" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N18" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O18" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,17 +2026,19 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2048,64 +2047,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C19" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D19" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E19" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F19" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H19" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I19" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J19" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K19" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L19" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M19" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N19" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O19" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,12 +2112,10 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2134,64 +2131,60 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C20" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D20" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E20" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F20" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H20" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I20" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J20" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K20" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L20" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M20" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N20" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O20" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2202,23 +2195,27 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="11" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2228,83 +2225,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C21" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D21" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E21" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F21" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H21" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I21" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J21" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K21" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L21" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M21" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N21" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O21" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2312,134 +2309,136 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C22" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D22" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E22" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F22" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H22" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I22" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J22" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K22" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L22" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M22" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N22" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O22" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="10" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C23" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D23" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E23" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F23" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H23" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I23" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J23" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K23" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L23" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M23" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N23" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O23" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2450,25 +2449,21 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="10" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2482,63 +2477,67 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C24" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D24" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E24" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H24" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I24" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J24" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K24" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L24" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M24" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N24" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O24" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2550,95 +2549,93 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="10" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C25" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D25" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E25" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F25" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H25" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I25" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J25" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K25" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L25" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M25" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N25" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O25" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2646,220 +2643,220 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C26" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D26" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E26" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F26" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H26" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I26" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J26" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K26" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L26" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M26" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N26" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O26" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C27" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D27" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E27" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F27" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H27" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I27" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J27" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K27" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L27" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M27" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N27" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O27" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C28" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D28" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E28" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F28" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H28" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I28" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J28" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K28" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L28" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M28" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N28" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O28" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,27 +2867,23 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="11" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2900,50 +2893,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C29" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D29" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E29" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F29" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H29" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I29" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J29" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K29" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L29" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M29" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N29" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O29" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2954,23 +2947,27 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="11" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2980,50 +2977,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C30" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D30" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E30" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F30" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H30" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I30" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J30" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K30" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L30" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M30" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N30" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O30" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3034,27 +3031,23 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3064,50 +3057,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C31" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D31" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E31" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F31" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I31" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J31" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K31" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L31" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M31" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N31" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O31" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3115,18 +3108,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3134,60 +3127,64 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C32" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D32" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E32" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F32" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H32" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I32" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J32" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K32" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L32" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M32" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N32" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O32" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3195,18 +3192,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3214,64 +3211,60 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C33" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D33" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E33" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F33" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H33" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I33" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J33" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K33" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L33" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M33" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N33" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O33" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3279,17 +3272,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3298,60 +3293,64 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C34" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D34" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E34" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F34" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H34" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I34" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J34" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K34" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L34" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M34" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N34" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O34" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3359,20 +3358,16 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3380,7 +3375,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3394,63 +3389,69 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C35" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D35" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E35" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F35" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H35" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I35" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J35" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K35" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L35" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M35" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N35" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O35" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3464,146 +3465,142 @@
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C36" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D36" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E36" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F36" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H36" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I36" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J36" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K36" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L36" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M36" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N36" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O36" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="10" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C37" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D37" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E37" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F37" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H37" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I37" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J37" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K37" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L37" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M37" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N37" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O37" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3614,23 +3611,25 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="11" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="10" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3644,63 +3643,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C38" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D38" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E38" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F38" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H38" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I38" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J38" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K38" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L38" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M38" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N38" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O38" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3711,92 +3714,86 @@
       <c r="U38" s="8" t="n">
         <v/>
       </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W38" s="10" t="inlineStr">
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C39" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D39" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E39" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F39" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H39" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I39" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J39" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K39" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L39" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M39" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N39" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O39" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3804,64 +3801,60 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="10" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C40" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D40" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E40" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F40" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H40" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I40" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J40" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K40" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L40" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M40" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N40" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O40" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3871,12 +3864,12 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3888,66 +3881,72 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="10" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C41" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D41" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E41" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F41" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H41" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I41" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J41" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K41" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L41" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M41" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N41" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O41" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
@@ -3956,7 +3955,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3968,95 +3967,93 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="10" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C42" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D42" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E42" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F42" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H42" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I42" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J42" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K42" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L42" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M42" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N42" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O42" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4064,50 +4061,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C43" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D43" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E43" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F43" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I43" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J43" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K43" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L43" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M43" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N43" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O43" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4115,83 +4112,83 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C44" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D44" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E44" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F44" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H44" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I44" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J44" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K44" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L44" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M44" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N44" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O44" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4204,7 +4201,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4218,64 +4215,60 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C45" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D45" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E45" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F45" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H45" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I45" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J45" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K45" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L45" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M45" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N45" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O45" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4283,26 +4276,30 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4312,50 +4309,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C46" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D46" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E46" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F46" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H46" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I46" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J46" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K46" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L46" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M46" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N46" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O46" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,7 +4363,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="11" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4378,15 +4375,15 @@
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4396,83 +4393,83 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C47" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D47" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E47" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F47" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H47" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I47" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J47" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K47" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L47" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M47" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N47" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O47" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr"/>
@@ -4480,69 +4477,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C48" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D48" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E48" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F48" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H48" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I48" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J48" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K48" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L48" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M48" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N48" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O48" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4554,7 +4545,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="10" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4564,50 +4555,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C49" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D49" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E49" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H49" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I49" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J49" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K49" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L49" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M49" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N49" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O49" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4618,74 +4609,82 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C50" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D50" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E50" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F50" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H50" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I50" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J50" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K50" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L50" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M50" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N50" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O50" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4693,85 +4692,81 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="10" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C51" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D51" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E51" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F51" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I51" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J51" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K51" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L51" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M51" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N51" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O51" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4781,18 +4776,16 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4800,66 +4793,72 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="10" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C52" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D52" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E52" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F52" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I52" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J52" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K52" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L52" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M52" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N52" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O52" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4880,71 +4879,67 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="10" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C53" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D53" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E53" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F53" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I53" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J53" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K53" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L53" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M53" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N53" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O53" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4954,7 +4949,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4966,7 +4961,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="10" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4976,57 +4971,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C54" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D54" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E54" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F54" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H54" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I54" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J54" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K54" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L54" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M54" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N54" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O54" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5036,7 +5031,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5048,7 +5043,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="10" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5058,71 +5053,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C55" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D55" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E55" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F55" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H55" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I55" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J55" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K55" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L55" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M55" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N55" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O55" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5130,60 +5123,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="10" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C56" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D56" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E56" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F56" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H56" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I56" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J56" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K56" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L56" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M56" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N56" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O56" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5194,9 +5191,9 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
@@ -5204,166 +5201,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C57" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D57" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E57" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F57" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I57" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J57" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K57" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L57" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M57" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N57" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O57" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C58" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D58" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E58" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F58" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H58" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I58" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J58" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K58" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L58" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M58" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N58" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O58" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5378,7 +5375,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5392,50 +5389,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C59" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D59" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E59" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F59" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H59" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I59" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J59" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K59" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L59" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M59" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N59" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O59" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5445,12 +5442,12 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5462,7 +5459,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5476,56 +5473,60 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C60" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D60" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E60" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F60" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H60" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I60" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J60" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K60" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L60" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M60" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N60" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O60" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5534,7 +5535,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5548,73 +5549,69 @@
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C61" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D61" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E61" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F61" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H61" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I61" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J61" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K61" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L61" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M61" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N61" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O61" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5634,7 +5631,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="10" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5644,198 +5641,114 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C62" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D62" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E62" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F62" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H62" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I62" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J62" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K62" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L62" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M62" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N62" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O62" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="10" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>24701.18</v>
-      </c>
-      <c r="C63" t="n">
-        <v>24926.24</v>
-      </c>
-      <c r="D63" t="n">
-        <v>24662.11</v>
-      </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v>264.13</v>
-      </c>
-      <c r="I63" t="n">
-        <v>24289.3</v>
-      </c>
-      <c r="J63" t="n">
-        <v>24572.15</v>
-      </c>
-      <c r="K63" t="n">
-        <v>24665.16</v>
-      </c>
-      <c r="L63" t="n">
-        <v>24758.17</v>
-      </c>
-      <c r="M63" t="n">
-        <v>24946.1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>25134.03</v>
-      </c>
-      <c r="O63" t="n">
-        <v>25132.12</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
+      <c r="I63" s="13" t="n">
         <v>24397.98</v>
       </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
+      <c r="J63" s="13" t="n">
+        <v>24715.18</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>24785.53</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>24855.89</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>25049.67</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>25243.44</v>
+      </c>
+      <c r="O63" s="13" t="n">
         <v>25190.37</v>
       </c>
     </row>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5725,31 +5728,119 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>24934.06</v>
+      </c>
+      <c r="C63" t="n">
+        <v>24934.06</v>
+      </c>
+      <c r="D63" t="n">
+        <v>24657.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v/>
+      </c>
+      <c r="F63" t="n">
+        <v/>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>277.05</v>
+      </c>
+      <c r="I63" t="n">
+        <v>24397.98</v>
+      </c>
+      <c r="J63" t="n">
+        <v>24715.18</v>
+      </c>
+      <c r="K63" t="n">
+        <v>24785.53</v>
+      </c>
+      <c r="L63" t="n">
+        <v>24855.89</v>
+      </c>
+      <c r="M63" t="n">
+        <v>25049.67</v>
+      </c>
+      <c r="N63" t="n">
+        <v>25243.44</v>
+      </c>
+      <c r="O63" t="n">
+        <v>25190.37</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>24397.98</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>24715.18</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>24785.53</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>24855.89</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>25049.67</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>25243.44</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>25190.37</v>
+      <c r="I64" s="14" t="n">
+        <v>24379.96</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>25211.11</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,66 +644,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24145.19</v>
+        <v>23811.76</v>
       </c>
       <c r="C2" t="n">
-        <v>24163.25</v>
+        <v>23863.71</v>
       </c>
       <c r="D2" t="n">
-        <v>23749.99</v>
+        <v>23444.86</v>
       </c>
       <c r="E2" t="n">
-        <v>23924.81</v>
+        <v>23768.52</v>
       </c>
       <c r="F2" t="n">
-        <v>-387.35</v>
+        <v>-156.29</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0159</v>
+        <v>-0.0065</v>
       </c>
       <c r="H2" t="n">
-        <v>413.26</v>
+        <v>418.85</v>
       </c>
       <c r="I2" t="n">
-        <v>23947.95</v>
+        <v>23336.73</v>
       </c>
       <c r="J2" t="n">
-        <v>23958.56</v>
+        <v>23495.65</v>
       </c>
       <c r="K2" t="n">
-        <v>24159.1</v>
+        <v>23718.18</v>
       </c>
       <c r="L2" t="n">
-        <v>24359.65</v>
+        <v>23940.72</v>
       </c>
       <c r="M2" t="n">
-        <v>24465.22</v>
+        <v>24131.44</v>
       </c>
       <c r="N2" t="n">
-        <v>24570.79</v>
+        <v>24322.17</v>
       </c>
       <c r="O2" t="n">
-        <v>24866.31</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>24576.51</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -720,70 +718,74 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23811.76</v>
+        <v>23800.02</v>
       </c>
       <c r="C3" t="n">
-        <v>23863.71</v>
+        <v>23825.81</v>
       </c>
       <c r="D3" t="n">
-        <v>23444.86</v>
+        <v>23252.13</v>
       </c>
       <c r="E3" t="n">
-        <v>23768.52</v>
+        <v>23336.28</v>
       </c>
       <c r="F3" t="n">
-        <v>-156.29</v>
+        <v>-432.24</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0182</v>
       </c>
       <c r="H3" t="n">
-        <v>418.85</v>
+        <v>573.6799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>23336.73</v>
+        <v>23026.01</v>
       </c>
       <c r="J3" t="n">
-        <v>23495.65</v>
+        <v>23406.79</v>
       </c>
       <c r="K3" t="n">
-        <v>23718.18</v>
+        <v>23559.09</v>
       </c>
       <c r="L3" t="n">
-        <v>23940.72</v>
+        <v>23711.4</v>
       </c>
       <c r="M3" t="n">
-        <v>24131.44</v>
+        <v>23977.95</v>
       </c>
       <c r="N3" t="n">
-        <v>24322.17</v>
+        <v>24244.49</v>
       </c>
       <c r="O3" t="n">
-        <v>24576.51</v>
+        <v>24282.56</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
@@ -800,7 +802,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -810,67 +812,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23800.02</v>
+        <v>23420.7</v>
       </c>
       <c r="C4" t="n">
-        <v>23825.81</v>
+        <v>23565.65</v>
       </c>
       <c r="D4" t="n">
-        <v>23252.13</v>
+        <v>23248.87</v>
       </c>
       <c r="E4" t="n">
-        <v>23336.28</v>
+        <v>23412.18</v>
       </c>
       <c r="F4" t="n">
-        <v>-432.24</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0033</v>
       </c>
       <c r="H4" t="n">
-        <v>573.6799999999999</v>
+        <v>316.78</v>
       </c>
       <c r="I4" t="n">
-        <v>23026.01</v>
+        <v>22678.45</v>
       </c>
       <c r="J4" t="n">
-        <v>23406.79</v>
+        <v>22661.25</v>
       </c>
       <c r="K4" t="n">
-        <v>23559.09</v>
+        <v>23049.44</v>
       </c>
       <c r="L4" t="n">
-        <v>23711.4</v>
+        <v>23437.62</v>
       </c>
       <c r="M4" t="n">
-        <v>23977.95</v>
+        <v>23623.12</v>
       </c>
       <c r="N4" t="n">
-        <v>24244.49</v>
+        <v>23808.61</v>
       </c>
       <c r="O4" t="n">
-        <v>24282.56</v>
+        <v>24399.49</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -882,73 +880,81 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23420.7</v>
+        <v>23388.5</v>
       </c>
       <c r="C5" t="n">
-        <v>23565.65</v>
+        <v>23388.5</v>
       </c>
       <c r="D5" t="n">
-        <v>23248.87</v>
+        <v>22978.59</v>
       </c>
       <c r="E5" t="n">
-        <v>23412.18</v>
+        <v>23076.91</v>
       </c>
       <c r="F5" t="n">
-        <v>75.90000000000001</v>
+        <v>-335.27</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.0143</v>
       </c>
       <c r="H5" t="n">
-        <v>316.78</v>
+        <v>409.91</v>
       </c>
       <c r="I5" t="n">
-        <v>22678.45</v>
+        <v>22932.09</v>
       </c>
       <c r="J5" t="n">
-        <v>22661.25</v>
+        <v>23097.86</v>
       </c>
       <c r="K5" t="n">
-        <v>23049.44</v>
+        <v>23253.79</v>
       </c>
       <c r="L5" t="n">
-        <v>23437.62</v>
+        <v>23409.72</v>
       </c>
       <c r="M5" t="n">
-        <v>23623.12</v>
+        <v>23570.57</v>
       </c>
       <c r="N5" t="n">
-        <v>23808.61</v>
+        <v>23731.42</v>
       </c>
       <c r="O5" t="n">
-        <v>24399.49</v>
+        <v>23882.43</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -960,67 +966,65 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23388.5</v>
+        <v>22952.09</v>
       </c>
       <c r="C6" t="n">
-        <v>23388.5</v>
+        <v>22962.46</v>
       </c>
       <c r="D6" t="n">
-        <v>22978.59</v>
+        <v>22518</v>
       </c>
       <c r="E6" t="n">
-        <v>23076.91</v>
+        <v>22671.86</v>
       </c>
       <c r="F6" t="n">
-        <v>-335.27</v>
+        <v>-405.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0176</v>
       </c>
       <c r="H6" t="n">
-        <v>409.91</v>
+        <v>444.46</v>
       </c>
       <c r="I6" t="n">
-        <v>22932.09</v>
+        <v>22568.68</v>
       </c>
       <c r="J6" t="n">
-        <v>23097.86</v>
+        <v>22613.68</v>
       </c>
       <c r="K6" t="n">
-        <v>23253.79</v>
+        <v>22871.96</v>
       </c>
       <c r="L6" t="n">
-        <v>23409.72</v>
+        <v>23130.23</v>
       </c>
       <c r="M6" t="n">
-        <v>23570.57</v>
+        <v>23281.87</v>
       </c>
       <c r="N6" t="n">
-        <v>23731.42</v>
+        <v>23433.5</v>
       </c>
       <c r="O6" t="n">
-        <v>23882.43</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
+        <v>23798.41</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
@@ -1046,7 +1050,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1056,134 +1060,136 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C7" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D7" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E7" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F7" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H7" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I7" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J7" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K7" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L7" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M7" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N7" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O7" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C8" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D8" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E8" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F8" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H8" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I8" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J8" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K8" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L8" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M8" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N8" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O8" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,85 +1197,79 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C9" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D9" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E9" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H9" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I9" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J9" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K9" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L9" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M9" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N9" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O9" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,79 +1277,85 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C10" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D10" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E10" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F10" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H10" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I10" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J10" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K10" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L10" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M10" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N10" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O10" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,25 +1366,25 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1392,50 +1398,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C11" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D11" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E11" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F11" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H11" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I11" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J11" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K11" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L11" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M11" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N11" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O11" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,7 +1452,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1464,7 +1470,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1478,50 +1484,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C12" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D12" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E12" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F12" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H12" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I12" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J12" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K12" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L12" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M12" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N12" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O12" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1532,82 +1538,78 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C13" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D13" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E13" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F13" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H13" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I13" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J13" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K13" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L13" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M13" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N13" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O13" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1618,78 +1620,80 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C14" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D14" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E14" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F14" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H14" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I14" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J14" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K14" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L14" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M14" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N14" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O14" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1700,80 +1704,78 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C15" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D15" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E15" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F15" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H15" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I15" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J15" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K15" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L15" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M15" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N15" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O15" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1784,78 +1786,78 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C16" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D16" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E16" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F16" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H16" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I16" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J16" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K16" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L16" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M16" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N16" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O16" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1866,78 +1868,80 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C17" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D17" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E17" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F17" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H17" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I17" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J17" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K17" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L17" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M17" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N17" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O17" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,17 +1949,19 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1964,64 +1970,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C18" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D18" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E18" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F18" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H18" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I18" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J18" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K18" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L18" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M18" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N18" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O18" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,12 +2035,10 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2050,64 +2054,60 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C19" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D19" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E19" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F19" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H19" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I19" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J19" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K19" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L19" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M19" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N19" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O19" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2118,23 +2118,27 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2144,83 +2148,83 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C20" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D20" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E20" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F20" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H20" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I20" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J20" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K20" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L20" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M20" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N20" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O20" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2228,134 +2232,136 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C21" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D21" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E21" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H21" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I21" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J21" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K21" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L21" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M21" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N21" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O21" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C22" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D22" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E22" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F22" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H22" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I22" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J22" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K22" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L22" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M22" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N22" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O22" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2366,25 +2372,21 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2398,63 +2400,67 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C23" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D23" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E23" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H23" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I23" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J23" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K23" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L23" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M23" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N23" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O23" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2466,95 +2472,93 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C24" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D24" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E24" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F24" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H24" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I24" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J24" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K24" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L24" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M24" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N24" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O24" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2562,220 +2566,220 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C25" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D25" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E25" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F25" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H25" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I25" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J25" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K25" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L25" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M25" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N25" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O25" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C26" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D26" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E26" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F26" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H26" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I26" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J26" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K26" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L26" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M26" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N26" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O26" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C27" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D27" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E27" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F27" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H27" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I27" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J27" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K27" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L27" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M27" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N27" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O27" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2786,27 +2790,23 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2816,50 +2816,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C28" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D28" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E28" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F28" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H28" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I28" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J28" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K28" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L28" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M28" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N28" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O28" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,23 +2870,27 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2896,50 +2900,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C29" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D29" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E29" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F29" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I29" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J29" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K29" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L29" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M29" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N29" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O29" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2950,27 +2954,23 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2980,50 +2980,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C30" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D30" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E30" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F30" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I30" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J30" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K30" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L30" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M30" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N30" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O30" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3031,18 +3031,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3050,60 +3050,64 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C31" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D31" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E31" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F31" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H31" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I31" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J31" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K31" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L31" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M31" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N31" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O31" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3111,18 +3115,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3130,64 +3134,60 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C32" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D32" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E32" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F32" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H32" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I32" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J32" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K32" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L32" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M32" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N32" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O32" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3195,17 +3195,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3214,60 +3216,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C33" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D33" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E33" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F33" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H33" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I33" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J33" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K33" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L33" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M33" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N33" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O33" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,20 +3281,16 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3296,7 +3298,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3310,63 +3312,69 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C34" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D34" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E34" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F34" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H34" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I34" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J34" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K34" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L34" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M34" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N34" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O34" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3378,148 +3386,144 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C35" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D35" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E35" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F35" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H35" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I35" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J35" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K35" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L35" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M35" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N35" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O35" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C36" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D36" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E36" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F36" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H36" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I36" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J36" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K36" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L36" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M36" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N36" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O36" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3530,23 +3534,25 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3560,63 +3566,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C37" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D37" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E37" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F37" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H37" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I37" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J37" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K37" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L37" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M37" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N37" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O37" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3627,92 +3637,86 @@
       <c r="U37" s="8" t="n">
         <v/>
       </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C38" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D38" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E38" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F38" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H38" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I38" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J38" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K38" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L38" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M38" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N38" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O38" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3720,64 +3724,60 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C39" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D39" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E39" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F39" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H39" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I39" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J39" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K39" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L39" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M39" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N39" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O39" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3804,66 +3804,72 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C40" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D40" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E40" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F40" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H40" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I40" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J40" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K40" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L40" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M40" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N40" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O40" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
@@ -3872,7 +3878,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3884,95 +3890,93 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C41" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D41" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E41" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F41" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H41" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I41" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J41" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K41" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L41" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M41" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N41" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O41" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3980,50 +3984,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C42" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D42" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E42" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F42" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I42" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J42" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K42" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L42" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M42" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N42" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O42" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4031,83 +4035,83 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C43" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D43" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E43" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F43" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H43" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I43" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J43" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K43" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L43" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M43" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N43" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O43" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4120,7 +4124,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4134,64 +4138,60 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C44" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D44" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E44" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F44" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H44" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I44" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J44" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K44" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L44" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M44" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N44" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O44" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,26 +4199,30 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4228,50 +4232,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C45" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D45" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E45" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F45" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H45" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I45" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J45" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K45" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L45" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M45" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N45" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O45" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4282,7 +4286,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4294,15 +4298,15 @@
       </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4312,83 +4316,83 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C46" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D46" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E46" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F46" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H46" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I46" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J46" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K46" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L46" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M46" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N46" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O46" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4396,69 +4400,63 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C47" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D47" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E47" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F47" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H47" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I47" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J47" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K47" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L47" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M47" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N47" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O47" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4470,7 +4468,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4480,50 +4478,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C48" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D48" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E48" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F48" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H48" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I48" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J48" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K48" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L48" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M48" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N48" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O48" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4534,74 +4532,82 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="S48" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C49" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D49" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E49" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F49" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H49" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I49" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J49" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K49" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L49" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M49" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N49" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O49" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4609,85 +4615,81 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C50" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D50" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E50" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F50" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I50" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J50" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K50" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L50" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M50" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N50" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O50" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4697,18 +4699,16 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4716,66 +4716,72 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C51" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D51" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E51" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F51" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I51" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J51" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K51" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L51" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M51" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N51" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O51" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4796,71 +4802,67 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C52" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D52" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E52" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F52" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I52" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J52" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K52" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L52" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M52" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N52" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O52" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4870,7 +4872,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4882,7 +4884,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4892,57 +4894,57 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C53" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D53" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E53" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F53" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H53" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I53" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J53" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K53" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L53" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M53" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N53" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O53" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4952,7 +4954,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4964,7 +4966,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4974,71 +4976,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C54" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D54" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E54" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F54" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H54" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I54" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J54" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K54" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L54" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M54" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N54" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O54" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5046,60 +5046,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C55" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D55" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E55" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F55" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H55" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I55" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J55" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K55" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L55" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M55" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N55" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O55" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5110,9 +5114,9 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S55" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -5120,166 +5124,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C56" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D56" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E56" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F56" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I56" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J56" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K56" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L56" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M56" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N56" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O56" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C57" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D57" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E57" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F57" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H57" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I57" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J57" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K57" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L57" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M57" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N57" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O57" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5294,7 +5298,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5308,50 +5312,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C58" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D58" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E58" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F58" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H58" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I58" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J58" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K58" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L58" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M58" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N58" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O58" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5361,12 +5365,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5378,7 +5382,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5392,56 +5396,60 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C59" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D59" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E59" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F59" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H59" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I59" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J59" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K59" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L59" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M59" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N59" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O59" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5450,7 +5458,7 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5462,75 +5470,71 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C60" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D60" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E60" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F60" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H60" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I60" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J60" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K60" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L60" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M60" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N60" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O60" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5550,7 +5554,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5560,155 +5564,159 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C61" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D61" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E61" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F61" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H61" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I61" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J61" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K61" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L61" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M61" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N61" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O61" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24701.18</v>
+        <v>24789.91</v>
       </c>
       <c r="C62" t="n">
-        <v>24926.24</v>
+        <v>24789.91</v>
       </c>
       <c r="D62" t="n">
-        <v>24662.11</v>
+        <v>24596.6</v>
       </c>
       <c r="E62" t="n">
-        <v>24917.6</v>
+        <v/>
       </c>
       <c r="F62" t="n">
-        <v>111.97</v>
+        <v/>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0045</v>
+        <v/>
       </c>
       <c r="H62" t="n">
-        <v>264.13</v>
+        <v>193.31</v>
       </c>
       <c r="I62" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J62" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K62" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L62" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M62" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N62" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O62" t="n">
-        <v>25132.12</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+        <v>25190.37</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S62" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5716,131 +5724,39 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>24934.06</v>
-      </c>
-      <c r="C63" t="n">
-        <v>24934.06</v>
-      </c>
-      <c r="D63" t="n">
-        <v>24657.01</v>
-      </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v>277.05</v>
-      </c>
-      <c r="I63" t="n">
-        <v>24397.98</v>
-      </c>
-      <c r="J63" t="n">
-        <v>24715.18</v>
-      </c>
-      <c r="K63" t="n">
-        <v>24785.53</v>
-      </c>
-      <c r="L63" t="n">
-        <v>24855.89</v>
-      </c>
-      <c r="M63" t="n">
-        <v>25049.67</v>
-      </c>
-      <c r="N63" t="n">
-        <v>25243.44</v>
-      </c>
-      <c r="O63" t="n">
-        <v>25190.37</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
-        <v>24379.96</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>25211.11</v>
+      <c r="I63" s="14" t="n">
+        <v>24403.29</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O63" s="14" t="n">
+        <v>24983.22</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,9 +118,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5654,25 +5651,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24789.91</v>
+        <v>24934.06</v>
       </c>
       <c r="C62" t="n">
-        <v>24789.91</v>
+        <v>24934.06</v>
       </c>
       <c r="D62" t="n">
-        <v>24596.6</v>
+        <v>24657.01</v>
       </c>
       <c r="E62" t="n">
-        <v/>
+        <v>24667.24</v>
       </c>
       <c r="F62" t="n">
-        <v/>
+        <v>-250.36</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v/>
+        <v>-0.01</v>
       </c>
       <c r="H62" t="n">
-        <v>193.31</v>
+        <v>277.05</v>
       </c>
       <c r="I62" t="n">
         <v>24397.98</v>
@@ -5695,24 +5692,22 @@
       <c r="O62" t="n">
         <v>25190.37</v>
       </c>
-      <c r="P62" s="6" t="inlineStr">
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5729,34 +5724,38 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="14" t="n">
-        <v>24403.29</v>
-      </c>
-      <c r="J63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="14" t="n">
-        <v>24983.22</v>
+      <c r="I63" s="13" t="n">
+        <v>24379.96</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>24326.04</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>24528.71</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>24731.39</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>24805.77</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>24880.14</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>25211.11</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5731,31 +5731,113 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>24789.91</v>
+      </c>
+      <c r="C63" t="n">
+        <v>24789.91</v>
+      </c>
+      <c r="D63" t="n">
+        <v>24574.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>24713.78</v>
+      </c>
+      <c r="F63" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="H63" t="n">
+        <v>215.16</v>
+      </c>
+      <c r="I63" t="n">
+        <v>24379.96</v>
+      </c>
+      <c r="J63" t="n">
+        <v>24326.04</v>
+      </c>
+      <c r="K63" t="n">
+        <v>24528.71</v>
+      </c>
+      <c r="L63" t="n">
+        <v>24731.39</v>
+      </c>
+      <c r="M63" t="n">
+        <v>24805.77</v>
+      </c>
+      <c r="N63" t="n">
+        <v>24880.14</v>
+      </c>
+      <c r="O63" t="n">
+        <v>25211.11</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>24379.96</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>24326.04</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>24528.71</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>24731.39</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>24805.77</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>24880.14</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>25211.11</v>
+      <c r="I64" s="13" t="n">
+        <v>24359.59</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>24514.34</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>24606.2</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>24698.05</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>24821.36</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>24944.66</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>25005.07</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -118,6 +118,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5746,13 +5749,13 @@
         <v>24574.75</v>
       </c>
       <c r="E63" t="n">
-        <v>24713.78</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>46.54</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0019</v>
+        <v/>
       </c>
       <c r="H63" t="n">
         <v>215.16</v>
@@ -5778,8 +5781,10 @@
       <c r="O63" t="n">
         <v>25211.11</v>
       </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="n">
         <v/>
@@ -5787,9 +5792,9 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5806,37 +5811,33 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
+      <c r="I64" s="14" t="n">
         <v>24359.59</v>
       </c>
-      <c r="J64" s="13" t="n">
-        <v>24514.34</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>24606.2</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>24698.05</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>24821.36</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>24944.66</v>
-      </c>
-      <c r="O64" s="13" t="n">
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
         <v>25005.07</v>
       </c>
     </row>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,62 +644,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23811.76</v>
+        <v>23800.02</v>
       </c>
       <c r="C2" t="n">
-        <v>23863.71</v>
+        <v>23825.81</v>
       </c>
       <c r="D2" t="n">
-        <v>23444.86</v>
+        <v>23252.13</v>
       </c>
       <c r="E2" t="n">
-        <v>23768.52</v>
+        <v>23336.28</v>
       </c>
       <c r="F2" t="n">
-        <v>-156.29</v>
+        <v>-432.24</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0182</v>
       </c>
       <c r="H2" t="n">
-        <v>418.85</v>
+        <v>573.6799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>23336.73</v>
+        <v>23026.01</v>
       </c>
       <c r="J2" t="n">
-        <v>23495.65</v>
+        <v>23406.79</v>
       </c>
       <c r="K2" t="n">
-        <v>23718.18</v>
+        <v>23559.09</v>
       </c>
       <c r="L2" t="n">
-        <v>23940.72</v>
+        <v>23711.4</v>
       </c>
       <c r="M2" t="n">
-        <v>24131.44</v>
+        <v>23977.95</v>
       </c>
       <c r="N2" t="n">
-        <v>24322.17</v>
+        <v>24244.49</v>
       </c>
       <c r="O2" t="n">
-        <v>24576.51</v>
+        <v>24282.56</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -718,79 +718,71 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23800.02</v>
+        <v>23420.7</v>
       </c>
       <c r="C3" t="n">
-        <v>23825.81</v>
+        <v>23565.65</v>
       </c>
       <c r="D3" t="n">
-        <v>23252.13</v>
+        <v>23248.87</v>
       </c>
       <c r="E3" t="n">
-        <v>23336.28</v>
+        <v>23412.18</v>
       </c>
       <c r="F3" t="n">
-        <v>-432.24</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0033</v>
       </c>
       <c r="H3" t="n">
-        <v>573.6799999999999</v>
+        <v>316.78</v>
       </c>
       <c r="I3" t="n">
-        <v>23026.01</v>
+        <v>22678.45</v>
       </c>
       <c r="J3" t="n">
-        <v>23406.79</v>
+        <v>22661.25</v>
       </c>
       <c r="K3" t="n">
-        <v>23559.09</v>
+        <v>23049.44</v>
       </c>
       <c r="L3" t="n">
-        <v>23711.4</v>
+        <v>23437.62</v>
       </c>
       <c r="M3" t="n">
-        <v>23977.95</v>
+        <v>23623.12</v>
       </c>
       <c r="N3" t="n">
-        <v>24244.49</v>
+        <v>23808.61</v>
       </c>
       <c r="O3" t="n">
-        <v>24282.56</v>
+        <v>24399.49</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -802,73 +794,81 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23420.7</v>
+        <v>23388.5</v>
       </c>
       <c r="C4" t="n">
-        <v>23565.65</v>
+        <v>23388.5</v>
       </c>
       <c r="D4" t="n">
-        <v>23248.87</v>
+        <v>22978.59</v>
       </c>
       <c r="E4" t="n">
-        <v>23412.18</v>
+        <v>23076.91</v>
       </c>
       <c r="F4" t="n">
-        <v>75.90000000000001</v>
+        <v>-335.27</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.0143</v>
       </c>
       <c r="H4" t="n">
-        <v>316.78</v>
+        <v>409.91</v>
       </c>
       <c r="I4" t="n">
-        <v>22678.45</v>
+        <v>22932.09</v>
       </c>
       <c r="J4" t="n">
-        <v>22661.25</v>
+        <v>23097.86</v>
       </c>
       <c r="K4" t="n">
-        <v>23049.44</v>
+        <v>23253.79</v>
       </c>
       <c r="L4" t="n">
-        <v>23437.62</v>
+        <v>23409.72</v>
       </c>
       <c r="M4" t="n">
-        <v>23623.12</v>
+        <v>23570.57</v>
       </c>
       <c r="N4" t="n">
-        <v>23808.61</v>
+        <v>23731.42</v>
       </c>
       <c r="O4" t="n">
-        <v>24399.49</v>
+        <v>23882.43</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -880,67 +880,65 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23388.5</v>
+        <v>22952.09</v>
       </c>
       <c r="C5" t="n">
-        <v>23388.5</v>
+        <v>22962.46</v>
       </c>
       <c r="D5" t="n">
-        <v>22978.59</v>
+        <v>22518</v>
       </c>
       <c r="E5" t="n">
-        <v>23076.91</v>
+        <v>22671.86</v>
       </c>
       <c r="F5" t="n">
-        <v>-335.27</v>
+        <v>-405.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0176</v>
       </c>
       <c r="H5" t="n">
-        <v>409.91</v>
+        <v>444.46</v>
       </c>
       <c r="I5" t="n">
-        <v>22932.09</v>
+        <v>22568.68</v>
       </c>
       <c r="J5" t="n">
-        <v>23097.86</v>
+        <v>22613.68</v>
       </c>
       <c r="K5" t="n">
-        <v>23253.79</v>
+        <v>22871.96</v>
       </c>
       <c r="L5" t="n">
-        <v>23409.72</v>
+        <v>23130.23</v>
       </c>
       <c r="M5" t="n">
-        <v>23570.57</v>
+        <v>23281.87</v>
       </c>
       <c r="N5" t="n">
-        <v>23731.42</v>
+        <v>23433.5</v>
       </c>
       <c r="O5" t="n">
-        <v>23882.43</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
+        <v>23798.41</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
@@ -966,7 +964,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -976,134 +974,136 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C6" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D6" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E6" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F6" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H6" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I6" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J6" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K6" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L6" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M6" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N6" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O6" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C7" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D7" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E7" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F7" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H7" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I7" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J7" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K7" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L7" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M7" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N7" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O7" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,85 +1111,79 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C8" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D8" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E8" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F8" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H8" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I8" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J8" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K8" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L8" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M8" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N8" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O8" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1197,79 +1191,85 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C9" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D9" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E9" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F9" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H9" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I9" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J9" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K9" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L9" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M9" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N9" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O9" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1280,25 +1280,25 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1312,50 +1312,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C10" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D10" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E10" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F10" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H10" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I10" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J10" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K10" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L10" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M10" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N10" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O10" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1366,7 +1366,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="11" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1384,7 +1384,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1398,50 +1398,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C11" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D11" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E11" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F11" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H11" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I11" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J11" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K11" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L11" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M11" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N11" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O11" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1452,82 +1452,78 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C12" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D12" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E12" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F12" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H12" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I12" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J12" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K12" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L12" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M12" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N12" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O12" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1538,78 +1534,80 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C13" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D13" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E13" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F13" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H13" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I13" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J13" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K13" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L13" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M13" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N13" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O13" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1620,80 +1618,78 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C14" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D14" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E14" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F14" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H14" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I14" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J14" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K14" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L14" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M14" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N14" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O14" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1704,78 +1700,78 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C15" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D15" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E15" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F15" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H15" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I15" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J15" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K15" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L15" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M15" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N15" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O15" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1786,78 +1782,80 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C16" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D16" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E16" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F16" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H16" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I16" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J16" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K16" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L16" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M16" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N16" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O16" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,17 +1863,19 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U16" s="8" t="n">
@@ -1884,64 +1884,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C17" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D17" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E17" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F17" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H17" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I17" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J17" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K17" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L17" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M17" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N17" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O17" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,12 +1949,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1970,64 +1968,60 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C18" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D18" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E18" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F18" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H18" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I18" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J18" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K18" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L18" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M18" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N18" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O18" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2038,23 +2032,27 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2064,83 +2062,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C19" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D19" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E19" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F19" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H19" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I19" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J19" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K19" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L19" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M19" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N19" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O19" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2148,134 +2146,136 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C20" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D20" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E20" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F20" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H20" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I20" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J20" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K20" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L20" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M20" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N20" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O20" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="10" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C21" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D21" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E21" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F21" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H21" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I21" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J21" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K21" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L21" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M21" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N21" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O21" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,25 +2286,21 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="10" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2318,63 +2314,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C22" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D22" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E22" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H22" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I22" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J22" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K22" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L22" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M22" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N22" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O22" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2386,95 +2386,93 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="10" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C23" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D23" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E23" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F23" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H23" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I23" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J23" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K23" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L23" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M23" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N23" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O23" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2482,220 +2480,220 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C24" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D24" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E24" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F24" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H24" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I24" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J24" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K24" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L24" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M24" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N24" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O24" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C25" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D25" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E25" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F25" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H25" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I25" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J25" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K25" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L25" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M25" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N25" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O25" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C26" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D26" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E26" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F26" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H26" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I26" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J26" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K26" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L26" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M26" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N26" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O26" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2706,27 +2704,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="11" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2736,50 +2730,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C27" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D27" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E27" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F27" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H27" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I27" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J27" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K27" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L27" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M27" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N27" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O27" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2790,23 +2784,27 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="11" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2816,50 +2814,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C28" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D28" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E28" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F28" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H28" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I28" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J28" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K28" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L28" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M28" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N28" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O28" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2870,27 +2868,23 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="11" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2900,50 +2894,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C29" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D29" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E29" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F29" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I29" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J29" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K29" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L29" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M29" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N29" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O29" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2951,18 +2945,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2970,60 +2964,64 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C30" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D30" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E30" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F30" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H30" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I30" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J30" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K30" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L30" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M30" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N30" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O30" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3031,18 +3029,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3050,64 +3048,60 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C31" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D31" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E31" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F31" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H31" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I31" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J31" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K31" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L31" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M31" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N31" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O31" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3115,17 +3109,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3134,60 +3130,64 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C32" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D32" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E32" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F32" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H32" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I32" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J32" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K32" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L32" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M32" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N32" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O32" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3195,20 +3195,16 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3216,7 +3212,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3230,63 +3226,69 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C33" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D33" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E33" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F33" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H33" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I33" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J33" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K33" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L33" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M33" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N33" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O33" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3300,146 +3302,142 @@
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C34" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D34" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E34" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F34" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H34" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I34" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J34" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K34" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L34" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M34" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N34" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O34" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="10" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C35" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D35" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E35" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F35" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H35" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I35" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J35" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K35" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L35" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M35" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N35" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O35" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3450,23 +3448,25 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="11" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="10" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3480,63 +3480,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C36" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D36" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E36" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F36" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H36" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I36" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J36" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K36" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L36" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M36" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N36" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O36" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3547,92 +3551,86 @@
       <c r="U36" s="8" t="n">
         <v/>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W36" s="10" t="inlineStr">
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C37" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D37" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E37" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F37" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H37" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I37" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J37" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K37" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L37" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M37" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N37" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O37" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3640,64 +3638,60 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="10" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C38" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D38" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E38" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F38" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H38" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I38" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J38" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K38" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L38" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M38" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N38" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O38" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3707,12 +3701,12 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3724,66 +3718,72 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="10" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C39" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D39" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E39" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F39" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H39" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I39" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J39" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K39" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L39" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M39" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N39" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O39" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3804,95 +3804,93 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="10" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C40" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D40" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E40" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F40" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H40" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I40" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J40" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K40" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L40" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M40" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N40" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O40" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3900,50 +3898,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C41" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D41" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E41" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F41" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I41" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J41" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K41" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L41" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M41" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N41" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O41" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3951,83 +3949,83 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C42" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D42" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E42" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F42" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H42" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I42" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J42" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K42" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L42" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M42" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N42" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O42" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4040,7 +4038,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="11" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4054,64 +4052,60 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C43" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D43" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E43" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F43" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H43" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I43" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J43" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K43" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L43" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M43" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N43" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O43" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4119,26 +4113,30 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4148,50 +4146,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C44" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D44" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E44" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F44" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H44" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I44" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J44" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K44" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L44" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M44" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N44" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O44" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4202,7 +4200,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4214,15 +4212,15 @@
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4232,83 +4230,83 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C45" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D45" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E45" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F45" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H45" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I45" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J45" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K45" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L45" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M45" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N45" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O45" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4316,69 +4314,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C46" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D46" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E46" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F46" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H46" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I46" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J46" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K46" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L46" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M46" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N46" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O46" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4390,7 +4382,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="10" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4400,50 +4392,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C47" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D47" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E47" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H47" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I47" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J47" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K47" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L47" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M47" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N47" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O47" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4454,74 +4446,82 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="10" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C48" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D48" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E48" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F48" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H48" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I48" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J48" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K48" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L48" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M48" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N48" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O48" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4529,85 +4529,81 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="10" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C49" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D49" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E49" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F49" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I49" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J49" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K49" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L49" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M49" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N49" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O49" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4617,18 +4613,16 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4636,66 +4630,72 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C50" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D50" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E50" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F50" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I50" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J50" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K50" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L50" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M50" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N50" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O50" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4716,71 +4716,67 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="10" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C51" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D51" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E51" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F51" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I51" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J51" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K51" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L51" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M51" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N51" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O51" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4790,7 +4786,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4802,7 +4798,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="10" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4812,57 +4808,57 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C52" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D52" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E52" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F52" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I52" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J52" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K52" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L52" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M52" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N52" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O52" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4872,7 +4868,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4884,7 +4880,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="10" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4894,71 +4890,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C53" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D53" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E53" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F53" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H53" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I53" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J53" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K53" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L53" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M53" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N53" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O53" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4966,60 +4960,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="10" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C54" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D54" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E54" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F54" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H54" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I54" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J54" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K54" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L54" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M54" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N54" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O54" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5030,9 +5028,9 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -5040,166 +5038,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C55" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D55" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E55" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F55" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I55" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J55" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K55" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L55" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M55" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N55" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O55" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C56" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D56" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E56" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F56" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H56" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I56" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J56" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K56" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L56" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M56" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N56" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O56" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5214,7 +5212,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5228,50 +5226,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C57" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D57" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E57" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F57" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H57" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I57" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J57" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K57" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L57" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M57" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N57" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O57" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5281,12 +5279,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5298,7 +5296,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5312,56 +5310,60 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C58" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D58" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E58" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F58" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H58" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I58" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J58" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K58" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L58" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M58" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N58" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O58" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5370,7 +5372,7 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5384,73 +5386,69 @@
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C59" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D59" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E59" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F59" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H59" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I59" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J59" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K59" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L59" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M59" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N59" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O59" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5470,7 +5468,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="10" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5480,155 +5478,157 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C60" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D60" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E60" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F60" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H60" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I60" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J60" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K60" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L60" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M60" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N60" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O60" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="10" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C61" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D61" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E61" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F61" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H61" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I61" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J61" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K61" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L61" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M61" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N61" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O61" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5636,81 +5636,79 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="10" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C62" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D62" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E62" t="n">
-        <v>24667.24</v>
+        <v/>
       </c>
       <c r="F62" t="n">
-        <v>-250.36</v>
+        <v/>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.01</v>
+        <v/>
       </c>
       <c r="H62" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I62" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J62" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K62" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L62" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M62" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N62" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O62" t="n">
-        <v>25190.37</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
+        <v>25211.11</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5722,122 +5720,38 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="10" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>24789.91</v>
-      </c>
-      <c r="C63" t="n">
-        <v>24789.91</v>
-      </c>
-      <c r="D63" t="n">
-        <v>24574.75</v>
-      </c>
-      <c r="E63" t="n">
-        <v/>
-      </c>
-      <c r="F63" t="n">
-        <v/>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H63" t="n">
-        <v>215.16</v>
-      </c>
-      <c r="I63" t="n">
-        <v>24379.96</v>
-      </c>
-      <c r="J63" t="n">
-        <v>24326.04</v>
-      </c>
-      <c r="K63" t="n">
-        <v>24528.71</v>
-      </c>
-      <c r="L63" t="n">
-        <v>24731.39</v>
-      </c>
-      <c r="M63" t="n">
-        <v>24805.77</v>
-      </c>
-      <c r="N63" t="n">
-        <v>24880.14</v>
-      </c>
-      <c r="O63" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
+      <c r="I63" s="14" t="n">
         <v>24359.59</v>
       </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
+      <c r="J63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N63" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O63" s="14" t="n">
         <v>25005.07</v>
       </c>
     </row>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5663,13 +5663,13 @@
         <v>24574.75</v>
       </c>
       <c r="E62" t="n">
-        <v/>
+        <v>24713.78</v>
       </c>
       <c r="F62" t="n">
-        <v/>
+        <v>46.54</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v/>
+        <v>0.0019</v>
       </c>
       <c r="H62" t="n">
         <v>215.16</v>
@@ -5695,64 +5695,150 @@
       <c r="O62" t="n">
         <v>25211.11</v>
       </c>
-      <c r="P62" s="6" t="inlineStr">
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>24480.57</v>
+      </c>
+      <c r="C63" t="n">
+        <v>24606.15</v>
+      </c>
+      <c r="D63" t="n">
+        <v>24357.69</v>
+      </c>
+      <c r="E63" t="n">
+        <v/>
+      </c>
+      <c r="F63" t="n">
+        <v/>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H63" t="n">
+        <v>248.46</v>
+      </c>
+      <c r="I63" t="n">
+        <v>24359.59</v>
+      </c>
+      <c r="J63" t="n">
+        <v>24514.34</v>
+      </c>
+      <c r="K63" t="n">
+        <v>24606.2</v>
+      </c>
+      <c r="L63" t="n">
+        <v>24698.05</v>
+      </c>
+      <c r="M63" t="n">
+        <v>24821.36</v>
+      </c>
+      <c r="N63" t="n">
+        <v>24944.66</v>
+      </c>
+      <c r="O63" t="n">
+        <v>25005.07</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="12" t="inlineStr">
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="12" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="14" t="n">
-        <v>24359.59</v>
-      </c>
-      <c r="J63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="14" t="n">
-        <v>25005.07</v>
+      <c r="I64" s="14" t="n">
+        <v>24109.23</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>24854.61</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,8 +118,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5813,34 +5806,6 @@
       </c>
       <c r="X63" t="inlineStr"/>
     </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="n">
-        <v>24109.23</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>24854.61</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5738,13 +5735,13 @@
         <v>24357.69</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>24604.29</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>-109.49</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>-0.0044</v>
       </c>
       <c r="H63" t="n">
         <v>248.46</v>
@@ -5772,22 +5769,22 @@
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5805,6 +5802,92 @@
         </is>
       </c>
       <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>24723.85</v>
+      </c>
+      <c r="C64" t="n">
+        <v>24862.98</v>
+      </c>
+      <c r="D64" t="n">
+        <v>24703.92</v>
+      </c>
+      <c r="E64" t="n">
+        <v>24750.78</v>
+      </c>
+      <c r="F64" t="n">
+        <v>146.49</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H64" t="n">
+        <v>159.06</v>
+      </c>
+      <c r="I64" t="n">
+        <v>24109.23</v>
+      </c>
+      <c r="J64" t="n">
+        <v>24417.01</v>
+      </c>
+      <c r="K64" t="n">
+        <v>24480.06</v>
+      </c>
+      <c r="L64" t="n">
+        <v>24543.1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>24728.52</v>
+      </c>
+      <c r="N64" t="n">
+        <v>24913.93</v>
+      </c>
+      <c r="O64" t="n">
+        <v>24854.61</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,11 +110,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,67 +637,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23800.02</v>
+        <v>23420.7</v>
       </c>
       <c r="C2" t="n">
-        <v>23825.81</v>
+        <v>23565.65</v>
       </c>
       <c r="D2" t="n">
-        <v>23252.13</v>
+        <v>23248.87</v>
       </c>
       <c r="E2" t="n">
-        <v>23336.28</v>
+        <v>23412.18</v>
       </c>
       <c r="F2" t="n">
-        <v>-432.24</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0033</v>
       </c>
       <c r="H2" t="n">
-        <v>573.6799999999999</v>
+        <v>316.78</v>
       </c>
       <c r="I2" t="n">
-        <v>23026.01</v>
+        <v>22678.45</v>
       </c>
       <c r="J2" t="n">
-        <v>23406.79</v>
+        <v>22661.25</v>
       </c>
       <c r="K2" t="n">
-        <v>23559.09</v>
+        <v>23049.44</v>
       </c>
       <c r="L2" t="n">
-        <v>23711.4</v>
+        <v>23437.62</v>
       </c>
       <c r="M2" t="n">
-        <v>23977.95</v>
+        <v>23623.12</v>
       </c>
       <c r="N2" t="n">
-        <v>24244.49</v>
+        <v>23808.61</v>
       </c>
       <c r="O2" t="n">
-        <v>24282.56</v>
+        <v>24399.49</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -708,71 +707,79 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23420.7</v>
+        <v>23388.5</v>
       </c>
       <c r="C3" t="n">
-        <v>23565.65</v>
+        <v>23388.5</v>
       </c>
       <c r="D3" t="n">
-        <v>23248.87</v>
+        <v>22978.59</v>
       </c>
       <c r="E3" t="n">
-        <v>23412.18</v>
+        <v>23076.91</v>
       </c>
       <c r="F3" t="n">
-        <v>75.90000000000001</v>
+        <v>-335.27</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.0143</v>
       </c>
       <c r="H3" t="n">
-        <v>316.78</v>
+        <v>409.91</v>
       </c>
       <c r="I3" t="n">
-        <v>22678.45</v>
+        <v>22932.09</v>
       </c>
       <c r="J3" t="n">
-        <v>22661.25</v>
+        <v>23097.86</v>
       </c>
       <c r="K3" t="n">
-        <v>23049.44</v>
+        <v>23253.79</v>
       </c>
       <c r="L3" t="n">
-        <v>23437.62</v>
+        <v>23409.72</v>
       </c>
       <c r="M3" t="n">
-        <v>23623.12</v>
+        <v>23570.57</v>
       </c>
       <c r="N3" t="n">
-        <v>23808.61</v>
+        <v>23731.42</v>
       </c>
       <c r="O3" t="n">
-        <v>24399.49</v>
+        <v>23882.43</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -784,67 +791,65 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23388.5</v>
+        <v>22952.09</v>
       </c>
       <c r="C4" t="n">
-        <v>23388.5</v>
+        <v>22962.46</v>
       </c>
       <c r="D4" t="n">
-        <v>22978.59</v>
+        <v>22518</v>
       </c>
       <c r="E4" t="n">
-        <v>23076.91</v>
+        <v>22671.86</v>
       </c>
       <c r="F4" t="n">
-        <v>-335.27</v>
+        <v>-405.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0176</v>
       </c>
       <c r="H4" t="n">
-        <v>409.91</v>
+        <v>444.46</v>
       </c>
       <c r="I4" t="n">
-        <v>22932.09</v>
+        <v>22568.68</v>
       </c>
       <c r="J4" t="n">
-        <v>23097.86</v>
+        <v>22613.68</v>
       </c>
       <c r="K4" t="n">
-        <v>23253.79</v>
+        <v>22871.96</v>
       </c>
       <c r="L4" t="n">
-        <v>23409.72</v>
+        <v>23130.23</v>
       </c>
       <c r="M4" t="n">
-        <v>23570.57</v>
+        <v>23281.87</v>
       </c>
       <c r="N4" t="n">
-        <v>23731.42</v>
+        <v>23433.5</v>
       </c>
       <c r="O4" t="n">
-        <v>23882.43</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
+        <v>23798.41</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
@@ -870,7 +875,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -880,134 +885,136 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C5" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D5" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E5" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F5" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H5" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I5" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J5" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K5" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L5" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M5" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N5" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O5" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C6" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D6" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E6" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F6" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H6" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I6" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J6" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K6" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L6" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M6" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N6" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O6" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,85 +1022,79 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C7" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D7" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E7" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F7" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H7" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I7" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J7" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K7" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L7" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M7" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N7" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O7" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,79 +1102,85 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C8" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D8" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E8" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F8" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H8" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I8" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J8" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K8" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L8" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M8" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N8" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O8" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1184,25 +1191,25 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1216,50 +1223,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C9" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D9" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E9" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F9" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H9" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I9" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J9" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K9" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L9" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M9" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N9" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O9" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,7 +1277,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1288,7 +1295,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1302,50 +1309,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C10" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D10" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E10" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F10" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H10" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I10" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J10" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K10" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L10" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M10" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N10" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O10" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,82 +1363,78 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C11" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D11" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E11" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F11" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H11" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I11" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J11" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K11" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L11" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M11" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N11" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O11" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,78 +1445,80 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C12" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D12" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E12" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F12" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H12" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I12" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J12" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K12" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L12" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M12" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N12" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O12" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,80 +1529,78 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C13" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D13" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E13" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F13" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H13" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I13" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J13" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K13" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L13" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M13" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N13" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O13" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,78 +1611,78 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C14" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D14" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E14" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F14" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H14" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I14" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J14" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K14" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L14" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M14" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N14" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O14" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,78 +1693,80 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C15" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D15" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E15" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F15" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H15" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I15" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J15" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K15" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L15" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M15" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N15" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O15" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,17 +1774,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1788,64 +1795,64 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C16" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D16" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E16" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F16" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H16" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I16" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J16" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K16" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L16" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M16" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N16" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O16" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,12 +1860,10 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1874,64 +1879,60 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C17" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D17" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E17" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F17" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H17" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I17" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J17" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K17" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L17" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M17" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N17" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O17" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,23 +1943,27 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1968,83 +1973,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C18" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D18" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E18" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F18" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H18" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I18" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J18" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K18" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L18" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M18" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N18" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O18" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2052,134 +2057,136 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C19" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D19" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E19" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F19" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H19" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I19" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J19" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K19" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L19" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M19" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N19" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O19" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C20" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D20" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E20" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F20" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H20" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I20" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J20" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K20" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L20" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M20" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N20" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O20" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,25 +2197,21 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2222,63 +2225,67 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C21" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D21" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E21" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H21" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I21" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J21" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K21" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L21" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M21" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N21" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O21" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2290,95 +2297,93 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C22" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D22" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E22" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F22" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H22" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I22" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J22" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K22" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L22" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M22" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N22" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O22" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2386,220 +2391,220 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C23" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D23" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E23" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F23" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H23" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I23" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J23" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K23" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L23" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M23" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N23" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O23" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C24" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D24" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E24" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F24" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H24" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I24" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J24" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K24" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L24" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M24" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N24" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O24" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C25" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D25" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E25" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F25" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H25" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I25" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J25" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K25" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L25" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M25" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N25" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O25" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2610,27 +2615,23 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2640,50 +2641,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C26" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D26" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E26" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F26" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H26" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I26" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J26" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K26" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L26" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M26" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N26" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O26" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,23 +2695,27 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2720,50 +2725,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C27" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D27" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E27" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F27" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H27" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I27" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J27" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K27" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L27" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M27" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N27" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O27" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2774,27 +2779,23 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2804,50 +2805,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C28" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D28" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E28" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F28" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I28" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J28" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K28" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L28" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M28" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N28" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O28" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2855,18 +2856,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2874,60 +2875,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C29" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D29" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E29" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F29" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H29" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I29" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J29" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K29" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L29" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M29" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N29" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O29" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2935,18 +2940,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2954,64 +2959,60 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C30" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D30" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E30" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F30" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H30" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I30" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J30" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K30" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L30" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M30" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N30" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O30" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3019,17 +3020,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3038,60 +3041,64 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C31" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D31" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E31" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F31" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H31" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I31" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J31" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K31" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L31" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M31" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N31" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O31" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3099,20 +3106,16 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3120,7 +3123,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3134,63 +3137,69 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C32" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D32" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E32" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F32" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H32" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I32" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J32" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K32" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L32" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M32" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N32" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O32" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3202,148 +3211,144 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C33" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D33" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E33" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F33" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H33" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I33" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J33" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K33" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L33" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M33" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N33" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O33" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C34" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D34" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E34" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F34" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H34" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I34" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J34" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K34" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L34" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M34" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N34" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O34" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3354,23 +3359,25 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3384,63 +3391,67 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C35" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D35" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E35" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F35" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H35" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I35" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J35" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K35" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L35" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M35" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N35" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O35" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3451,92 +3462,86 @@
       <c r="U35" s="8" t="n">
         <v/>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C36" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D36" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E36" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F36" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H36" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I36" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J36" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K36" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L36" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M36" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N36" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O36" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3544,64 +3549,60 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C37" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D37" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E37" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F37" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H37" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I37" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J37" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K37" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L37" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M37" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N37" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O37" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,12 +3612,12 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3628,66 +3629,72 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C38" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D38" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E38" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F38" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H38" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I38" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J38" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K38" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L38" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M38" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N38" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O38" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3696,7 +3703,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3708,95 +3715,93 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C39" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D39" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E39" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F39" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H39" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I39" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J39" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K39" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L39" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M39" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N39" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O39" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3804,50 +3809,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C40" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D40" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E40" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F40" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I40" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J40" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K40" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L40" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M40" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N40" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O40" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,83 +3860,83 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C41" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D41" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E41" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F41" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H41" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I41" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J41" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K41" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L41" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M41" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N41" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O41" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3944,7 +3949,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3958,64 +3963,60 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C42" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D42" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E42" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F42" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H42" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I42" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J42" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K42" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L42" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M42" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N42" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O42" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4023,26 +4024,30 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4052,50 +4057,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C43" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D43" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E43" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F43" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H43" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I43" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J43" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K43" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L43" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M43" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N43" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O43" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4106,7 +4111,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4118,15 +4123,15 @@
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4136,83 +4141,83 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C44" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D44" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E44" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F44" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H44" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I44" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J44" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K44" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L44" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M44" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N44" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O44" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4220,69 +4225,63 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C45" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D45" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E45" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F45" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H45" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I45" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J45" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K45" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L45" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M45" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N45" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O45" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4294,7 +4293,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4304,50 +4303,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C46" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D46" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E46" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H46" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I46" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J46" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K46" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L46" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M46" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N46" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O46" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4358,74 +4357,82 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="S46" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C47" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D47" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E47" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F47" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H47" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I47" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J47" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K47" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L47" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M47" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N47" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O47" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4433,85 +4440,81 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C48" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D48" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E48" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F48" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I48" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J48" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K48" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L48" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M48" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N48" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O48" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4521,18 +4524,16 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4540,66 +4541,72 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C49" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D49" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E49" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F49" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I49" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J49" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K49" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L49" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M49" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N49" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O49" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
@@ -4620,71 +4627,67 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C50" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D50" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E50" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F50" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I50" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J50" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K50" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L50" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M50" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N50" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O50" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -4694,7 +4697,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4706,7 +4709,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4716,57 +4719,57 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C51" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D51" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E51" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F51" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I51" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J51" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K51" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L51" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M51" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N51" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O51" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4776,7 +4779,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4788,7 +4791,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4798,71 +4801,69 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C52" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D52" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E52" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F52" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H52" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I52" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J52" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K52" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L52" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M52" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N52" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O52" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4870,60 +4871,64 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C53" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D53" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E53" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F53" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H53" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I53" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J53" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K53" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L53" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M53" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N53" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O53" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4934,9 +4939,9 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S53" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
@@ -4944,166 +4949,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C54" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D54" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E54" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F54" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I54" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J54" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K54" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L54" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M54" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N54" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O54" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C55" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D55" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E55" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F55" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H55" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I55" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J55" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K55" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L55" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M55" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N55" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O55" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5118,7 +5123,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5132,50 +5137,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C56" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D56" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E56" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F56" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H56" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I56" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J56" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K56" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L56" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M56" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N56" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O56" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5185,12 +5190,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5202,7 +5207,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5216,56 +5221,60 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C57" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D57" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E57" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F57" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H57" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I57" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J57" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K57" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L57" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M57" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N57" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O57" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5274,7 +5283,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5286,75 +5295,71 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C58" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D58" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E58" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F58" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H58" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I58" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J58" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K58" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L58" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M58" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N58" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O58" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5374,7 +5379,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5384,155 +5389,157 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C59" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D59" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E59" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F59" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H59" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I59" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J59" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K59" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L59" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M59" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N59" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O59" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C60" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D60" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E60" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F60" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H60" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I60" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J60" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K60" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L60" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M60" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N60" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O60" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5540,81 +5547,77 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C61" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D61" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E61" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F61" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H61" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I61" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J61" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K61" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L61" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M61" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N61" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O61" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5626,7 +5629,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5640,63 +5643,69 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C62" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D62" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E62" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F62" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H62" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I62" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J62" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K62" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L62" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M62" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N62" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O62" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+        <v>25005.07</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5708,151 +5717,151 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C63" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D63" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E63" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F63" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H63" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I63" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J63" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K63" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L63" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M63" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N63" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O63" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W63" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C64" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D64" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E64" t="n">
-        <v>24750.78</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>146.49</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.006</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I64" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J64" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K64" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L64" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M64" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N64" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O64" t="n">
-        <v>24854.61</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+        <v>25022.04</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
@@ -5860,32 +5869,34 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V64" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W64" s="9" t="inlineStr">
+      <c r="W64" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,14 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,63 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23420.7</v>
+        <v>23388.5</v>
       </c>
       <c r="C2" t="n">
-        <v>23565.65</v>
+        <v>23388.5</v>
       </c>
       <c r="D2" t="n">
-        <v>23248.87</v>
+        <v>22978.59</v>
       </c>
       <c r="E2" t="n">
-        <v>23412.18</v>
+        <v>23076.91</v>
       </c>
       <c r="F2" t="n">
-        <v>75.90000000000001</v>
+        <v>-335.27</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.0143</v>
       </c>
       <c r="H2" t="n">
-        <v>316.78</v>
+        <v>409.91</v>
       </c>
       <c r="I2" t="n">
-        <v>22678.45</v>
+        <v>22932.09</v>
       </c>
       <c r="J2" t="n">
-        <v>22661.25</v>
+        <v>23097.86</v>
       </c>
       <c r="K2" t="n">
-        <v>23049.44</v>
+        <v>23253.79</v>
       </c>
       <c r="L2" t="n">
-        <v>23437.62</v>
+        <v>23409.72</v>
       </c>
       <c r="M2" t="n">
-        <v>23623.12</v>
+        <v>23570.57</v>
       </c>
       <c r="N2" t="n">
-        <v>23808.61</v>
+        <v>23731.42</v>
       </c>
       <c r="O2" t="n">
-        <v>24399.49</v>
+        <v>23882.43</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -707,65 +708,63 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23388.5</v>
+        <v>22952.09</v>
       </c>
       <c r="C3" t="n">
-        <v>23388.5</v>
+        <v>22962.46</v>
       </c>
       <c r="D3" t="n">
-        <v>22978.59</v>
+        <v>22518</v>
       </c>
       <c r="E3" t="n">
-        <v>23076.91</v>
+        <v>22671.86</v>
       </c>
       <c r="F3" t="n">
-        <v>-335.27</v>
+        <v>-405.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0176</v>
       </c>
       <c r="H3" t="n">
-        <v>409.91</v>
+        <v>444.46</v>
       </c>
       <c r="I3" t="n">
-        <v>22932.09</v>
+        <v>22568.68</v>
       </c>
       <c r="J3" t="n">
-        <v>23097.86</v>
+        <v>22613.68</v>
       </c>
       <c r="K3" t="n">
-        <v>23253.79</v>
+        <v>22871.96</v>
       </c>
       <c r="L3" t="n">
-        <v>23409.72</v>
+        <v>23130.23</v>
       </c>
       <c r="M3" t="n">
-        <v>23570.57</v>
+        <v>23281.87</v>
       </c>
       <c r="N3" t="n">
-        <v>23731.42</v>
+        <v>23433.5</v>
       </c>
       <c r="O3" t="n">
-        <v>23882.43</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
+        <v>23798.41</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
@@ -791,7 +790,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -801,134 +800,136 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C4" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D4" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E4" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F4" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H4" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I4" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J4" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K4" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L4" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M4" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N4" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O4" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C5" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D5" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E5" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F5" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H5" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I5" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J5" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K5" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L5" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M5" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N5" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O5" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,85 +937,79 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C6" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D6" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E6" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F6" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H6" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I6" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J6" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K6" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L6" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M6" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N6" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O6" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,79 +1017,85 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C7" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D7" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E7" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F7" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H7" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I7" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J7" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K7" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L7" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M7" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N7" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O7" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,25 +1106,25 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="11" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1137,50 +1138,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C8" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D8" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E8" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F8" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H8" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I8" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J8" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K8" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L8" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M8" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N8" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O8" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,7 +1192,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="11" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1209,7 +1210,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1223,50 +1224,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C9" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D9" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E9" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F9" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H9" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I9" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J9" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K9" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L9" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M9" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N9" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O9" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,82 +1278,78 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C10" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D10" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E10" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F10" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H10" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I10" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J10" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K10" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L10" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M10" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N10" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O10" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,78 +1360,80 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C11" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D11" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E11" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F11" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H11" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I11" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J11" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K11" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L11" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M11" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N11" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O11" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,80 +1444,78 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C12" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D12" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E12" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F12" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H12" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I12" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J12" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K12" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L12" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M12" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N12" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O12" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1529,78 +1526,78 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C13" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D13" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E13" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F13" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H13" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I13" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J13" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K13" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L13" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M13" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N13" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O13" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1611,78 +1608,80 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C14" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D14" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E14" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F14" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H14" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I14" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J14" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K14" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L14" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M14" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N14" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O14" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,17 +1689,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1709,64 +1710,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C15" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D15" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E15" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F15" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H15" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I15" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J15" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K15" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L15" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M15" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N15" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O15" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,12 +1775,10 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1795,64 +1794,60 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C16" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D16" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E16" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F16" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H16" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I16" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J16" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K16" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L16" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M16" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N16" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O16" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1863,23 +1858,27 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="11" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1889,83 +1888,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C17" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D17" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E17" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F17" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H17" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I17" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J17" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K17" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L17" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M17" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N17" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O17" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1973,134 +1972,136 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C18" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D18" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E18" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F18" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H18" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I18" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J18" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K18" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L18" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M18" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N18" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O18" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C19" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D19" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E19" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F19" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H19" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I19" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J19" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K19" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L19" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M19" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N19" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O19" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2111,25 +2112,21 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="10" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2143,63 +2140,67 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C20" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D20" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E20" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H20" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I20" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J20" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K20" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L20" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M20" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N20" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O20" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2211,95 +2212,93 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="10" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C21" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D21" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E21" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F21" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H21" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I21" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J21" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K21" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L21" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M21" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N21" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O21" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2307,220 +2306,220 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C22" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D22" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E22" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F22" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H22" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I22" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J22" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K22" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L22" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M22" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N22" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O22" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C23" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D23" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E23" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F23" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H23" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I23" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J23" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K23" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L23" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M23" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N23" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O23" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C24" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D24" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E24" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F24" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H24" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I24" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J24" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K24" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L24" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M24" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N24" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O24" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2531,27 +2530,23 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="11" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2561,50 +2556,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C25" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D25" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E25" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F25" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H25" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I25" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J25" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K25" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L25" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M25" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N25" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O25" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2615,23 +2610,27 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="11" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2641,50 +2640,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C26" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D26" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E26" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F26" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H26" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I26" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J26" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K26" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L26" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M26" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N26" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O26" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,27 +2694,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="11" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2725,50 +2720,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C27" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D27" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E27" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F27" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I27" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J27" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K27" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L27" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M27" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N27" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O27" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2776,18 +2771,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2795,60 +2790,64 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C28" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D28" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E28" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F28" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H28" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I28" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J28" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K28" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L28" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M28" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N28" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O28" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,18 +2855,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2875,64 +2874,60 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C29" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D29" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E29" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F29" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H29" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I29" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J29" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K29" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L29" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M29" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N29" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O29" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,17 +2935,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2959,60 +2956,64 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C30" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D30" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E30" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F30" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H30" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I30" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J30" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K30" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L30" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M30" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N30" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O30" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3020,20 +3021,16 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3041,7 +3038,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3055,63 +3052,69 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C31" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D31" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E31" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F31" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H31" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I31" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J31" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K31" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L31" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M31" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N31" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O31" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3125,146 +3128,142 @@
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C32" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D32" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E32" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F32" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H32" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I32" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J32" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K32" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L32" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M32" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N32" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O32" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="10" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C33" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D33" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E33" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F33" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H33" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I33" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J33" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K33" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L33" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M33" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N33" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O33" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,23 +3274,25 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3305,63 +3306,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C34" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D34" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E34" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F34" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H34" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I34" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J34" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K34" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L34" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M34" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N34" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O34" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3372,92 +3377,86 @@
       <c r="U34" s="8" t="n">
         <v/>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W34" s="10" t="inlineStr">
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C35" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D35" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E35" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F35" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H35" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I35" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J35" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K35" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L35" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M35" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N35" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O35" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3465,64 +3464,60 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="10" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C36" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D36" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E36" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F36" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H36" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I36" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J36" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K36" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L36" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M36" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N36" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O36" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,12 +3527,12 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3549,66 +3544,72 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="10" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C37" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D37" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E37" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F37" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H37" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I37" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J37" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K37" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L37" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M37" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N37" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O37" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3617,7 +3618,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3629,95 +3630,93 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="10" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C38" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D38" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E38" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F38" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H38" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I38" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J38" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K38" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L38" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M38" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N38" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O38" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3725,50 +3724,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C39" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D39" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E39" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F39" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H39" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I39" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J39" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K39" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L39" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M39" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N39" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O39" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3776,83 +3775,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C40" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D40" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E40" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F40" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H40" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I40" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J40" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K40" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L40" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M40" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N40" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O40" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3865,7 +3864,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="11" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3879,64 +3878,60 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C41" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D41" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E41" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F41" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H41" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I41" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J41" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K41" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L41" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M41" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N41" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O41" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3944,26 +3939,30 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3973,50 +3972,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C42" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D42" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E42" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F42" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H42" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I42" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J42" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K42" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L42" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M42" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N42" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O42" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4027,7 +4026,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="11" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4039,15 +4038,15 @@
       </c>
       <c r="U42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4057,83 +4056,83 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C43" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D43" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E43" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F43" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H43" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I43" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J43" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K43" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L43" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M43" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N43" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O43" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4141,69 +4140,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C44" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D44" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E44" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F44" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H44" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I44" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J44" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K44" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L44" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M44" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N44" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O44" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4215,7 +4208,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="10" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4225,50 +4218,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C45" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D45" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E45" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F45" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H45" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I45" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J45" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K45" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L45" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M45" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N45" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O45" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4279,74 +4272,82 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="10" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C46" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D46" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E46" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F46" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H46" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I46" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J46" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K46" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L46" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M46" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N46" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O46" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4354,85 +4355,81 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="10" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C47" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D47" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E47" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F47" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I47" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J47" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K47" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L47" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M47" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N47" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O47" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4442,18 +4439,16 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4461,66 +4456,72 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="10" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C48" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D48" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E48" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F48" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I48" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J48" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K48" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L48" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M48" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N48" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O48" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4541,71 +4542,67 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="10" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C49" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D49" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E49" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F49" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I49" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J49" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K49" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L49" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M49" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N49" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O49" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -4615,7 +4612,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4627,7 +4624,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4637,57 +4634,57 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C50" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D50" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E50" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F50" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I50" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J50" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K50" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L50" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M50" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N50" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O50" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -4697,7 +4694,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4709,7 +4706,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="10" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4719,71 +4716,69 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C51" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D51" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E51" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F51" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H51" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I51" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J51" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K51" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L51" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M51" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N51" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O51" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4791,60 +4786,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="10" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C52" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D52" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E52" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F52" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H52" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I52" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J52" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K52" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L52" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M52" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N52" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O52" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4855,9 +4854,9 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4865,166 +4864,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C53" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D53" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E53" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F53" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I53" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J53" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K53" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L53" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M53" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N53" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O53" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C54" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D54" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E54" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F54" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H54" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I54" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J54" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K54" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L54" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M54" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N54" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O54" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5039,7 +5038,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5053,50 +5052,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C55" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D55" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E55" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F55" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H55" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I55" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J55" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K55" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L55" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M55" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N55" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O55" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5106,12 +5105,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5123,7 +5122,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5137,56 +5136,60 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C56" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D56" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E56" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F56" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H56" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I56" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J56" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K56" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L56" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M56" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N56" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O56" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5195,7 +5198,7 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5209,73 +5212,69 @@
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C57" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D57" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E57" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F57" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H57" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I57" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J57" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K57" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L57" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M57" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N57" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O57" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5295,7 +5294,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="10" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5305,155 +5304,157 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C58" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D58" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E58" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H58" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I58" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J58" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K58" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L58" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M58" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N58" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O58" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="10" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C59" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D59" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E59" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F59" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H59" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I59" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J59" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K59" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L59" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M59" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N59" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O59" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5461,81 +5462,77 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="10" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C60" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D60" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E60" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F60" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H60" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I60" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J60" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K60" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L60" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M60" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N60" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O60" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5547,7 +5544,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="10" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5561,63 +5558,69 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C61" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D61" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E61" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F61" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H61" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I61" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J61" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K61" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L61" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M61" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N61" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O61" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+        <v>25005.07</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5629,148 +5632,146 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="10" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C62" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D62" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E62" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F62" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H62" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I62" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J62" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K62" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L62" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M62" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N62" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O62" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="10" t="inlineStr">
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C63" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D63" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E63" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F63" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H63" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I63" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J63" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K63" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L63" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M63" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N63" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O63" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5781,124 +5782,112 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="11" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W63" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>24748.45</v>
+        <v>25170.8</v>
       </c>
       <c r="C64" t="n">
-        <v>25042.71</v>
+        <v>25254.11</v>
       </c>
       <c r="D64" t="n">
-        <v>24736.92</v>
+        <v>25043.64</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>25087.75</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>45.04</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>0.0018</v>
       </c>
       <c r="H64" t="n">
-        <v>305.79</v>
+        <v>210.47</v>
       </c>
       <c r="I64" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J64" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K64" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L64" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M64" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N64" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O64" t="n">
-        <v>25022.04</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
+        <v>25348.5</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W64" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5825,13 +5828,13 @@
         <v>25043.64</v>
       </c>
       <c r="E64" t="n">
-        <v>25087.75</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>45.04</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0018</v>
+        <v/>
       </c>
       <c r="H64" t="n">
         <v>210.47</v>
@@ -5857,8 +5860,10 @@
       <c r="O64" t="n">
         <v>25348.5</v>
       </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
@@ -5866,14 +5871,14 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U64" s="8" t="n">

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,53 +637,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23388.5</v>
+        <v>22952.09</v>
       </c>
       <c r="C2" t="n">
-        <v>23388.5</v>
+        <v>22962.46</v>
       </c>
       <c r="D2" t="n">
-        <v>22978.59</v>
+        <v>22518</v>
       </c>
       <c r="E2" t="n">
-        <v>23076.91</v>
+        <v>22671.86</v>
       </c>
       <c r="F2" t="n">
-        <v>-335.27</v>
+        <v>-405.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0176</v>
       </c>
       <c r="H2" t="n">
-        <v>409.91</v>
+        <v>444.46</v>
       </c>
       <c r="I2" t="n">
-        <v>22932.09</v>
+        <v>22568.68</v>
       </c>
       <c r="J2" t="n">
-        <v>23097.86</v>
+        <v>22613.68</v>
       </c>
       <c r="K2" t="n">
-        <v>23253.79</v>
+        <v>22871.96</v>
       </c>
       <c r="L2" t="n">
-        <v>23409.72</v>
+        <v>23130.23</v>
       </c>
       <c r="M2" t="n">
-        <v>23570.57</v>
+        <v>23281.87</v>
       </c>
       <c r="N2" t="n">
-        <v>23731.42</v>
+        <v>23433.5</v>
       </c>
       <c r="O2" t="n">
-        <v>23882.43</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>23798.41</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -711,91 +713,93 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C3" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D3" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E3" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F3" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H3" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I3" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J3" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K3" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L3" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M3" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N3" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O3" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -803,50 +807,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C4" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D4" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E4" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F4" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H4" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I4" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J4" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K4" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L4" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M4" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N4" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O4" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,30 +858,28 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -889,50 +891,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C5" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D5" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E5" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F5" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H5" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I5" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J5" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K5" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L5" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M5" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N5" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O5" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,28 +942,30 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -969,50 +973,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C6" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D6" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E6" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F6" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H6" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I6" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J6" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K6" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L6" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M6" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N6" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O6" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1030,75 +1034,71 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C7" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D7" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E7" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F7" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H7" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I7" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J7" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K7" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L7" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M7" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N7" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O7" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1129,62 +1129,58 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C8" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D8" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E8" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F8" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H8" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I8" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J8" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K8" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L8" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M8" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N8" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O8" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,82 +1191,78 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C9" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D9" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E9" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F9" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H9" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I9" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J9" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K9" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L9" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M9" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N9" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O9" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1281,78 +1273,80 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C10" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D10" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E10" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F10" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H10" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I10" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J10" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K10" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L10" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M10" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N10" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O10" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,80 +1357,78 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C11" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D11" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E11" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F11" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H11" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I11" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J11" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K11" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L11" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M11" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N11" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O11" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1447,78 +1439,78 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C12" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D12" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E12" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F12" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H12" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I12" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J12" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K12" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L12" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M12" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N12" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O12" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1529,78 +1521,80 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C13" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D13" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E13" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F13" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H13" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I13" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J13" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K13" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L13" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M13" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N13" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O13" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,17 +1602,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1627,64 +1623,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C14" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D14" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E14" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F14" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H14" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I14" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J14" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K14" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L14" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M14" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N14" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O14" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1692,10 +1688,8 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
@@ -1713,64 +1707,60 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C15" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D15" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E15" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F15" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H15" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I15" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J15" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K15" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L15" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M15" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N15" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O15" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1788,16 +1778,20 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1807,83 +1801,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C16" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D16" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E16" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F16" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H16" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I16" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J16" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K16" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L16" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M16" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N16" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O16" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1891,134 +1885,136 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C17" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D17" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E17" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F17" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H17" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I17" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J17" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K17" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L17" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M17" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N17" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O17" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C18" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D18" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E18" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F18" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H18" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I18" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J18" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K18" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L18" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M18" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N18" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O18" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2031,23 +2027,19 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2061,63 +2053,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C19" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D19" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E19" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H19" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I19" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J19" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K19" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L19" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M19" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N19" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O19" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2129,95 +2125,93 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C20" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D20" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E20" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F20" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H20" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I20" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J20" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K20" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L20" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M20" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N20" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O20" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2225,220 +2219,220 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C21" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D21" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E21" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F21" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H21" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I21" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J21" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K21" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L21" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M21" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N21" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O21" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C22" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D22" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E22" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F22" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H22" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I22" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J22" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K22" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L22" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M22" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N22" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O22" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C23" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D23" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E23" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F23" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H23" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I23" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J23" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K23" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L23" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M23" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N23" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O23" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2456,20 +2450,16 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2479,50 +2469,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C24" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D24" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E24" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F24" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H24" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I24" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J24" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K24" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L24" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M24" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N24" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O24" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,16 +2530,20 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2559,50 +2553,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C25" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D25" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E25" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F25" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H25" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I25" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J25" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K25" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L25" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M25" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N25" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O25" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2620,20 +2614,16 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2643,50 +2633,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C26" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D26" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E26" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F26" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I26" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J26" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K26" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L26" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M26" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N26" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O26" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,18 +2684,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2713,60 +2703,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C27" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D27" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E27" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F27" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H27" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I27" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J27" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K27" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L27" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M27" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N27" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O27" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2774,18 +2768,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2793,64 +2787,60 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C28" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D28" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E28" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F28" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H28" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I28" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J28" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K28" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L28" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M28" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N28" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O28" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2858,17 +2848,19 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2877,60 +2869,64 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C29" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D29" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E29" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F29" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H29" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I29" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J29" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K29" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L29" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M29" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N29" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O29" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2938,20 +2934,16 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2959,7 +2951,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2973,63 +2965,69 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C30" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D30" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E30" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F30" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H30" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I30" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J30" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K30" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L30" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M30" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N30" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O30" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3043,146 +3041,142 @@
       </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C31" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D31" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E31" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F31" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H31" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I31" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J31" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K31" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L31" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M31" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N31" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O31" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C32" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D32" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E32" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F32" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H32" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I32" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J32" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K32" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L32" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M32" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N32" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O32" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3200,16 +3194,18 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3223,63 +3219,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C33" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D33" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E33" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F33" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H33" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I33" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J33" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K33" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L33" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M33" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N33" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O33" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3290,92 +3290,86 @@
       <c r="U33" s="8" t="n">
         <v/>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C34" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D34" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E34" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F34" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H34" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I34" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J34" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K34" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L34" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M34" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N34" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O34" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3383,64 +3377,60 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C35" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D35" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E35" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F35" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H35" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I35" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J35" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K35" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L35" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M35" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N35" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O35" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3450,12 +3440,12 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3467,66 +3457,72 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C36" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D36" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E36" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F36" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H36" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I36" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J36" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K36" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L36" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M36" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N36" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O36" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
@@ -3535,7 +3531,7 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3547,95 +3543,93 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C37" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D37" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E37" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F37" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H37" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I37" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J37" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K37" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L37" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M37" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N37" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O37" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3643,50 +3637,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C38" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D38" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E38" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F38" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H38" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I38" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J38" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K38" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L38" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M38" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N38" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O38" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3694,83 +3688,83 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W38" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C39" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D39" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E39" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F39" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H39" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I39" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J39" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K39" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L39" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M39" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N39" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O39" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3797,64 +3791,60 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C40" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D40" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E40" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F40" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H40" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I40" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J40" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K40" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L40" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M40" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N40" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O40" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3862,26 +3852,30 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3891,50 +3885,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C41" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D41" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E41" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F41" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H41" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I41" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J41" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K41" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L41" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M41" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N41" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O41" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3957,15 +3951,15 @@
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3975,83 +3969,83 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C42" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D42" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E42" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F42" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H42" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I42" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J42" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K42" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L42" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M42" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N42" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O42" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
       <c r="W42" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4059,69 +4053,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C43" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D43" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E43" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F43" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H43" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I43" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J43" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K43" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L43" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M43" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N43" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O43" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4133,7 +4121,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4143,50 +4131,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C44" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D44" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E44" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F44" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H44" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I44" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J44" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K44" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L44" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M44" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N44" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O44" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4197,74 +4185,82 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C45" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D45" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E45" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F45" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H45" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I45" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J45" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K45" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L45" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M45" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N45" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O45" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4272,85 +4268,81 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C46" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D46" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E46" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F46" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I46" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J46" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K46" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L46" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M46" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N46" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O46" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4360,18 +4352,16 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4379,66 +4369,72 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C47" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D47" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E47" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F47" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I47" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J47" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K47" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L47" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M47" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N47" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O47" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
@@ -4459,71 +4455,67 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C48" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D48" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E48" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F48" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I48" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J48" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K48" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L48" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M48" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N48" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O48" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -4533,7 +4525,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4545,7 +4537,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4555,57 +4547,57 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C49" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D49" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E49" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F49" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I49" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J49" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K49" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L49" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M49" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N49" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O49" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -4615,7 +4607,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4627,7 +4619,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4637,71 +4629,69 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C50" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D50" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E50" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F50" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H50" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I50" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J50" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K50" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L50" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M50" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N50" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O50" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4709,60 +4699,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C51" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D51" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E51" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F51" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H51" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I51" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J51" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K51" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L51" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M51" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N51" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O51" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4773,9 +4767,9 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4783,166 +4777,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C52" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D52" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E52" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F52" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I52" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J52" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K52" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L52" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M52" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N52" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O52" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C53" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D53" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E53" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F53" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H53" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I53" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J53" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K53" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L53" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M53" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N53" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O53" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4957,7 +4951,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4971,50 +4965,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C54" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D54" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E54" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F54" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H54" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I54" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J54" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K54" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L54" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M54" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N54" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O54" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5024,12 +5018,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5041,7 +5035,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5055,56 +5049,60 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C55" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D55" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E55" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F55" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H55" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I55" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J55" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K55" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L55" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M55" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N55" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O55" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5113,7 +5111,7 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5127,73 +5125,69 @@
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C56" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D56" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E56" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F56" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H56" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I56" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J56" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K56" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L56" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M56" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N56" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O56" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5213,7 +5207,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5223,155 +5217,157 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C57" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D57" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E57" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F57" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H57" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I57" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J57" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K57" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L57" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M57" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N57" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O57" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C58" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D58" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E58" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F58" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H58" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I58" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J58" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K58" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L58" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M58" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N58" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O58" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5379,81 +5375,77 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C59" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D59" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E59" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F59" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H59" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I59" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J59" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K59" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L59" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M59" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N59" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O59" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5465,7 +5457,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5479,63 +5471,69 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C60" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D60" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E60" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F60" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H60" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I60" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J60" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K60" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L60" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M60" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N60" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O60" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+        <v>25005.07</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5547,148 +5545,146 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C61" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D61" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E61" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F61" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H61" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I61" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J61" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K61" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L61" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M61" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N61" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O61" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C62" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D62" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E62" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F62" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H62" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I62" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J62" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K62" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L62" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M62" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N62" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O62" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5706,78 +5702,78 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24748.45</v>
+        <v>25064.84</v>
       </c>
       <c r="C63" t="n">
-        <v>25042.71</v>
+        <v>25064.84</v>
       </c>
       <c r="D63" t="n">
-        <v>24736.92</v>
+        <v>25064.84</v>
       </c>
       <c r="E63" t="n">
-        <v>25042.71</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>291.93</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0118</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>305.79</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J63" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K63" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L63" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M63" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N63" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O63" t="n">
-        <v>25022.04</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+        <v>25348.5</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="n">
         <v/>
@@ -5785,114 +5781,26 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>25170.8</v>
-      </c>
-      <c r="C64" t="n">
-        <v>25254.11</v>
-      </c>
-      <c r="D64" t="n">
-        <v>25043.64</v>
-      </c>
-      <c r="E64" t="n">
-        <v/>
-      </c>
-      <c r="F64" t="n">
-        <v/>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v>210.47</v>
-      </c>
-      <c r="I64" t="n">
-        <v>24431.13</v>
-      </c>
-      <c r="J64" t="n">
-        <v>24813.37</v>
-      </c>
-      <c r="K64" t="n">
-        <v>24889.82</v>
-      </c>
-      <c r="L64" t="n">
-        <v>24966.26</v>
-      </c>
-      <c r="M64" t="n">
-        <v>25195.61</v>
-      </c>
-      <c r="N64" t="n">
-        <v>25424.95</v>
-      </c>
-      <c r="O64" t="n">
-        <v>25348.5</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -5732,10 +5732,10 @@
         <v>25064.84</v>
       </c>
       <c r="C63" t="n">
-        <v>25064.84</v>
+        <v>25072.25</v>
       </c>
       <c r="D63" t="n">
-        <v>25064.84</v>
+        <v>24898.39</v>
       </c>
       <c r="E63" t="n">
         <v/>
@@ -5747,7 +5747,7 @@
         <v/>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>173.86</v>
       </c>
       <c r="I63" t="n">
         <v>24431.13</v>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -5735,7 +5735,7 @@
         <v>25072.25</v>
       </c>
       <c r="D63" t="n">
-        <v>24898.39</v>
+        <v>24836.16</v>
       </c>
       <c r="E63" t="n">
         <v/>
@@ -5747,7 +5747,7 @@
         <v/>
       </c>
       <c r="H63" t="n">
-        <v>173.86</v>
+        <v>236.09</v>
       </c>
       <c r="I63" t="n">
         <v>24431.13</v>
@@ -5778,8 +5778,10 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S63" s="12" t="inlineStr">
         <is>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5725,7 +5722,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -5735,19 +5732,19 @@
         <v>25072.25</v>
       </c>
       <c r="D63" t="n">
-        <v>24836.16</v>
+        <v>24811.85</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>24834.12</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>-208.59</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>-0.0083</v>
       </c>
       <c r="H63" t="n">
-        <v>236.09</v>
+        <v>260.4</v>
       </c>
       <c r="I63" t="n">
         <v>24431.13</v>
@@ -5770,22 +5767,22 @@
       <c r="O63" t="n">
         <v>25348.5</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5802,7 +5799,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5735,13 +5738,13 @@
         <v>24811.85</v>
       </c>
       <c r="E63" t="n">
-        <v>24834.12</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>-208.59</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0083</v>
+        <v/>
       </c>
       <c r="H63" t="n">
         <v>260.4</v>
@@ -5767,12 +5770,14 @@
       <c r="O63" t="n">
         <v>25348.5</v>
       </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -5780,9 +5785,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5799,11 +5804,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -637,77 +637,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22952.09</v>
+        <v>22827.65</v>
       </c>
       <c r="C2" t="n">
-        <v>22962.46</v>
+        <v>23183.17</v>
       </c>
       <c r="D2" t="n">
-        <v>22518</v>
+        <v>22783.64</v>
       </c>
       <c r="E2" t="n">
-        <v>22671.86</v>
+        <v>23026.68</v>
       </c>
       <c r="F2" t="n">
-        <v>-405.05</v>
+        <v>354.82</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0176</v>
+        <v>0.0157</v>
       </c>
       <c r="H2" t="n">
-        <v>444.46</v>
+        <v>399.53</v>
       </c>
       <c r="I2" t="n">
-        <v>22568.68</v>
+        <v>22073.54</v>
       </c>
       <c r="J2" t="n">
-        <v>22613.68</v>
+        <v>22193.21</v>
       </c>
       <c r="K2" t="n">
-        <v>22871.96</v>
+        <v>22449.63</v>
       </c>
       <c r="L2" t="n">
-        <v>23130.23</v>
+        <v>22706.04</v>
       </c>
       <c r="M2" t="n">
-        <v>23281.87</v>
+        <v>22894.09</v>
       </c>
       <c r="N2" t="n">
-        <v>23433.5</v>
+        <v>23082.13</v>
       </c>
       <c r="O2" t="n">
-        <v>23798.41</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>23406.92</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -716,59 +714,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C3" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D3" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E3" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F3" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H3" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I3" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J3" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K3" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L3" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M3" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N3" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O3" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -776,23 +770,21 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -802,55 +794,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C4" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D4" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E4" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F4" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H4" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I4" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J4" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K4" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L4" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M4" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N4" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O4" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,21 +854,23 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -882,59 +880,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C5" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D5" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E5" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F5" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H5" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I5" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J5" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K5" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L5" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M5" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N5" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O5" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,19 +939,19 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V5" s="8" t="n">
@@ -973,50 +967,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C6" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D6" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E6" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F6" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H6" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I6" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J6" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K6" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L6" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M6" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N6" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O6" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1027,7 +1021,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1055,50 +1049,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C7" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D7" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E7" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F7" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H7" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I7" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J7" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K7" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L7" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M7" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N7" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O7" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,18 +1105,14 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1132,55 +1122,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C8" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D8" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E8" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F8" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H8" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I8" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J8" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K8" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L8" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M8" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N8" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O8" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1193,76 +1187,78 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C9" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D9" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E9" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F9" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H9" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I9" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J9" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K9" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L9" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M9" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N9" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O9" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,78 +1271,76 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C10" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D10" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E10" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F10" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H10" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I10" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J10" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K10" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L10" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M10" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N10" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O10" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,14 +1353,18 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1376,59 +1374,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C11" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D11" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E11" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F11" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H11" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I11" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J11" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K11" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L11" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M11" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N11" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O11" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,18 +1435,16 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1462,55 +1454,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C12" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D12" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E12" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F12" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H12" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I12" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J12" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K12" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L12" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M12" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N12" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O12" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,17 +1514,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1544,57 +1542,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C13" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D13" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E13" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F13" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H13" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I13" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J13" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K13" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L13" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M13" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N13" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O13" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1602,12 +1600,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1628,59 +1624,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C14" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D14" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E14" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F14" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H14" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I14" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J14" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K14" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L14" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M14" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N14" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O14" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,21 +1683,25 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1717,83 +1713,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C15" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D15" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E15" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F15" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H15" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I15" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J15" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K15" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L15" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M15" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N15" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O15" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>25617.86</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1801,77 +1797,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C16" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D16" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E16" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F16" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H16" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I16" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J16" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K16" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L16" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M16" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N16" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O16" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1880,55 +1874,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C17" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D17" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E17" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F17" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H17" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I17" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J17" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K17" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L17" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M17" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N17" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O17" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,20 +1937,16 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1971,63 +1965,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C18" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D18" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E18" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H18" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I18" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J18" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K18" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L18" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M18" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N18" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O18" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2044,90 +2042,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C19" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D19" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E19" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F19" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H19" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I19" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J19" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K19" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L19" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M19" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N19" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O19" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2135,220 +2131,220 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C20" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D20" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E20" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F20" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H20" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I20" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J20" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K20" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L20" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M20" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N20" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O20" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C21" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D21" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E21" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F21" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H21" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I21" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J21" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K21" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L21" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M21" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N21" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O21" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C22" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D22" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E22" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F22" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H22" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I22" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J22" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K22" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L22" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M22" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N22" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O22" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2359,25 +2355,21 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2389,50 +2381,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C23" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D23" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E23" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F23" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H23" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I23" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J23" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K23" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L23" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M23" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N23" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O23" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2443,21 +2435,25 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2469,50 +2465,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C24" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D24" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E24" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F24" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H24" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I24" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J24" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K24" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L24" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M24" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N24" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O24" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,25 +2519,21 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2553,50 +2545,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C25" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D25" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E25" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F25" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I25" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J25" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K25" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L25" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M25" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N25" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O25" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2604,18 +2596,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2628,55 +2620,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C26" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D26" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E26" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F26" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H26" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I26" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J26" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K26" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L26" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M26" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N26" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O26" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2684,18 +2680,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2708,59 +2704,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C27" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D27" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E27" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F27" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H27" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I27" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J27" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K27" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L27" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M27" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N27" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O27" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2768,17 +2760,19 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2792,55 +2786,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C28" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D28" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E28" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F28" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H28" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I28" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J28" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K28" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L28" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M28" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N28" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O28" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2848,20 +2846,16 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2883,63 +2877,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C29" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D29" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E29" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F29" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H29" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I29" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J29" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K29" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L29" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M29" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N29" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O29" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>26218.02</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2951,88 +2951,80 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C30" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D30" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E30" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F30" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H30" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I30" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J30" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K30" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L30" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M30" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N30" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O30" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3044,55 +3036,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C31" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D31" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E31" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F31" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H31" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I31" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J31" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K31" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L31" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M31" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N31" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O31" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,21 +3099,23 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
@@ -3133,63 +3131,67 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C32" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D32" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E32" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F32" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H32" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I32" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J32" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K32" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L32" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M32" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N32" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O32" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3200,10 +3202,8 @@
       <c r="U32" s="8" t="n">
         <v/>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
@@ -3212,80 +3212,76 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C33" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D33" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E33" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F33" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H33" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I33" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J33" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K33" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L33" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M33" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N33" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O33" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3298,59 +3294,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C34" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D34" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E34" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F34" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H34" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I34" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J34" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K34" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L34" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M34" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N34" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O34" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3360,12 +3352,12 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3382,70 +3374,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C35" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D35" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E35" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F35" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H35" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I35" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J35" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K35" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L35" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M35" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N35" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O35" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3462,90 +3460,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C36" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D36" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E36" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F36" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H36" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I36" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J36" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K36" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L36" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M36" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N36" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O36" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3553,50 +3549,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C37" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D37" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E37" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F37" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H37" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I37" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J37" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K37" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L37" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M37" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N37" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O37" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3604,83 +3600,83 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C38" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D38" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E38" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F38" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H38" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I38" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J38" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K38" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L38" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M38" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N38" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O38" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,7 +3689,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3712,59 +3708,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C39" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D39" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E39" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F39" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H39" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I39" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J39" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K39" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L39" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M39" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N39" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O39" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3772,24 +3764,28 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3801,50 +3797,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C40" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D40" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E40" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F40" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H40" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I40" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J40" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K40" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L40" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M40" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N40" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O40" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,7 +3851,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3867,12 +3863,12 @@
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
@@ -3885,83 +3881,83 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C41" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D41" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E41" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F41" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H41" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I41" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J41" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K41" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L41" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M41" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N41" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O41" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>26211.31</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3969,69 +3965,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C42" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D42" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E42" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F42" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H42" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I42" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J42" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K42" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L42" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M42" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N42" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O42" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26129.3</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4053,50 +4043,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C43" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D43" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E43" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F43" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H43" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I43" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J43" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K43" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L43" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M43" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N43" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O43" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4109,14 +4099,18 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4126,55 +4120,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C44" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D44" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E44" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F44" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H44" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I44" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J44" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K44" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L44" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M44" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N44" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O44" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4182,23 +4180,23 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4208,59 +4206,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C45" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D45" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E45" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F45" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I45" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J45" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K45" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L45" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M45" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N45" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O45" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4270,18 +4264,16 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4294,68 +4286,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C46" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D46" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E46" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F46" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I46" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J46" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K46" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L46" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M46" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N46" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O46" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4374,66 +4372,62 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C47" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D47" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E47" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F47" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I47" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J47" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K47" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L47" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M47" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N47" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O47" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -4441,9 +4435,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4465,57 +4459,57 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C48" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D48" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E48" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F48" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I48" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J48" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K48" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L48" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M48" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N48" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O48" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -4523,9 +4517,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4547,71 +4541,69 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C49" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D49" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E49" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F49" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H49" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I49" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J49" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K49" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L49" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M49" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N49" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O49" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4624,55 +4616,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C50" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D50" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E50" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F50" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H50" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I50" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J50" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K50" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L50" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M50" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N50" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O50" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4685,7 +4681,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4693,94 +4689,92 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C51" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D51" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E51" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F51" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I51" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J51" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K51" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L51" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M51" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N51" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O51" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4790,70 +4784,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C52" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D52" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E52" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F52" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H52" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I52" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J52" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K52" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L52" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M52" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N52" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O52" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4881,50 +4877,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C53" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D53" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E53" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F53" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H53" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I53" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J53" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K53" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L53" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M53" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N53" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O53" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4934,12 +4930,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4965,65 +4961,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C54" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D54" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E54" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F54" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H54" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I54" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J54" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K54" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L54" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M54" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N54" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O54" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5035,81 +5035,77 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C55" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D55" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E55" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F55" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H55" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I55" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J55" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K55" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L55" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M55" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N55" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O55" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5133,74 +5129,72 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C56" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D56" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E56" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F56" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H56" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I56" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J56" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K56" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L56" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M56" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N56" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O56" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5212,61 +5206,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C57" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D57" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E57" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F57" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H57" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I57" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J57" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K57" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L57" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M57" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N57" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O57" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5275,13 +5275,11 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5296,74 +5294,70 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C58" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D58" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E58" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H58" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I58" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J58" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K58" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L58" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M58" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N58" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O58" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5389,63 +5383,69 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C59" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D59" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E59" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F59" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H59" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I59" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J59" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K59" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L59" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M59" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N59" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O59" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>25005.07</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5462,143 +5462,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C60" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D60" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E60" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F60" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H60" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I60" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J60" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K60" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L60" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M60" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N60" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O60" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
-      <c r="V60" s="8" t="n">
-        <v/>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C61" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D61" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E61" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F61" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H61" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I61" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J61" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K61" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L61" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M61" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N61" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O61" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5609,133 +5607,133 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24748.45</v>
+        <v>25064.84</v>
       </c>
       <c r="C62" t="n">
-        <v>25042.71</v>
+        <v>25072.25</v>
       </c>
       <c r="D62" t="n">
-        <v>24736.92</v>
+        <v>24811.85</v>
       </c>
       <c r="E62" t="n">
-        <v>25042.71</v>
+        <v>24834.12</v>
       </c>
       <c r="F62" t="n">
-        <v>291.93</v>
+        <v>-208.59</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0083</v>
       </c>
       <c r="H62" t="n">
-        <v>305.79</v>
+        <v>260.4</v>
       </c>
       <c r="I62" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J62" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K62" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L62" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M62" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N62" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O62" t="n">
-        <v>25022.04</v>
+        <v>25348.5</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>25064.84</v>
+        <v>24649.45</v>
       </c>
       <c r="C63" t="n">
-        <v>25072.25</v>
+        <v>24791.2</v>
       </c>
       <c r="D63" t="n">
-        <v>24811.85</v>
+        <v>24648.29</v>
       </c>
       <c r="E63" t="n">
         <v/>
@@ -5747,38 +5745,36 @@
         <v/>
       </c>
       <c r="H63" t="n">
-        <v>260.4</v>
+        <v>142.91</v>
       </c>
       <c r="I63" t="n">
-        <v>24431.13</v>
+        <v>24551.45</v>
       </c>
       <c r="J63" t="n">
-        <v>24813.37</v>
+        <v>24519.75</v>
       </c>
       <c r="K63" t="n">
-        <v>24889.82</v>
+        <v>24703.92</v>
       </c>
       <c r="L63" t="n">
-        <v>24966.26</v>
+        <v>24888.08</v>
       </c>
       <c r="M63" t="n">
-        <v>25195.61</v>
+        <v>24964.32</v>
       </c>
       <c r="N63" t="n">
-        <v>25424.95</v>
+        <v>25040.55</v>
       </c>
       <c r="O63" t="n">
-        <v>25348.5</v>
+        <v>25332.65</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q63" s="6" t="n">
+        <v/>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
@@ -5804,7 +5800,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,20 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22827.65</v>
+        <v>23007.87</v>
       </c>
       <c r="C2" t="n">
-        <v>23183.17</v>
+        <v>23086.85</v>
       </c>
       <c r="D2" t="n">
-        <v>22783.64</v>
+        <v>22685.14</v>
       </c>
       <c r="E2" t="n">
-        <v>23026.68</v>
+        <v>22881.02</v>
       </c>
       <c r="F2" t="n">
-        <v>354.82</v>
+        <v>-145.66</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0063</v>
       </c>
       <c r="H2" t="n">
-        <v>399.53</v>
+        <v>401.71</v>
       </c>
       <c r="I2" t="n">
-        <v>22073.54</v>
+        <v>22384.11</v>
       </c>
       <c r="J2" t="n">
-        <v>22193.21</v>
+        <v>22648.79</v>
       </c>
       <c r="K2" t="n">
-        <v>22449.63</v>
+        <v>22826.92</v>
       </c>
       <c r="L2" t="n">
-        <v>22706.04</v>
+        <v>23005.04</v>
       </c>
       <c r="M2" t="n">
-        <v>22894.09</v>
+        <v>23226.44</v>
       </c>
       <c r="N2" t="n">
-        <v>23082.13</v>
+        <v>23447.85</v>
       </c>
       <c r="O2" t="n">
-        <v>23406.92</v>
+        <v>23582.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -688,23 +685,21 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -714,55 +709,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C3" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D3" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E3" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F3" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H3" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I3" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J3" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K3" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L3" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M3" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N3" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O3" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,21 +769,23 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -794,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C4" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D4" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E4" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F4" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H4" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I4" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J4" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K4" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L4" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M4" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N4" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O4" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,19 +854,19 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V4" s="8" t="n">
@@ -885,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C5" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D5" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E5" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F5" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H5" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I5" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J5" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K5" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L5" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M5" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N5" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O5" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,7 +936,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -967,50 +964,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C6" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D6" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E6" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F6" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H6" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I6" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J6" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K6" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L6" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M6" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N6" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O6" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,18 +1020,14 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1044,55 +1037,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C7" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D7" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E7" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F7" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H7" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I7" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J7" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K7" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L7" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M7" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N7" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O7" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,76 +1102,78 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C8" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D8" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E8" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F8" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H8" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I8" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J8" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K8" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L8" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M8" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N8" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O8" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,78 +1186,76 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C9" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D9" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E9" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F9" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H9" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I9" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J9" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K9" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L9" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M9" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N9" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O9" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,14 +1268,18 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1288,59 +1289,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C10" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D10" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E10" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F10" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H10" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I10" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J10" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K10" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L10" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M10" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N10" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O10" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,18 +1350,16 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1374,55 +1369,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C11" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D11" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E11" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F11" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H11" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I11" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J11" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K11" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L11" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M11" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N11" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O11" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1430,17 +1429,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1456,57 +1457,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C12" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D12" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E12" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F12" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H12" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I12" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J12" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K12" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L12" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M12" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N12" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O12" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1514,12 +1515,10 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1540,59 +1539,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C13" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D13" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E13" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F13" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H13" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I13" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J13" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K13" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L13" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M13" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N13" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O13" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,21 +1598,25 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1629,83 +1628,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C14" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D14" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E14" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F14" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H14" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I14" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J14" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K14" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L14" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M14" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N14" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O14" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>25617.86</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1713,77 +1712,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C15" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D15" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E15" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F15" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H15" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I15" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J15" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K15" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L15" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M15" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N15" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O15" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1792,55 +1789,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C16" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D16" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E16" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F16" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H16" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I16" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J16" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K16" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L16" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M16" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N16" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O16" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,20 +1852,16 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1883,63 +1880,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C17" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D17" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E17" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H17" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I17" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J17" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K17" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L17" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M17" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N17" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O17" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1956,90 +1957,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C18" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D18" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E18" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F18" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H18" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I18" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J18" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K18" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L18" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M18" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N18" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O18" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2047,220 +2046,220 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C19" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D19" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E19" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F19" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H19" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I19" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J19" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K19" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L19" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M19" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N19" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O19" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C20" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D20" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E20" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F20" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H20" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I20" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J20" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K20" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L20" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M20" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N20" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O20" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C21" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D21" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E21" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F21" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H21" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I21" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J21" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K21" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L21" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M21" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N21" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O21" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2271,25 +2270,21 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2301,50 +2296,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C22" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D22" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E22" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F22" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H22" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I22" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J22" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K22" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L22" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M22" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N22" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O22" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,21 +2350,25 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2381,50 +2380,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C23" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D23" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E23" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F23" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H23" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I23" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J23" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K23" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L23" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M23" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N23" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O23" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,25 +2434,21 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2465,50 +2460,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C24" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D24" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E24" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F24" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I24" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J24" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K24" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L24" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M24" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N24" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O24" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,18 +2511,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2540,55 +2535,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C25" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D25" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E25" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F25" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H25" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I25" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J25" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K25" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L25" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M25" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N25" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O25" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2596,18 +2595,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2620,59 +2619,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C26" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D26" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E26" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F26" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H26" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I26" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J26" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K26" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L26" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M26" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N26" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O26" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2680,17 +2675,19 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
@@ -2704,55 +2701,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C27" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D27" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E27" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F27" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H27" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I27" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J27" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K27" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L27" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M27" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N27" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O27" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,20 +2761,16 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2795,63 +2792,69 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C28" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D28" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E28" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F28" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H28" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I28" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J28" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K28" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L28" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M28" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N28" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O28" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>26218.02</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2863,88 +2866,80 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C29" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D29" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E29" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F29" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H29" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I29" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J29" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K29" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L29" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M29" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N29" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O29" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2956,55 +2951,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C30" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D30" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E30" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F30" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H30" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I30" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J30" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K30" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L30" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M30" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N30" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O30" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3015,21 +3014,23 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
       </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
@@ -3045,63 +3046,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C31" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D31" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E31" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F31" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H31" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I31" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J31" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K31" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L31" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M31" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N31" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O31" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3112,10 +3117,8 @@
       <c r="U31" s="8" t="n">
         <v/>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
@@ -3124,80 +3127,76 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C32" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D32" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E32" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F32" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H32" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I32" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J32" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K32" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L32" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M32" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N32" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O32" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3210,59 +3209,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C33" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D33" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E33" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F33" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H33" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I33" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J33" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K33" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L33" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M33" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N33" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O33" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3272,12 +3267,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3294,70 +3289,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C34" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D34" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E34" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F34" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H34" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I34" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J34" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K34" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L34" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M34" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N34" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O34" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3374,90 +3375,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C35" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D35" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E35" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F35" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H35" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I35" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J35" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K35" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L35" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M35" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N35" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O35" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3465,50 +3464,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C36" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D36" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E36" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F36" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H36" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I36" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J36" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K36" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L36" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M36" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N36" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O36" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3516,83 +3515,83 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C37" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D37" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E37" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F37" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H37" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I37" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J37" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K37" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L37" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M37" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N37" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O37" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,7 +3604,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3624,59 +3623,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C38" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D38" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E38" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F38" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H38" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I38" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J38" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K38" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L38" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M38" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N38" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O38" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3684,24 +3679,28 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3713,50 +3712,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C39" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D39" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E39" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F39" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H39" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I39" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J39" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K39" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L39" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M39" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N39" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O39" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3767,7 +3766,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3779,12 +3778,12 @@
       </c>
       <c r="U39" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
@@ -3797,83 +3796,83 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C40" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D40" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E40" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F40" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H40" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I40" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J40" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K40" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L40" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M40" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N40" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O40" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>26211.31</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3881,69 +3880,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C41" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D41" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E41" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F41" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H41" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I41" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J41" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K41" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L41" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M41" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N41" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O41" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26129.3</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3965,50 +3958,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C42" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D42" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E42" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F42" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H42" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I42" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J42" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K42" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L42" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M42" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N42" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O42" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4021,14 +4014,18 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4038,55 +4035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C43" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D43" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E43" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F43" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H43" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I43" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J43" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K43" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L43" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M43" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N43" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O43" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4094,23 +4095,23 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4120,59 +4121,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C44" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D44" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E44" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F44" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I44" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J44" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K44" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L44" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M44" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N44" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O44" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4182,18 +4179,16 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4206,68 +4201,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C45" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D45" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E45" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F45" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I45" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J45" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K45" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L45" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M45" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N45" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O45" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4286,66 +4287,62 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C46" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D46" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E46" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F46" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I46" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J46" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K46" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L46" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M46" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N46" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O46" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -4353,9 +4350,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4377,57 +4374,57 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C47" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D47" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E47" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F47" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I47" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J47" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K47" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L47" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M47" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N47" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O47" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -4435,9 +4432,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4459,71 +4456,69 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C48" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D48" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E48" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F48" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H48" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I48" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J48" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K48" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L48" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M48" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N48" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O48" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4536,55 +4531,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C49" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D49" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E49" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F49" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H49" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I49" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J49" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K49" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L49" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M49" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N49" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O49" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4597,7 +4596,7 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4605,94 +4604,92 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C50" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D50" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E50" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F50" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I50" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J50" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K50" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L50" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M50" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N50" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O50" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4702,70 +4699,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C51" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D51" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E51" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F51" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H51" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I51" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J51" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K51" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L51" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M51" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N51" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O51" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4793,50 +4792,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C52" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D52" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E52" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F52" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H52" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I52" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J52" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K52" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L52" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M52" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N52" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O52" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4846,12 +4845,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4877,65 +4876,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C53" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D53" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E53" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F53" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H53" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I53" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J53" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K53" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L53" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M53" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N53" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O53" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4947,81 +4950,77 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C54" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D54" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E54" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F54" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H54" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I54" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J54" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K54" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L54" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M54" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N54" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O54" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5045,74 +5044,72 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C55" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D55" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E55" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F55" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H55" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I55" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J55" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K55" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L55" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M55" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N55" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O55" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5124,61 +5121,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C56" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D56" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E56" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F56" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H56" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I56" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J56" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K56" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L56" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M56" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N56" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O56" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
@@ -5187,13 +5190,11 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5208,74 +5209,70 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C57" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D57" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E57" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F57" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H57" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I57" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J57" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K57" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L57" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M57" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N57" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O57" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5301,63 +5298,69 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C58" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D58" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E58" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F58" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H58" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I58" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J58" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K58" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L58" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M58" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N58" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O58" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>25005.07</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5374,143 +5377,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C59" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D59" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E59" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F59" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H59" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I59" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J59" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K59" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L59" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M59" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N59" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O59" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
-      <c r="V59" s="8" t="n">
-        <v/>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C60" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D60" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E60" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F60" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H60" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I60" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J60" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K60" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L60" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M60" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N60" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O60" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5521,82 +5522,80 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24748.45</v>
+        <v>25170.8</v>
       </c>
       <c r="C61" t="n">
-        <v>25042.71</v>
+        <v>25254.11</v>
       </c>
       <c r="D61" t="n">
-        <v>24736.92</v>
+        <v>25043.64</v>
       </c>
       <c r="E61" t="n">
-        <v>25042.71</v>
+        <v>25087.75</v>
       </c>
       <c r="F61" t="n">
-        <v>291.93</v>
+        <v>45.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0018</v>
       </c>
       <c r="H61" t="n">
-        <v>305.79</v>
+        <v>210.47</v>
       </c>
       <c r="I61" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J61" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K61" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L61" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M61" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N61" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O61" t="n">
-        <v>25022.04</v>
+        <v>25348.5</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5607,25 +5606,21 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5653,41 +5648,43 @@
         <v>24834.12</v>
       </c>
       <c r="F62" t="n">
-        <v>-208.59</v>
+        <v>-253.63</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0101</v>
       </c>
       <c r="H62" t="n">
         <v>260.4</v>
       </c>
       <c r="I62" t="n">
-        <v>24431.13</v>
+        <v>24833.17</v>
       </c>
       <c r="J62" t="n">
-        <v>24813.37</v>
+        <v>24846.72</v>
       </c>
       <c r="K62" t="n">
-        <v>24889.82</v>
+        <v>24982.52</v>
       </c>
       <c r="L62" t="n">
-        <v>24966.26</v>
+        <v>25118.31</v>
       </c>
       <c r="M62" t="n">
-        <v>25195.61</v>
+        <v>25192.98</v>
       </c>
       <c r="N62" t="n">
-        <v>25424.95</v>
+        <v>25267.66</v>
       </c>
       <c r="O62" t="n">
-        <v>25348.5</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
+        <v>25464.58</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -5695,7 +5692,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5709,16 +5706,12 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5736,13 +5729,13 @@
         <v>24648.29</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>24761.13</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>-72.98999999999999</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>-0.0029</v>
       </c>
       <c r="H63" t="n">
         <v>142.91</v>
@@ -5768,22 +5761,20 @@
       <c r="O63" t="n">
         <v>25332.65</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5795,16 +5786,96 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>24523.5</v>
+      </c>
+      <c r="C64" t="n">
+        <v>24537.14</v>
+      </c>
+      <c r="D64" t="n">
+        <v>24275.56</v>
+      </c>
+      <c r="E64" t="n">
+        <v>24510.09</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-251.04</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.0101</v>
+      </c>
+      <c r="H64" t="n">
+        <v>261.58</v>
+      </c>
+      <c r="I64" t="n">
+        <v>24505.38</v>
+      </c>
+      <c r="J64" t="n">
+        <v>24638.91</v>
+      </c>
+      <c r="K64" t="n">
+        <v>24689.68</v>
+      </c>
+      <c r="L64" t="n">
+        <v>24740.44</v>
+      </c>
+      <c r="M64" t="n">
+        <v>24832.59</v>
+      </c>
+      <c r="N64" t="n">
+        <v>24924.73</v>
+      </c>
+      <c r="O64" t="n">
+        <v>24934.11</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,17 +104,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23007.87</v>
+        <v>23071.43</v>
       </c>
       <c r="C2" t="n">
-        <v>23086.85</v>
+        <v>23335.92</v>
       </c>
       <c r="D2" t="n">
-        <v>22685.14</v>
+        <v>22953.7</v>
       </c>
       <c r="E2" t="n">
-        <v>22881.02</v>
+        <v>23055.03</v>
       </c>
       <c r="F2" t="n">
-        <v>-145.66</v>
+        <v>174.01</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0076</v>
       </c>
       <c r="H2" t="n">
-        <v>401.71</v>
+        <v>382.22</v>
       </c>
       <c r="I2" t="n">
-        <v>22384.11</v>
+        <v>22283.43</v>
       </c>
       <c r="J2" t="n">
-        <v>22648.79</v>
+        <v>22476.82</v>
       </c>
       <c r="K2" t="n">
-        <v>22826.92</v>
+        <v>22680.17</v>
       </c>
       <c r="L2" t="n">
-        <v>23005.04</v>
+        <v>22883.51</v>
       </c>
       <c r="M2" t="n">
-        <v>23226.44</v>
+        <v>23081.87</v>
       </c>
       <c r="N2" t="n">
-        <v>23447.85</v>
+        <v>23280.24</v>
       </c>
       <c r="O2" t="n">
-        <v>23582.7</v>
+        <v>23488.56</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,21 +688,23 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -709,59 +714,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C3" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D3" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E3" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F3" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H3" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I3" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J3" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K3" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L3" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M3" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N3" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O3" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,19 +773,19 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V3" s="8" t="n">
@@ -800,50 +801,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C4" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D4" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E4" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F4" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H4" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I4" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J4" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K4" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L4" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M4" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N4" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O4" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,7 +855,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -882,50 +883,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C5" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D5" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E5" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F5" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H5" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I5" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J5" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K5" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L5" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M5" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N5" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O5" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,18 +939,14 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -959,55 +956,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C6" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D6" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E6" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F6" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H6" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I6" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J6" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K6" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L6" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M6" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N6" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O6" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,76 +1021,78 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C7" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D7" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E7" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F7" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H7" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I7" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J7" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K7" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L7" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M7" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N7" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O7" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,78 +1105,76 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C8" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D8" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E8" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F8" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H8" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I8" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J8" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K8" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L8" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M8" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N8" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O8" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,14 +1187,18 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1203,59 +1208,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C9" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D9" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E9" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F9" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H9" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I9" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J9" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K9" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L9" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M9" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N9" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O9" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,18 +1269,16 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1289,55 +1288,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C10" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D10" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E10" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F10" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H10" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I10" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J10" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K10" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L10" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M10" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N10" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O10" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1345,17 +1348,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1371,57 +1376,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C11" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D11" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E11" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F11" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H11" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I11" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J11" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K11" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L11" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M11" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N11" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O11" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1429,12 +1434,10 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1455,59 +1458,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C12" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D12" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E12" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F12" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H12" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I12" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J12" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K12" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L12" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M12" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N12" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O12" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,21 +1517,25 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1544,83 +1547,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C13" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D13" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E13" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F13" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H13" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I13" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J13" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K13" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L13" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M13" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N13" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O13" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>25617.86</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1628,77 +1631,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C14" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D14" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E14" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F14" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H14" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I14" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J14" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K14" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L14" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M14" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N14" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O14" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1707,55 +1708,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C15" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D15" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E15" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F15" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H15" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I15" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J15" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K15" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L15" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M15" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N15" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O15" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1766,20 +1771,16 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1798,63 +1799,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C16" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D16" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E16" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H16" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I16" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J16" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K16" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L16" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M16" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N16" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O16" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1871,90 +1876,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C17" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D17" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E17" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F17" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H17" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I17" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J17" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K17" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L17" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M17" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N17" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O17" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1962,220 +1965,220 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C18" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D18" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E18" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F18" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H18" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I18" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J18" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K18" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L18" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M18" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N18" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O18" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C19" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D19" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E19" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F19" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H19" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I19" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J19" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K19" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L19" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M19" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N19" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O19" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C20" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D20" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E20" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F20" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H20" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I20" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J20" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K20" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L20" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M20" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N20" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O20" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2186,25 +2189,21 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2216,50 +2215,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C21" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D21" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E21" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F21" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H21" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I21" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J21" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K21" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L21" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M21" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N21" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O21" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2270,21 +2269,25 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2296,50 +2299,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C22" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D22" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E22" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F22" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H22" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I22" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J22" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K22" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L22" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M22" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N22" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O22" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,25 +2353,21 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2380,50 +2379,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C23" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D23" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E23" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F23" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I23" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J23" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K23" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L23" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M23" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N23" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O23" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2431,18 +2430,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2455,55 +2454,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C24" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D24" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E24" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F24" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H24" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I24" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J24" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K24" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L24" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M24" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N24" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O24" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2511,18 +2514,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2535,59 +2538,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C25" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D25" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E25" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F25" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H25" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I25" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J25" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K25" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L25" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M25" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N25" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O25" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2595,17 +2594,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2619,55 +2620,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C26" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D26" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E26" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F26" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H26" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I26" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J26" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K26" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L26" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M26" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N26" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O26" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2675,20 +2680,16 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2710,63 +2711,69 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C27" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D27" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E27" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F27" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H27" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I27" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J27" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K27" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L27" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M27" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N27" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O27" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>26218.02</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2778,88 +2785,80 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C28" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D28" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E28" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F28" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H28" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I28" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J28" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K28" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L28" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M28" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N28" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O28" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2871,55 +2870,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C29" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D29" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E29" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F29" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H29" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I29" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J29" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K29" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L29" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M29" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N29" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O29" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2930,21 +2933,23 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
@@ -2960,63 +2965,67 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C30" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D30" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E30" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F30" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H30" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I30" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J30" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K30" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L30" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M30" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N30" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O30" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3027,10 +3036,8 @@
       <c r="U30" s="8" t="n">
         <v/>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="11" t="inlineStr">
         <is>
@@ -3039,80 +3046,76 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C31" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D31" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E31" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F31" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I31" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J31" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K31" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L31" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M31" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N31" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O31" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3125,59 +3128,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C32" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D32" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E32" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F32" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H32" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I32" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J32" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K32" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L32" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M32" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N32" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O32" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,12 +3186,12 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3209,70 +3208,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C33" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D33" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E33" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F33" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H33" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I33" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J33" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K33" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L33" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M33" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N33" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O33" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3289,90 +3294,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C34" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D34" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E34" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F34" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H34" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I34" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J34" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K34" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L34" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M34" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N34" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O34" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3380,50 +3383,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C35" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D35" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E35" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F35" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H35" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I35" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J35" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K35" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L35" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M35" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N35" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O35" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3431,83 +3434,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C36" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D36" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E36" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F36" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H36" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I36" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J36" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K36" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L36" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M36" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N36" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O36" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3520,7 +3523,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3539,59 +3542,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C37" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D37" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E37" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F37" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H37" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I37" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J37" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K37" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L37" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M37" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N37" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O37" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3599,24 +3598,28 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3628,50 +3631,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C38" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D38" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E38" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F38" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H38" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I38" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J38" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K38" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L38" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M38" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N38" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O38" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3682,7 +3685,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3694,12 +3697,12 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
@@ -3712,83 +3715,83 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C39" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D39" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E39" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F39" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H39" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I39" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J39" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K39" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L39" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M39" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N39" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O39" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+        <v>26211.31</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3796,69 +3799,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C40" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D40" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E40" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F40" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H40" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I40" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J40" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K40" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L40" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M40" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N40" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O40" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26129.3</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3880,50 +3877,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C41" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D41" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E41" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H41" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I41" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J41" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K41" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L41" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M41" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N41" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O41" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3936,14 +3933,18 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3953,55 +3954,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C42" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D42" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E42" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F42" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H42" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I42" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J42" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K42" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L42" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M42" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N42" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O42" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4009,23 +4014,23 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4035,59 +4040,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C43" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D43" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E43" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F43" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I43" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J43" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K43" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L43" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M43" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N43" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O43" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4097,18 +4098,16 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4121,68 +4120,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C44" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D44" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E44" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F44" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I44" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J44" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K44" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L44" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M44" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N44" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O44" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4201,66 +4206,62 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C45" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D45" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E45" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F45" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I45" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J45" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K45" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L45" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M45" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N45" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O45" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4268,9 +4269,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4292,57 +4293,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C46" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D46" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E46" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F46" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I46" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J46" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K46" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L46" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M46" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N46" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O46" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -4350,9 +4351,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4374,71 +4375,69 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C47" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D47" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E47" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F47" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H47" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I47" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J47" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K47" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L47" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M47" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N47" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O47" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4451,55 +4450,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C48" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D48" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E48" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F48" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H48" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I48" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J48" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K48" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L48" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M48" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N48" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O48" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4512,7 +4515,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4520,94 +4523,92 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C49" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D49" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E49" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F49" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I49" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J49" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K49" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L49" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M49" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N49" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O49" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4617,70 +4618,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C50" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D50" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E50" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F50" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H50" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I50" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J50" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K50" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L50" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M50" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N50" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O50" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4708,50 +4711,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C51" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D51" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E51" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F51" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H51" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I51" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J51" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K51" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L51" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M51" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N51" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O51" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4761,12 +4764,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4792,65 +4795,69 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C52" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D52" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E52" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F52" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H52" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I52" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J52" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K52" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L52" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M52" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N52" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O52" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4862,81 +4869,77 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C53" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D53" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E53" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F53" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H53" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I53" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J53" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K53" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L53" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M53" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N53" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O53" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4960,74 +4963,72 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C54" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D54" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E54" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F54" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H54" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I54" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J54" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K54" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L54" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M54" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N54" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O54" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5039,61 +5040,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C55" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D55" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E55" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F55" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H55" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I55" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J55" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K55" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L55" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M55" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N55" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O55" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5102,13 +5109,11 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5123,74 +5128,70 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C56" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D56" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E56" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F56" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H56" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I56" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J56" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K56" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L56" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M56" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N56" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O56" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5216,63 +5217,69 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C57" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D57" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E57" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F57" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H57" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I57" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J57" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K57" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L57" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M57" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N57" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O57" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>25005.07</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5289,143 +5296,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C58" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D58" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E58" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H58" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I58" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J58" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K58" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L58" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M58" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N58" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O58" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
-      <c r="V58" s="8" t="n">
-        <v/>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C59" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D59" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E59" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F59" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H59" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I59" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J59" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K59" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L59" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M59" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N59" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O59" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5436,82 +5441,80 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24748.45</v>
+        <v>25170.8</v>
       </c>
       <c r="C60" t="n">
-        <v>25042.71</v>
+        <v>25254.11</v>
       </c>
       <c r="D60" t="n">
-        <v>24736.92</v>
+        <v>25043.64</v>
       </c>
       <c r="E60" t="n">
-        <v>25042.71</v>
+        <v>25087.75</v>
       </c>
       <c r="F60" t="n">
-        <v>291.93</v>
+        <v>45.04</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0018</v>
       </c>
       <c r="H60" t="n">
-        <v>305.79</v>
+        <v>210.47</v>
       </c>
       <c r="I60" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J60" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K60" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L60" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M60" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N60" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O60" t="n">
-        <v>25022.04</v>
+        <v>25348.5</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5522,25 +5525,21 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5552,69 +5551,73 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25170.8</v>
+        <v>25064.84</v>
       </c>
       <c r="C61" t="n">
-        <v>25254.11</v>
+        <v>25072.25</v>
       </c>
       <c r="D61" t="n">
-        <v>25043.64</v>
+        <v>24811.85</v>
       </c>
       <c r="E61" t="n">
-        <v>25087.75</v>
+        <v>24834.12</v>
       </c>
       <c r="F61" t="n">
-        <v>45.04</v>
+        <v>-253.63</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0018</v>
+        <v>-0.0101</v>
       </c>
       <c r="H61" t="n">
-        <v>210.47</v>
+        <v>260.4</v>
       </c>
       <c r="I61" t="n">
-        <v>24431.13</v>
+        <v>24833.17</v>
       </c>
       <c r="J61" t="n">
-        <v>24813.37</v>
+        <v>24846.72</v>
       </c>
       <c r="K61" t="n">
-        <v>24889.82</v>
+        <v>24982.52</v>
       </c>
       <c r="L61" t="n">
-        <v>24966.26</v>
+        <v>25118.31</v>
       </c>
       <c r="M61" t="n">
-        <v>25195.61</v>
+        <v>25192.98</v>
       </c>
       <c r="N61" t="n">
-        <v>25424.95</v>
+        <v>25267.66</v>
       </c>
       <c r="O61" t="n">
-        <v>25348.5</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+        <v>25464.58</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5622,9 +5625,9 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -5632,67 +5635,63 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>25064.84</v>
+        <v>24649.45</v>
       </c>
       <c r="C62" t="n">
-        <v>25072.25</v>
+        <v>24791.2</v>
       </c>
       <c r="D62" t="n">
-        <v>24811.85</v>
+        <v>24648.29</v>
       </c>
       <c r="E62" t="n">
-        <v>24834.12</v>
+        <v>24761.13</v>
       </c>
       <c r="F62" t="n">
-        <v>-253.63</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0029</v>
       </c>
       <c r="H62" t="n">
-        <v>260.4</v>
+        <v>142.91</v>
       </c>
       <c r="I62" t="n">
-        <v>24833.17</v>
+        <v>24551.45</v>
       </c>
       <c r="J62" t="n">
-        <v>24846.72</v>
+        <v>24519.75</v>
       </c>
       <c r="K62" t="n">
-        <v>24982.52</v>
+        <v>24703.92</v>
       </c>
       <c r="L62" t="n">
-        <v>25118.31</v>
+        <v>24888.08</v>
       </c>
       <c r="M62" t="n">
-        <v>25192.98</v>
+        <v>24964.32</v>
       </c>
       <c r="N62" t="n">
-        <v>25267.66</v>
+        <v>25040.55</v>
       </c>
       <c r="O62" t="n">
-        <v>25464.58</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+        <v>25332.65</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5716,63 +5715,67 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24649.45</v>
+        <v>24523.5</v>
       </c>
       <c r="C63" t="n">
-        <v>24791.2</v>
+        <v>24537.14</v>
       </c>
       <c r="D63" t="n">
-        <v>24648.29</v>
+        <v>24275.56</v>
       </c>
       <c r="E63" t="n">
-        <v>24761.13</v>
+        <v>24510.09</v>
       </c>
       <c r="F63" t="n">
-        <v>-72.98999999999999</v>
+        <v>-251.04</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H63" t="n">
-        <v>142.91</v>
+        <v>261.58</v>
       </c>
       <c r="I63" t="n">
-        <v>24551.45</v>
+        <v>24505.38</v>
       </c>
       <c r="J63" t="n">
-        <v>24519.75</v>
+        <v>24638.91</v>
       </c>
       <c r="K63" t="n">
-        <v>24703.92</v>
+        <v>24689.68</v>
       </c>
       <c r="L63" t="n">
-        <v>24888.08</v>
+        <v>24740.44</v>
       </c>
       <c r="M63" t="n">
-        <v>24964.32</v>
+        <v>24832.59</v>
       </c>
       <c r="N63" t="n">
-        <v>25040.55</v>
+        <v>24924.73</v>
       </c>
       <c r="O63" t="n">
-        <v>25332.65</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
+        <v>24934.11</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5796,73 +5799,71 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>24523.5</v>
+        <v>24554.58</v>
       </c>
       <c r="C64" t="n">
-        <v>24537.14</v>
+        <v>24767.22</v>
       </c>
       <c r="D64" t="n">
-        <v>24275.56</v>
+        <v>24554.58</v>
       </c>
       <c r="E64" t="n">
-        <v>24510.09</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>-251.04</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0101</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>261.58</v>
+        <v>212.64</v>
       </c>
       <c r="I64" t="n">
-        <v>24505.38</v>
+        <v>24013.98</v>
       </c>
       <c r="J64" t="n">
-        <v>24638.91</v>
+        <v>24300.38</v>
       </c>
       <c r="K64" t="n">
-        <v>24689.68</v>
+        <v>24379.3</v>
       </c>
       <c r="L64" t="n">
-        <v>24740.44</v>
+        <v>24458.22</v>
       </c>
       <c r="M64" t="n">
-        <v>24832.59</v>
+        <v>24640.88</v>
       </c>
       <c r="N64" t="n">
-        <v>24924.73</v>
+        <v>24823.54</v>
       </c>
       <c r="O64" t="n">
-        <v>24934.11</v>
+        <v>24798.72</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5875,7 +5876,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -637,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23071.43</v>
+        <v>23240.85</v>
       </c>
       <c r="C2" t="n">
-        <v>23335.92</v>
+        <v>23516.7</v>
       </c>
       <c r="D2" t="n">
-        <v>22953.7</v>
+        <v>23226.2</v>
       </c>
       <c r="E2" t="n">
-        <v>23055.03</v>
+        <v>23350.03</v>
       </c>
       <c r="F2" t="n">
-        <v>174.01</v>
+        <v>295</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0128</v>
       </c>
       <c r="H2" t="n">
-        <v>382.22</v>
+        <v>290.5</v>
       </c>
       <c r="I2" t="n">
-        <v>22283.43</v>
+        <v>22571.48</v>
       </c>
       <c r="J2" t="n">
-        <v>22476.82</v>
+        <v>22627.92</v>
       </c>
       <c r="K2" t="n">
-        <v>22680.17</v>
+        <v>22863.92</v>
       </c>
       <c r="L2" t="n">
-        <v>22883.51</v>
+        <v>23099.92</v>
       </c>
       <c r="M2" t="n">
-        <v>23081.87</v>
+        <v>23246.14</v>
       </c>
       <c r="N2" t="n">
-        <v>23280.24</v>
+        <v>23392.36</v>
       </c>
       <c r="O2" t="n">
-        <v>23488.56</v>
+        <v>23718.14</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,12 +698,12 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V2" s="8" t="n">
@@ -719,50 +719,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C3" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D3" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E3" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F3" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H3" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I3" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J3" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K3" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L3" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M3" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N3" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O3" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -801,50 +801,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C4" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D4" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E4" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F4" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H4" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I4" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J4" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K4" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L4" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M4" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N4" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O4" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,20 +855,16 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -878,55 +874,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C5" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D5" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E5" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F5" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H5" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I5" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J5" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K5" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L5" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M5" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N5" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O5" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,78 +937,80 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C6" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D6" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E6" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F6" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H6" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I6" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J6" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K6" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L6" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M6" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N6" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O6" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,80 +1021,78 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C7" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D7" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E7" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F7" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H7" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I7" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J7" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K7" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L7" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M7" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N7" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O7" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,16 +1103,20 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1122,59 +1126,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C8" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D8" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E8" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F8" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H8" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I8" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J8" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K8" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L8" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M8" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N8" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O8" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,20 +1185,18 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1208,55 +1206,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C9" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D9" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E9" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F9" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H9" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I9" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J9" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K9" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L9" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M9" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N9" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O9" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1264,17 +1266,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1290,57 +1294,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C10" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D10" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E10" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F10" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H10" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I10" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J10" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K10" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L10" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M10" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N10" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O10" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1348,10 +1352,8 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1374,59 +1376,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C11" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D11" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E11" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F11" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H11" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I11" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J11" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K11" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L11" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M11" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N11" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O11" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,14 +1442,18 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1463,83 +1465,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C12" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D12" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E12" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F12" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H12" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I12" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J12" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K12" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L12" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M12" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N12" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O12" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1547,77 +1549,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C13" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D13" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E13" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F13" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H13" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I13" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J13" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K13" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L13" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M13" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N13" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O13" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1626,55 +1626,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C14" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D14" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E14" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F14" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H14" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I14" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J14" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K14" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L14" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M14" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N14" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O14" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,18 +1691,14 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1717,63 +1717,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C15" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D15" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E15" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H15" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I15" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J15" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K15" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L15" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M15" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N15" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O15" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1790,90 +1794,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C16" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D16" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E16" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F16" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H16" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I16" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J16" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K16" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L16" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M16" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N16" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O16" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1881,220 +1883,220 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C17" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D17" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E17" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F17" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H17" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I17" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J17" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K17" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L17" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M17" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N17" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O17" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C18" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D18" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E18" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F18" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H18" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I18" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J18" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K18" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L18" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M18" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N18" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O18" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C19" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D19" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E19" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F19" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H19" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I19" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J19" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K19" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L19" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M19" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N19" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O19" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,18 +2114,14 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2135,50 +2133,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C20" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D20" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E20" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F20" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H20" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I20" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J20" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K20" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L20" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M20" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N20" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O20" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2196,14 +2194,18 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2215,50 +2217,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C21" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D21" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E21" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F21" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H21" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I21" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J21" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K21" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L21" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M21" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N21" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O21" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,18 +2278,14 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2299,50 +2297,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C22" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D22" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E22" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F22" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I22" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J22" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K22" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L22" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M22" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N22" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O22" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,18 +2348,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2374,55 +2372,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C23" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D23" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E23" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F23" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H23" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I23" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J23" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K23" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L23" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M23" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N23" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O23" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2430,18 +2432,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2454,59 +2456,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C24" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D24" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E24" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F24" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H24" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I24" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J24" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K24" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L24" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M24" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N24" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O24" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2514,17 +2512,19 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2538,55 +2538,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C25" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D25" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E25" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F25" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H25" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I25" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J25" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K25" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L25" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M25" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N25" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O25" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2594,20 +2598,16 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2629,63 +2629,69 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C26" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D26" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E26" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F26" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H26" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I26" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J26" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K26" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L26" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M26" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N26" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O26" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2697,88 +2703,80 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C27" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D27" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E27" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F27" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H27" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I27" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J27" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K27" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L27" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M27" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N27" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O27" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2790,55 +2788,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C28" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D28" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E28" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F28" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H28" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I28" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J28" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K28" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L28" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M28" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N28" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O28" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,14 +2858,16 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
@@ -2879,63 +2883,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C29" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D29" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E29" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F29" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H29" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I29" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J29" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K29" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L29" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M29" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N29" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O29" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2946,10 +2954,8 @@
       <c r="U29" s="8" t="n">
         <v/>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
@@ -2958,80 +2964,76 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C30" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D30" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E30" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F30" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H30" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I30" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J30" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K30" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L30" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M30" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N30" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O30" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3044,59 +3046,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C31" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D31" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E31" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F31" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H31" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I31" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J31" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K31" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L31" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M31" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N31" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O31" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3106,12 +3104,12 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3128,61 +3126,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C32" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D32" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E32" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F32" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H32" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I32" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J32" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K32" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L32" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M32" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N32" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O32" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
@@ -3191,7 +3195,7 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3208,90 +3212,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C33" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D33" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E33" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F33" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H33" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I33" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J33" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K33" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L33" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M33" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N33" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O33" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3299,50 +3301,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C34" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D34" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E34" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F34" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H34" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I34" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J34" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K34" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L34" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M34" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N34" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O34" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,83 +3352,83 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C35" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D35" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E35" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F35" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H35" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I35" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J35" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K35" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L35" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M35" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N35" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O35" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3458,59 +3460,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C36" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D36" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E36" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F36" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H36" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I36" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J36" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K36" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L36" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M36" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N36" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O36" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3518,24 +3516,28 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3547,50 +3549,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C37" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D37" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E37" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F37" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H37" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I37" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J37" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K37" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L37" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M37" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N37" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O37" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,12 +3615,12 @@
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
@@ -3631,83 +3633,83 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C38" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D38" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E38" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F38" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H38" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I38" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J38" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K38" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L38" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M38" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N38" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O38" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3715,69 +3717,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C39" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D39" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E39" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F39" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H39" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I39" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J39" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K39" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L39" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M39" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N39" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O39" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3799,50 +3795,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C40" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D40" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E40" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H40" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I40" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J40" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K40" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L40" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M40" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N40" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O40" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3853,16 +3849,20 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3872,55 +3872,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C41" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D41" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E41" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F41" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H41" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I41" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J41" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K41" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L41" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M41" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N41" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O41" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3928,23 +3932,23 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3954,59 +3958,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C42" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D42" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E42" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F42" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I42" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J42" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K42" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L42" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M42" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N42" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O42" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4016,18 +4016,16 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4040,61 +4038,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C43" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D43" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E43" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F43" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I43" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J43" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K43" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L43" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M43" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N43" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O43" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4120,66 +4124,62 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C44" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D44" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E44" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F44" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I44" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J44" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K44" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L44" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M44" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N44" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O44" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4211,57 +4211,57 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C45" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D45" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E45" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F45" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I45" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J45" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K45" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L45" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M45" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N45" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O45" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4293,71 +4293,69 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C46" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D46" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E46" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F46" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H46" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I46" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J46" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K46" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L46" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M46" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N46" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O46" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4370,55 +4368,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C47" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D47" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E47" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F47" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H47" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I47" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J47" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K47" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L47" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M47" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N47" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O47" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4429,9 +4431,9 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4439,95 +4441,93 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C48" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D48" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E48" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F48" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I48" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J48" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K48" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L48" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M48" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N48" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O48" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4536,67 +4536,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C49" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D49" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E49" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F49" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H49" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I49" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J49" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K49" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L49" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M49" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N49" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O49" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4627,50 +4629,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C50" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D50" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E50" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F50" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H50" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I50" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J50" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K50" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L50" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M50" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N50" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O50" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4680,12 +4682,12 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4711,56 +4713,60 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C51" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D51" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E51" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F51" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H51" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I51" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J51" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K51" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L51" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M51" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N51" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O51" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4769,7 +4775,7 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4781,73 +4787,69 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C52" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D52" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E52" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F52" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H52" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I52" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J52" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K52" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L52" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M52" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N52" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O52" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4879,74 +4881,72 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C53" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D53" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E53" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F53" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H53" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I53" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J53" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K53" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L53" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M53" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N53" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O53" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4958,76 +4958,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C54" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D54" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E54" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F54" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H54" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I54" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J54" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K54" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L54" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M54" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N54" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O54" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5042,74 +5046,70 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C55" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D55" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E55" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F55" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H55" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I55" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J55" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K55" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L55" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M55" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N55" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O55" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5135,63 +5135,69 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C56" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D56" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E56" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F56" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H56" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I56" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J56" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K56" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L56" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M56" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N56" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O56" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+        <v>25005.07</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5208,143 +5214,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C57" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D57" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E57" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F57" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H57" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I57" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J57" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K57" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L57" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M57" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N57" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O57" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C58" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D58" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E58" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F58" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H58" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I58" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J58" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K58" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L58" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M58" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N58" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O58" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5362,75 +5366,73 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>24748.45</v>
+        <v>25170.8</v>
       </c>
       <c r="C59" t="n">
-        <v>25042.71</v>
+        <v>25254.11</v>
       </c>
       <c r="D59" t="n">
-        <v>24736.92</v>
+        <v>25043.64</v>
       </c>
       <c r="E59" t="n">
-        <v>25042.71</v>
+        <v>25087.75</v>
       </c>
       <c r="F59" t="n">
-        <v>291.93</v>
+        <v>45.04</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0018</v>
       </c>
       <c r="H59" t="n">
-        <v>305.79</v>
+        <v>210.47</v>
       </c>
       <c r="I59" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J59" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K59" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L59" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M59" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N59" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O59" t="n">
-        <v>25022.04</v>
+        <v>25348.5</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5448,18 +5450,14 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5471,79 +5469,83 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25170.8</v>
+        <v>25064.84</v>
       </c>
       <c r="C60" t="n">
-        <v>25254.11</v>
+        <v>25072.25</v>
       </c>
       <c r="D60" t="n">
-        <v>25043.64</v>
+        <v>24811.85</v>
       </c>
       <c r="E60" t="n">
-        <v>25087.75</v>
+        <v>24834.12</v>
       </c>
       <c r="F60" t="n">
-        <v>45.04</v>
+        <v>-253.63</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0018</v>
+        <v>-0.0101</v>
       </c>
       <c r="H60" t="n">
-        <v>210.47</v>
+        <v>260.4</v>
       </c>
       <c r="I60" t="n">
-        <v>24431.13</v>
+        <v>24833.17</v>
       </c>
       <c r="J60" t="n">
-        <v>24813.37</v>
+        <v>24846.72</v>
       </c>
       <c r="K60" t="n">
-        <v>24889.82</v>
+        <v>24982.52</v>
       </c>
       <c r="L60" t="n">
-        <v>24966.26</v>
+        <v>25118.31</v>
       </c>
       <c r="M60" t="n">
-        <v>25195.61</v>
+        <v>25192.98</v>
       </c>
       <c r="N60" t="n">
-        <v>25424.95</v>
+        <v>25267.66</v>
       </c>
       <c r="O60" t="n">
-        <v>25348.5</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+        <v>25464.58</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5551,64 +5553,60 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25064.84</v>
+        <v>24649.45</v>
       </c>
       <c r="C61" t="n">
-        <v>25072.25</v>
+        <v>24791.2</v>
       </c>
       <c r="D61" t="n">
-        <v>24811.85</v>
+        <v>24648.29</v>
       </c>
       <c r="E61" t="n">
-        <v>24834.12</v>
+        <v>24761.13</v>
       </c>
       <c r="F61" t="n">
-        <v>-253.63</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0029</v>
       </c>
       <c r="H61" t="n">
-        <v>260.4</v>
+        <v>142.91</v>
       </c>
       <c r="I61" t="n">
-        <v>24833.17</v>
+        <v>24551.45</v>
       </c>
       <c r="J61" t="n">
-        <v>24846.72</v>
+        <v>24519.75</v>
       </c>
       <c r="K61" t="n">
-        <v>24982.52</v>
+        <v>24703.92</v>
       </c>
       <c r="L61" t="n">
-        <v>25118.31</v>
+        <v>24888.08</v>
       </c>
       <c r="M61" t="n">
-        <v>25192.98</v>
+        <v>24964.32</v>
       </c>
       <c r="N61" t="n">
-        <v>25267.66</v>
+        <v>25040.55</v>
       </c>
       <c r="O61" t="n">
-        <v>25464.58</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>25332.65</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
@@ -5635,60 +5633,64 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24649.45</v>
+        <v>24523.5</v>
       </c>
       <c r="C62" t="n">
-        <v>24791.2</v>
+        <v>24537.14</v>
       </c>
       <c r="D62" t="n">
-        <v>24648.29</v>
+        <v>24275.56</v>
       </c>
       <c r="E62" t="n">
-        <v>24761.13</v>
+        <v>24510.09</v>
       </c>
       <c r="F62" t="n">
-        <v>-72.98999999999999</v>
+        <v>-251.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H62" t="n">
-        <v>142.91</v>
+        <v>261.58</v>
       </c>
       <c r="I62" t="n">
-        <v>24551.45</v>
+        <v>24505.38</v>
       </c>
       <c r="J62" t="n">
-        <v>24519.75</v>
+        <v>24638.91</v>
       </c>
       <c r="K62" t="n">
-        <v>24703.92</v>
+        <v>24689.68</v>
       </c>
       <c r="L62" t="n">
-        <v>24888.08</v>
+        <v>24740.44</v>
       </c>
       <c r="M62" t="n">
-        <v>24964.32</v>
+        <v>24832.59</v>
       </c>
       <c r="N62" t="n">
-        <v>25040.55</v>
+        <v>24924.73</v>
       </c>
       <c r="O62" t="n">
-        <v>25332.65</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+        <v>24934.11</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
@@ -5715,74 +5717,70 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24523.5</v>
+        <v>24554.58</v>
       </c>
       <c r="C63" t="n">
-        <v>24537.14</v>
+        <v>24767.22</v>
       </c>
       <c r="D63" t="n">
-        <v>24275.56</v>
+        <v>24554.58</v>
       </c>
       <c r="E63" t="n">
-        <v>24510.09</v>
+        <v>24642.51</v>
       </c>
       <c r="F63" t="n">
-        <v>-251.04</v>
+        <v>132.42</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0054</v>
       </c>
       <c r="H63" t="n">
-        <v>261.58</v>
+        <v>212.64</v>
       </c>
       <c r="I63" t="n">
-        <v>24505.38</v>
+        <v>24013.98</v>
       </c>
       <c r="J63" t="n">
-        <v>24638.91</v>
+        <v>24300.38</v>
       </c>
       <c r="K63" t="n">
-        <v>24689.68</v>
+        <v>24379.3</v>
       </c>
       <c r="L63" t="n">
-        <v>24740.44</v>
+        <v>24458.22</v>
       </c>
       <c r="M63" t="n">
-        <v>24832.59</v>
+        <v>24640.88</v>
       </c>
       <c r="N63" t="n">
-        <v>24924.73</v>
+        <v>24823.54</v>
       </c>
       <c r="O63" t="n">
-        <v>24934.11</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
+        <v>24798.72</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
@@ -5794,22 +5792,26 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>24554.58</v>
+        <v>24648.64</v>
       </c>
       <c r="C64" t="n">
-        <v>24767.22</v>
+        <v>24648.64</v>
       </c>
       <c r="D64" t="n">
-        <v>24554.58</v>
+        <v>24444.15</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5821,28 +5823,28 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>212.64</v>
+        <v>204.49</v>
       </c>
       <c r="I64" t="n">
-        <v>24013.98</v>
+        <v>24341.94</v>
       </c>
       <c r="J64" t="n">
-        <v>24300.38</v>
+        <v>24420.67</v>
       </c>
       <c r="K64" t="n">
-        <v>24379.3</v>
+        <v>24536.19</v>
       </c>
       <c r="L64" t="n">
-        <v>24458.22</v>
+        <v>24651.71</v>
       </c>
       <c r="M64" t="n">
-        <v>24640.88</v>
+        <v>24748.83</v>
       </c>
       <c r="N64" t="n">
-        <v>24823.54</v>
+        <v>24845.96</v>
       </c>
       <c r="O64" t="n">
-        <v>24798.72</v>
+        <v>24979.86</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -5852,18 +5854,18 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S64" s="12" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5876,11 +5878,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5814,13 +5814,13 @@
         <v>24444.15</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>24523.57</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>-118.94</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>-0.0048</v>
       </c>
       <c r="H64" t="n">
         <v>204.49</v>
@@ -5846,39 +5846,121 @@
       <c r="O64" t="n">
         <v>24979.86</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>24393.88</v>
+      </c>
+      <c r="C65" t="n">
+        <v>24637.65</v>
+      </c>
+      <c r="D65" t="n">
+        <v>24332.64</v>
+      </c>
+      <c r="E65" t="n">
+        <v/>
+      </c>
+      <c r="F65" t="n">
+        <v/>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H65" t="n">
+        <v>305.01</v>
+      </c>
+      <c r="I65" t="n">
+        <v>24239.66</v>
+      </c>
+      <c r="J65" t="n">
+        <v>24307.67</v>
+      </c>
+      <c r="K65" t="n">
+        <v>24421.33</v>
+      </c>
+      <c r="L65" t="n">
+        <v>24534.98</v>
+      </c>
+      <c r="M65" t="n">
+        <v>24625.82</v>
+      </c>
+      <c r="N65" t="n">
+        <v>24716.65</v>
+      </c>
+      <c r="O65" t="n">
+        <v>24853.13</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S65" s="12" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23240.85</v>
+        <v>23404.61</v>
       </c>
       <c r="C2" t="n">
-        <v>23516.7</v>
+        <v>23686.56</v>
       </c>
       <c r="D2" t="n">
-        <v>23226.2</v>
+        <v>23229.38</v>
       </c>
       <c r="E2" t="n">
-        <v>23350.03</v>
+        <v>23616.32</v>
       </c>
       <c r="F2" t="n">
-        <v>295</v>
+        <v>266.29</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0114</v>
       </c>
       <c r="H2" t="n">
-        <v>290.5</v>
+        <v>457.18</v>
       </c>
       <c r="I2" t="n">
-        <v>22571.48</v>
+        <v>22935.7</v>
       </c>
       <c r="J2" t="n">
-        <v>22627.92</v>
+        <v>23048.82</v>
       </c>
       <c r="K2" t="n">
-        <v>22863.92</v>
+        <v>23204.78</v>
       </c>
       <c r="L2" t="n">
-        <v>23099.92</v>
+        <v>23360.74</v>
       </c>
       <c r="M2" t="n">
-        <v>23246.14</v>
+        <v>23495.28</v>
       </c>
       <c r="N2" t="n">
-        <v>23392.36</v>
+        <v>23629.82</v>
       </c>
       <c r="O2" t="n">
-        <v>23718.14</v>
+        <v>23807.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -719,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C3" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D3" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E3" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F3" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H3" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I3" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J3" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K3" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L3" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M3" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N3" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O3" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,20 +770,16 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -796,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C4" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D4" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E4" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F4" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H4" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I4" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J4" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K4" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L4" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M4" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N4" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O4" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,78 +852,80 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C5" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D5" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E5" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F5" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H5" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I5" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J5" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K5" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L5" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M5" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N5" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O5" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,80 +936,78 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C6" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D6" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E6" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F6" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H6" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I6" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J6" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K6" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L6" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M6" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N6" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O6" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,16 +1018,20 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1040,59 +1041,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C7" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D7" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E7" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F7" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H7" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I7" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J7" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K7" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L7" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M7" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N7" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O7" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,20 +1100,18 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1126,55 +1121,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C8" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D8" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E8" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F8" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H8" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I8" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J8" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K8" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L8" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M8" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N8" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O8" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1182,17 +1181,19 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1208,57 +1209,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C9" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D9" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E9" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F9" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H9" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I9" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J9" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K9" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L9" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M9" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N9" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O9" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,10 +1267,8 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
@@ -1292,59 +1291,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C10" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D10" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E10" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F10" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H10" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I10" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J10" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K10" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L10" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M10" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N10" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O10" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,14 +1357,18 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1381,83 +1380,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C11" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D11" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E11" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F11" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H11" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I11" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J11" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K11" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L11" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M11" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N11" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O11" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
+        <v>25617.86</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1465,77 +1464,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C12" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D12" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E12" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F12" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H12" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I12" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J12" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K12" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L12" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M12" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N12" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O12" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1544,55 +1541,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C13" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D13" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E13" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F13" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H13" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I13" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J13" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K13" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L13" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M13" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N13" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O13" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1605,18 +1606,14 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1635,63 +1632,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C14" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D14" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E14" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H14" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I14" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J14" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K14" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L14" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M14" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N14" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O14" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1708,90 +1709,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C15" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D15" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E15" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F15" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H15" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I15" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J15" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K15" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L15" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M15" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N15" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O15" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1799,220 +1798,220 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C16" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D16" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E16" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F16" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H16" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I16" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J16" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K16" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L16" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M16" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N16" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O16" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C17" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D17" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E17" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F17" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H17" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I17" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J17" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K17" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L17" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M17" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N17" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O17" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C18" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D18" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E18" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F18" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H18" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I18" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J18" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K18" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L18" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M18" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N18" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O18" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,18 +2029,14 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2053,50 +2048,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C19" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D19" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E19" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F19" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H19" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I19" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J19" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K19" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L19" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M19" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N19" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O19" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2114,14 +2109,18 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2133,50 +2132,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C20" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D20" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E20" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F20" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H20" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I20" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J20" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K20" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L20" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M20" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N20" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O20" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,18 +2193,14 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2217,50 +2212,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C21" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D21" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E21" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F21" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I21" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J21" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K21" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L21" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M21" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N21" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O21" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2268,18 +2263,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2292,55 +2287,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C22" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D22" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E22" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F22" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H22" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I22" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J22" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K22" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L22" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M22" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N22" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O22" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2348,18 +2347,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2372,59 +2371,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C23" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D23" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E23" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F23" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H23" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I23" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J23" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K23" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L23" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M23" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N23" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O23" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2432,17 +2427,19 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2456,55 +2453,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C24" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D24" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E24" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F24" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H24" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I24" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J24" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K24" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L24" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M24" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N24" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O24" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2512,20 +2513,16 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2547,63 +2544,69 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C25" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D25" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E25" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F25" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H25" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I25" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J25" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K25" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L25" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M25" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N25" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O25" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>26218.02</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2615,88 +2618,80 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C26" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D26" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E26" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F26" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H26" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I26" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J26" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K26" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L26" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M26" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N26" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O26" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2708,55 +2703,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C27" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D27" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E27" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F27" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H27" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I27" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J27" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K27" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L27" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M27" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N27" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O27" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2774,14 +2773,16 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
@@ -2797,63 +2798,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C28" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D28" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E28" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F28" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H28" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I28" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J28" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K28" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L28" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M28" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N28" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O28" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2864,10 +2869,8 @@
       <c r="U28" s="8" t="n">
         <v/>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
@@ -2876,80 +2879,76 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C29" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D29" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E29" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F29" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H29" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I29" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J29" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K29" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L29" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M29" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N29" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O29" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2962,59 +2961,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C30" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D30" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E30" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F30" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H30" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I30" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J30" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K30" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L30" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M30" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N30" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O30" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3024,12 +3019,12 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3046,61 +3041,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C31" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D31" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E31" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F31" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H31" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I31" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J31" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K31" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L31" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M31" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N31" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O31" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
@@ -3109,7 +3110,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3126,90 +3127,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C32" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D32" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E32" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F32" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H32" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I32" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J32" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K32" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L32" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M32" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N32" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O32" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3217,50 +3216,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C33" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D33" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E33" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F33" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H33" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I33" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J33" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K33" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L33" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M33" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N33" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O33" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3268,83 +3267,83 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C34" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D34" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E34" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F34" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H34" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I34" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J34" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K34" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L34" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M34" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N34" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O34" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3376,59 +3375,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C35" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D35" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E35" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F35" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H35" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I35" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J35" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K35" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L35" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M35" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N35" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O35" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3436,24 +3431,28 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3465,50 +3464,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C36" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D36" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E36" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F36" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H36" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I36" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J36" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K36" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L36" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M36" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N36" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O36" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3531,12 +3530,12 @@
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
@@ -3549,83 +3548,83 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C37" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D37" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E37" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F37" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H37" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I37" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J37" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K37" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L37" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M37" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N37" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O37" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
+        <v>26211.31</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3633,69 +3632,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C38" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D38" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E38" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F38" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H38" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I38" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J38" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K38" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L38" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M38" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N38" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O38" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>26129.3</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3717,50 +3710,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C39" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D39" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E39" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H39" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I39" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J39" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K39" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L39" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M39" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N39" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O39" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3771,16 +3764,20 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3790,55 +3787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C40" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D40" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E40" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F40" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H40" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I40" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J40" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K40" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L40" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M40" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N40" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O40" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3846,23 +3847,23 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3872,59 +3873,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C41" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D41" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E41" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F41" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I41" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J41" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K41" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L41" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M41" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N41" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O41" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3934,18 +3931,16 @@
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3958,61 +3953,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C42" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D42" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E42" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F42" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I42" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J42" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K42" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L42" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M42" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N42" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O42" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4038,66 +4039,62 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C43" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D43" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E43" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F43" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I43" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J43" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K43" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L43" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M43" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N43" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O43" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -4107,7 +4104,7 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4129,57 +4126,57 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C44" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D44" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E44" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F44" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I44" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J44" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K44" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L44" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M44" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N44" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O44" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -4189,7 +4186,7 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4211,71 +4208,69 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C45" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D45" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E45" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F45" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H45" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I45" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J45" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K45" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L45" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M45" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N45" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O45" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4288,55 +4283,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C46" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D46" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E46" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F46" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H46" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I46" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J46" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K46" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L46" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M46" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N46" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O46" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4347,9 +4346,9 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4357,95 +4356,93 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C47" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D47" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E47" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F47" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I47" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J47" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K47" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L47" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M47" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N47" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O47" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="Q47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4454,67 +4451,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C48" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D48" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E48" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F48" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H48" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I48" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J48" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K48" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L48" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M48" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N48" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O48" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
@@ -4545,50 +4544,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C49" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D49" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E49" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F49" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H49" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I49" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J49" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K49" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L49" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M49" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N49" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O49" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4598,12 +4597,12 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4629,56 +4628,60 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C50" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D50" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E50" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F50" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H50" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I50" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J50" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K50" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L50" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M50" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N50" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O50" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4687,7 +4690,7 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4699,73 +4702,69 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C51" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D51" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E51" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F51" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H51" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I51" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J51" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K51" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L51" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M51" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N51" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O51" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4797,74 +4796,72 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C52" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D52" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E52" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F52" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H52" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I52" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J52" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K52" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L52" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M52" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N52" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O52" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4876,76 +4873,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C53" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D53" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E53" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F53" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H53" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I53" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J53" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K53" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L53" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M53" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N53" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O53" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4960,74 +4961,70 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C54" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D54" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E54" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F54" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H54" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I54" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J54" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K54" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L54" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M54" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N54" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O54" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5053,63 +5050,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C55" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D55" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E55" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F55" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H55" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I55" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J55" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K55" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L55" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M55" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N55" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O55" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>25005.07</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5126,143 +5129,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C56" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D56" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E56" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F56" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H56" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I56" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J56" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K56" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L56" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M56" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N56" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O56" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C57" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D57" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E57" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F57" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H57" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I57" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J57" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K57" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L57" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M57" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N57" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O57" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5280,75 +5281,73 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24748.45</v>
+        <v>25170.8</v>
       </c>
       <c r="C58" t="n">
-        <v>25042.71</v>
+        <v>25254.11</v>
       </c>
       <c r="D58" t="n">
-        <v>24736.92</v>
+        <v>25043.64</v>
       </c>
       <c r="E58" t="n">
-        <v>25042.71</v>
+        <v>25087.75</v>
       </c>
       <c r="F58" t="n">
-        <v>291.93</v>
+        <v>45.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0018</v>
       </c>
       <c r="H58" t="n">
-        <v>305.79</v>
+        <v>210.47</v>
       </c>
       <c r="I58" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J58" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K58" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L58" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M58" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N58" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O58" t="n">
-        <v>25022.04</v>
+        <v>25348.5</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5366,18 +5365,14 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5389,79 +5384,83 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25170.8</v>
+        <v>25064.84</v>
       </c>
       <c r="C59" t="n">
-        <v>25254.11</v>
+        <v>25072.25</v>
       </c>
       <c r="D59" t="n">
-        <v>25043.64</v>
+        <v>24811.85</v>
       </c>
       <c r="E59" t="n">
-        <v>25087.75</v>
+        <v>24834.12</v>
       </c>
       <c r="F59" t="n">
-        <v>45.04</v>
+        <v>-253.63</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0018</v>
+        <v>-0.0101</v>
       </c>
       <c r="H59" t="n">
-        <v>210.47</v>
+        <v>260.4</v>
       </c>
       <c r="I59" t="n">
-        <v>24431.13</v>
+        <v>24833.17</v>
       </c>
       <c r="J59" t="n">
-        <v>24813.37</v>
+        <v>24846.72</v>
       </c>
       <c r="K59" t="n">
-        <v>24889.82</v>
+        <v>24982.52</v>
       </c>
       <c r="L59" t="n">
-        <v>24966.26</v>
+        <v>25118.31</v>
       </c>
       <c r="M59" t="n">
-        <v>25195.61</v>
+        <v>25192.98</v>
       </c>
       <c r="N59" t="n">
-        <v>25424.95</v>
+        <v>25267.66</v>
       </c>
       <c r="O59" t="n">
-        <v>25348.5</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+        <v>25464.58</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W59" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5469,64 +5468,60 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25064.84</v>
+        <v>24649.45</v>
       </c>
       <c r="C60" t="n">
-        <v>25072.25</v>
+        <v>24791.2</v>
       </c>
       <c r="D60" t="n">
-        <v>24811.85</v>
+        <v>24648.29</v>
       </c>
       <c r="E60" t="n">
-        <v>24834.12</v>
+        <v>24761.13</v>
       </c>
       <c r="F60" t="n">
-        <v>-253.63</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0029</v>
       </c>
       <c r="H60" t="n">
-        <v>260.4</v>
+        <v>142.91</v>
       </c>
       <c r="I60" t="n">
-        <v>24833.17</v>
+        <v>24551.45</v>
       </c>
       <c r="J60" t="n">
-        <v>24846.72</v>
+        <v>24519.75</v>
       </c>
       <c r="K60" t="n">
-        <v>24982.52</v>
+        <v>24703.92</v>
       </c>
       <c r="L60" t="n">
-        <v>25118.31</v>
+        <v>24888.08</v>
       </c>
       <c r="M60" t="n">
-        <v>25192.98</v>
+        <v>24964.32</v>
       </c>
       <c r="N60" t="n">
-        <v>25267.66</v>
+        <v>25040.55</v>
       </c>
       <c r="O60" t="n">
-        <v>25464.58</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>25332.65</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
@@ -5553,60 +5548,64 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24649.45</v>
+        <v>24523.5</v>
       </c>
       <c r="C61" t="n">
-        <v>24791.2</v>
+        <v>24537.14</v>
       </c>
       <c r="D61" t="n">
-        <v>24648.29</v>
+        <v>24275.56</v>
       </c>
       <c r="E61" t="n">
-        <v>24761.13</v>
+        <v>24510.09</v>
       </c>
       <c r="F61" t="n">
-        <v>-72.98999999999999</v>
+        <v>-251.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H61" t="n">
-        <v>142.91</v>
+        <v>261.58</v>
       </c>
       <c r="I61" t="n">
-        <v>24551.45</v>
+        <v>24505.38</v>
       </c>
       <c r="J61" t="n">
-        <v>24519.75</v>
+        <v>24638.91</v>
       </c>
       <c r="K61" t="n">
-        <v>24703.92</v>
+        <v>24689.68</v>
       </c>
       <c r="L61" t="n">
-        <v>24888.08</v>
+        <v>24740.44</v>
       </c>
       <c r="M61" t="n">
-        <v>24964.32</v>
+        <v>24832.59</v>
       </c>
       <c r="N61" t="n">
-        <v>25040.55</v>
+        <v>24924.73</v>
       </c>
       <c r="O61" t="n">
-        <v>25332.65</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+        <v>24934.11</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
@@ -5633,74 +5632,70 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24523.5</v>
+        <v>24554.58</v>
       </c>
       <c r="C62" t="n">
-        <v>24537.14</v>
+        <v>24767.22</v>
       </c>
       <c r="D62" t="n">
-        <v>24275.56</v>
+        <v>24554.58</v>
       </c>
       <c r="E62" t="n">
-        <v>24510.09</v>
+        <v>24642.51</v>
       </c>
       <c r="F62" t="n">
-        <v>-251.04</v>
+        <v>132.42</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0054</v>
       </c>
       <c r="H62" t="n">
-        <v>261.58</v>
+        <v>212.64</v>
       </c>
       <c r="I62" t="n">
-        <v>24505.38</v>
+        <v>24013.98</v>
       </c>
       <c r="J62" t="n">
-        <v>24638.91</v>
+        <v>24300.38</v>
       </c>
       <c r="K62" t="n">
-        <v>24689.68</v>
+        <v>24379.3</v>
       </c>
       <c r="L62" t="n">
-        <v>24740.44</v>
+        <v>24458.22</v>
       </c>
       <c r="M62" t="n">
-        <v>24832.59</v>
+        <v>24640.88</v>
       </c>
       <c r="N62" t="n">
-        <v>24924.73</v>
+        <v>24823.54</v>
       </c>
       <c r="O62" t="n">
-        <v>24934.11</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+        <v>24798.72</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5712,55 +5707,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24554.58</v>
+        <v>24648.64</v>
       </c>
       <c r="C63" t="n">
-        <v>24767.22</v>
+        <v>24648.64</v>
       </c>
       <c r="D63" t="n">
-        <v>24554.58</v>
+        <v>24444.15</v>
       </c>
       <c r="E63" t="n">
-        <v>24642.51</v>
+        <v>24523.57</v>
       </c>
       <c r="F63" t="n">
-        <v>132.42</v>
+        <v>-118.94</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H63" t="n">
-        <v>212.64</v>
+        <v>204.49</v>
       </c>
       <c r="I63" t="n">
-        <v>24013.98</v>
+        <v>24341.94</v>
       </c>
       <c r="J63" t="n">
-        <v>24300.38</v>
+        <v>24420.67</v>
       </c>
       <c r="K63" t="n">
-        <v>24379.3</v>
+        <v>24536.19</v>
       </c>
       <c r="L63" t="n">
-        <v>24458.22</v>
+        <v>24651.71</v>
       </c>
       <c r="M63" t="n">
-        <v>24640.88</v>
+        <v>24748.83</v>
       </c>
       <c r="N63" t="n">
-        <v>24823.54</v>
+        <v>24845.96</v>
       </c>
       <c r="O63" t="n">
-        <v>24798.72</v>
+        <v>24979.86</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5768,19 +5767,19 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
@@ -5792,59 +5791,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>24648.64</v>
+        <v>24393.88</v>
       </c>
       <c r="C64" t="n">
-        <v>24648.64</v>
+        <v>24637.65</v>
       </c>
       <c r="D64" t="n">
-        <v>24444.15</v>
+        <v>24332.64</v>
       </c>
       <c r="E64" t="n">
-        <v>24523.57</v>
+        <v>24613.27</v>
       </c>
       <c r="F64" t="n">
-        <v>-118.94</v>
+        <v>89.7</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0037</v>
       </c>
       <c r="H64" t="n">
-        <v>204.49</v>
+        <v>305.01</v>
       </c>
       <c r="I64" t="n">
-        <v>24341.94</v>
+        <v>24239.66</v>
       </c>
       <c r="J64" t="n">
-        <v>24420.67</v>
+        <v>24307.67</v>
       </c>
       <c r="K64" t="n">
-        <v>24536.19</v>
+        <v>24421.33</v>
       </c>
       <c r="L64" t="n">
-        <v>24651.71</v>
+        <v>24534.98</v>
       </c>
       <c r="M64" t="n">
-        <v>24748.83</v>
+        <v>24625.82</v>
       </c>
       <c r="N64" t="n">
-        <v>24845.96</v>
+        <v>24716.65</v>
       </c>
       <c r="O64" t="n">
-        <v>24979.86</v>
+        <v>24853.13</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5854,17 +5849,19 @@
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
       <c r="U64" s="8" t="n">
         <v/>
       </c>
@@ -5876,91 +5873,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>24393.88</v>
-      </c>
-      <c r="C65" t="n">
-        <v>24637.65</v>
-      </c>
-      <c r="D65" t="n">
-        <v>24332.64</v>
-      </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v>305.01</v>
-      </c>
-      <c r="I65" t="n">
-        <v>24239.66</v>
-      </c>
-      <c r="J65" t="n">
-        <v>24307.67</v>
-      </c>
-      <c r="K65" t="n">
-        <v>24421.33</v>
-      </c>
-      <c r="L65" t="n">
-        <v>24534.98</v>
-      </c>
-      <c r="M65" t="n">
-        <v>24625.82</v>
-      </c>
-      <c r="N65" t="n">
-        <v>24716.65</v>
-      </c>
-      <c r="O65" t="n">
-        <v>24853.13</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23404.61</v>
+        <v>23568.49</v>
       </c>
       <c r="C2" t="n">
-        <v>23686.56</v>
+        <v>23820.92</v>
       </c>
       <c r="D2" t="n">
-        <v>23229.38</v>
+        <v>23398.27</v>
       </c>
       <c r="E2" t="n">
-        <v>23616.32</v>
+        <v>23496.89</v>
       </c>
       <c r="F2" t="n">
-        <v>266.29</v>
+        <v>-119.43</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0051</v>
       </c>
       <c r="H2" t="n">
-        <v>457.18</v>
+        <v>422.65</v>
       </c>
       <c r="I2" t="n">
-        <v>22935.7</v>
+        <v>22772.2</v>
       </c>
       <c r="J2" t="n">
-        <v>23048.82</v>
+        <v>23238.32</v>
       </c>
       <c r="K2" t="n">
-        <v>23204.78</v>
+        <v>23387.73</v>
       </c>
       <c r="L2" t="n">
-        <v>23360.74</v>
+        <v>23537.15</v>
       </c>
       <c r="M2" t="n">
-        <v>23495.28</v>
+        <v>23844.91</v>
       </c>
       <c r="N2" t="n">
-        <v>23629.82</v>
+        <v>24152.67</v>
       </c>
       <c r="O2" t="n">
-        <v>23807.2</v>
+        <v>24143.74</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,18 +690,14 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -711,55 +707,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C3" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D3" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E3" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F3" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H3" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I3" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J3" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K3" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L3" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M3" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N3" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O3" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,76 +772,78 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C4" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D4" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E4" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F4" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H4" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I4" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J4" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K4" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L4" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M4" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N4" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O4" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,78 +856,76 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C5" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D5" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E5" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F5" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H5" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I5" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J5" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K5" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L5" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M5" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N5" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O5" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,14 +938,18 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -955,59 +959,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C6" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D6" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E6" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F6" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H6" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I6" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J6" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K6" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L6" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M6" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N6" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O6" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,18 +1020,16 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1041,55 +1039,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C7" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D7" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E7" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F7" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H7" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I7" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J7" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K7" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L7" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M7" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N7" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O7" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,17 +1099,19 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1123,57 +1127,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C8" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D8" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E8" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F8" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H8" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I8" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J8" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K8" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L8" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M8" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N8" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O8" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1181,12 +1185,10 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1207,59 +1209,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C9" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D9" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E9" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F9" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H9" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I9" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J9" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K9" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L9" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M9" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N9" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O9" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,21 +1268,25 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1296,83 +1298,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C10" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D10" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E10" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F10" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H10" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I10" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J10" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K10" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L10" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M10" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N10" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O10" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>25617.86</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1380,77 +1382,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C11" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D11" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E11" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F11" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H11" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I11" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J11" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K11" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L11" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M11" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N11" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O11" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1459,55 +1459,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C12" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D12" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E12" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F12" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H12" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I12" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J12" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K12" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L12" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M12" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N12" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O12" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,20 +1522,16 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1550,63 +1550,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C13" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D13" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E13" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H13" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I13" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J13" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K13" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L13" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M13" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N13" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O13" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1623,90 +1627,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C14" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D14" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E14" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F14" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H14" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I14" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J14" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K14" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L14" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M14" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N14" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O14" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1714,220 +1716,220 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C15" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D15" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E15" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F15" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H15" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I15" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J15" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K15" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L15" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M15" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N15" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O15" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C16" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D16" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E16" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F16" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H16" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I16" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J16" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K16" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L16" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M16" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N16" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O16" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C17" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D17" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E17" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F17" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H17" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I17" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J17" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K17" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L17" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M17" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N17" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O17" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,25 +1940,21 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1968,50 +1966,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C18" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D18" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E18" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F18" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H18" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I18" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J18" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K18" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L18" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M18" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N18" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O18" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,21 +2020,25 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2048,50 +2050,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C19" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D19" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E19" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F19" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H19" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I19" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J19" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K19" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L19" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M19" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N19" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O19" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,25 +2104,21 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2132,50 +2130,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C20" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D20" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E20" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F20" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I20" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J20" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K20" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L20" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M20" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N20" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O20" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2183,18 +2181,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2207,55 +2205,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C21" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D21" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E21" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F21" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H21" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I21" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J21" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K21" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L21" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M21" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N21" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O21" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2263,18 +2265,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2287,59 +2289,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C22" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D22" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E22" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F22" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H22" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I22" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J22" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K22" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L22" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M22" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N22" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O22" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2347,17 +2345,19 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2371,55 +2371,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C23" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D23" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E23" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F23" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H23" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I23" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J23" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K23" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L23" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M23" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N23" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O23" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2427,20 +2431,16 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2462,63 +2462,69 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C24" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D24" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E24" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F24" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H24" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I24" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J24" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K24" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L24" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M24" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N24" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O24" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>26218.02</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2530,88 +2536,80 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C25" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D25" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E25" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F25" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H25" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I25" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J25" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K25" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L25" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M25" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N25" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O25" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2623,55 +2621,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C26" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D26" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E26" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F26" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H26" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I26" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J26" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K26" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L26" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M26" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N26" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O26" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2682,21 +2684,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
@@ -2712,63 +2716,67 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C27" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D27" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E27" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F27" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H27" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I27" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J27" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K27" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L27" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M27" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N27" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O27" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2779,10 +2787,8 @@
       <c r="U27" s="8" t="n">
         <v/>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
@@ -2791,80 +2797,76 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C28" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D28" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E28" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F28" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H28" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I28" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J28" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K28" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L28" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M28" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N28" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O28" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2877,59 +2879,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C29" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D29" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E29" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F29" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H29" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I29" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J29" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K29" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L29" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M29" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N29" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O29" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,12 +2937,12 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2961,70 +2959,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C30" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D30" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E30" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F30" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H30" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I30" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J30" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K30" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L30" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M30" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N30" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O30" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3041,90 +3045,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C31" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D31" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E31" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F31" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H31" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I31" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J31" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K31" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L31" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M31" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N31" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O31" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3132,50 +3134,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C32" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D32" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E32" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F32" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H32" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I32" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J32" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K32" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L32" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M32" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N32" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O32" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3183,83 +3185,83 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C33" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D33" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E33" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F33" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H33" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I33" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J33" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K33" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L33" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M33" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N33" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O33" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3272,7 +3274,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3291,59 +3293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C34" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D34" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E34" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F34" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H34" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I34" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J34" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K34" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L34" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M34" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N34" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O34" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3351,24 +3349,28 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3380,50 +3382,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C35" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D35" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E35" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F35" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H35" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I35" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J35" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K35" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L35" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M35" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N35" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O35" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3434,7 +3436,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3446,12 +3448,12 @@
       </c>
       <c r="U35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
@@ -3464,83 +3466,83 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C36" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D36" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E36" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F36" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H36" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I36" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J36" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K36" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L36" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M36" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N36" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O36" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>26211.31</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3548,69 +3550,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C37" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D37" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E37" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F37" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H37" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I37" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J37" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K37" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L37" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M37" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N37" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O37" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26129.3</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3632,50 +3628,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C38" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D38" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E38" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F38" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H38" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I38" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J38" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K38" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L38" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M38" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N38" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O38" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3688,14 +3684,18 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3705,55 +3705,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C39" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D39" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E39" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F39" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H39" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I39" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J39" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K39" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L39" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M39" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N39" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O39" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3761,23 +3765,23 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3787,59 +3791,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C40" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D40" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E40" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F40" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I40" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J40" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K40" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L40" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M40" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N40" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O40" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3849,18 +3849,16 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3873,68 +3871,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C41" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D41" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E41" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F41" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I41" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J41" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K41" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L41" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M41" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N41" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O41" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3953,66 +3957,62 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C42" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D42" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E42" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F42" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I42" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J42" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K42" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L42" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M42" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N42" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O42" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -4020,9 +4020,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4044,57 +4044,57 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C43" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D43" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E43" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F43" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I43" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J43" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K43" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L43" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M43" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N43" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O43" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -4102,9 +4102,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4126,71 +4126,69 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C44" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D44" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E44" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F44" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H44" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I44" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J44" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K44" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L44" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M44" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N44" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O44" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4203,55 +4201,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C45" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D45" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E45" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F45" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H45" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I45" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J45" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K45" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L45" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M45" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N45" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O45" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4264,7 +4266,7 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4272,94 +4274,92 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C46" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D46" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E46" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F46" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I46" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J46" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K46" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L46" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M46" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N46" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O46" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4369,70 +4369,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C47" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D47" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E47" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F47" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H47" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I47" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J47" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K47" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L47" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M47" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N47" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O47" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4460,50 +4462,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C48" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D48" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E48" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F48" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H48" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I48" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J48" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K48" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L48" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M48" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N48" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O48" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4513,12 +4515,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4544,65 +4546,69 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C49" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D49" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E49" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F49" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H49" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I49" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J49" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K49" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L49" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M49" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N49" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O49" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4614,81 +4620,77 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C50" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D50" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E50" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F50" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H50" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I50" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J50" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K50" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L50" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M50" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N50" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O50" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4712,74 +4714,72 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C51" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D51" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E51" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F51" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H51" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I51" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J51" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K51" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L51" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M51" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N51" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O51" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4791,61 +4791,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24701.18</v>
+        <v>24934.06</v>
       </c>
       <c r="C52" t="n">
-        <v>24926.24</v>
+        <v>24934.06</v>
       </c>
       <c r="D52" t="n">
-        <v>24662.11</v>
+        <v>24657.01</v>
       </c>
       <c r="E52" t="n">
-        <v>24917.6</v>
+        <v>24667.24</v>
       </c>
       <c r="F52" t="n">
-        <v>111.97</v>
+        <v>-250.36</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.01</v>
       </c>
       <c r="H52" t="n">
-        <v>264.13</v>
+        <v>277.05</v>
       </c>
       <c r="I52" t="n">
-        <v>24289.3</v>
+        <v>24397.98</v>
       </c>
       <c r="J52" t="n">
-        <v>24572.15</v>
+        <v>24715.18</v>
       </c>
       <c r="K52" t="n">
-        <v>24665.16</v>
+        <v>24785.53</v>
       </c>
       <c r="L52" t="n">
-        <v>24758.17</v>
+        <v>24855.89</v>
       </c>
       <c r="M52" t="n">
-        <v>24946.1</v>
+        <v>25049.67</v>
       </c>
       <c r="N52" t="n">
-        <v>25134.03</v>
+        <v>25243.44</v>
       </c>
       <c r="O52" t="n">
-        <v>25132.12</v>
+        <v>25190.37</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4854,13 +4860,11 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4875,74 +4879,70 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="C53" t="n">
-        <v>24934.06</v>
+        <v>24789.91</v>
       </c>
       <c r="D53" t="n">
-        <v>24657.01</v>
+        <v>24574.75</v>
       </c>
       <c r="E53" t="n">
-        <v>24667.24</v>
+        <v>24713.78</v>
       </c>
       <c r="F53" t="n">
-        <v>-250.36</v>
+        <v>46.54</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.01</v>
+        <v>0.0019</v>
       </c>
       <c r="H53" t="n">
-        <v>277.05</v>
+        <v>215.16</v>
       </c>
       <c r="I53" t="n">
-        <v>24397.98</v>
+        <v>24379.96</v>
       </c>
       <c r="J53" t="n">
-        <v>24715.18</v>
+        <v>24326.04</v>
       </c>
       <c r="K53" t="n">
-        <v>24785.53</v>
+        <v>24528.71</v>
       </c>
       <c r="L53" t="n">
-        <v>24855.89</v>
+        <v>24731.39</v>
       </c>
       <c r="M53" t="n">
-        <v>25049.67</v>
+        <v>24805.77</v>
       </c>
       <c r="N53" t="n">
-        <v>25243.44</v>
+        <v>24880.14</v>
       </c>
       <c r="O53" t="n">
-        <v>25190.37</v>
+        <v>25211.11</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4968,63 +4968,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24789.91</v>
+        <v>24480.57</v>
       </c>
       <c r="C54" t="n">
-        <v>24789.91</v>
+        <v>24606.15</v>
       </c>
       <c r="D54" t="n">
-        <v>24574.75</v>
+        <v>24357.69</v>
       </c>
       <c r="E54" t="n">
-        <v>24713.78</v>
+        <v>24604.29</v>
       </c>
       <c r="F54" t="n">
-        <v>46.54</v>
+        <v>-109.49</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0044</v>
       </c>
       <c r="H54" t="n">
-        <v>215.16</v>
+        <v>248.46</v>
       </c>
       <c r="I54" t="n">
-        <v>24379.96</v>
+        <v>24359.59</v>
       </c>
       <c r="J54" t="n">
-        <v>24326.04</v>
+        <v>24514.34</v>
       </c>
       <c r="K54" t="n">
-        <v>24528.71</v>
+        <v>24606.2</v>
       </c>
       <c r="L54" t="n">
-        <v>24731.39</v>
+        <v>24698.05</v>
       </c>
       <c r="M54" t="n">
-        <v>24805.77</v>
+        <v>24821.36</v>
       </c>
       <c r="N54" t="n">
-        <v>24880.14</v>
+        <v>24944.66</v>
       </c>
       <c r="O54" t="n">
-        <v>25211.11</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>25005.07</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5041,143 +5047,141 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24480.57</v>
+        <v>24723.85</v>
       </c>
       <c r="C55" t="n">
-        <v>24606.15</v>
+        <v>24862.98</v>
       </c>
       <c r="D55" t="n">
-        <v>24357.69</v>
+        <v>24703.92</v>
       </c>
       <c r="E55" t="n">
-        <v>24604.29</v>
+        <v>24750.78</v>
       </c>
       <c r="F55" t="n">
-        <v>-109.49</v>
+        <v>146.49</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.006</v>
       </c>
       <c r="H55" t="n">
-        <v>248.46</v>
+        <v>159.06</v>
       </c>
       <c r="I55" t="n">
-        <v>24359.59</v>
+        <v>24109.23</v>
       </c>
       <c r="J55" t="n">
-        <v>24514.34</v>
+        <v>24417.01</v>
       </c>
       <c r="K55" t="n">
-        <v>24606.2</v>
+        <v>24480.06</v>
       </c>
       <c r="L55" t="n">
-        <v>24698.05</v>
+        <v>24543.1</v>
       </c>
       <c r="M55" t="n">
-        <v>24821.36</v>
+        <v>24728.52</v>
       </c>
       <c r="N55" t="n">
-        <v>24944.66</v>
+        <v>24913.93</v>
       </c>
       <c r="O55" t="n">
-        <v>25005.07</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
+        <v>24854.61</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>24723.85</v>
+        <v>24748.45</v>
       </c>
       <c r="C56" t="n">
-        <v>24862.98</v>
+        <v>25042.71</v>
       </c>
       <c r="D56" t="n">
-        <v>24703.92</v>
+        <v>24736.92</v>
       </c>
       <c r="E56" t="n">
-        <v>24750.78</v>
+        <v>25042.71</v>
       </c>
       <c r="F56" t="n">
-        <v>146.49</v>
+        <v>291.93</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="H56" t="n">
-        <v>159.06</v>
+        <v>305.79</v>
       </c>
       <c r="I56" t="n">
-        <v>24109.23</v>
+        <v>24544.86</v>
       </c>
       <c r="J56" t="n">
-        <v>24417.01</v>
+        <v>24575.38</v>
       </c>
       <c r="K56" t="n">
-        <v>24480.06</v>
+        <v>24671.25</v>
       </c>
       <c r="L56" t="n">
-        <v>24543.1</v>
+        <v>24767.11</v>
       </c>
       <c r="M56" t="n">
-        <v>24728.52</v>
+        <v>24830.31</v>
       </c>
       <c r="N56" t="n">
-        <v>24913.93</v>
+        <v>24893.5</v>
       </c>
       <c r="O56" t="n">
-        <v>24854.61</v>
+        <v>25022.04</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5188,82 +5192,80 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24748.45</v>
+        <v>25170.8</v>
       </c>
       <c r="C57" t="n">
-        <v>25042.71</v>
+        <v>25254.11</v>
       </c>
       <c r="D57" t="n">
-        <v>24736.92</v>
+        <v>25043.64</v>
       </c>
       <c r="E57" t="n">
-        <v>25042.71</v>
+        <v>25087.75</v>
       </c>
       <c r="F57" t="n">
-        <v>291.93</v>
+        <v>45.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0018</v>
       </c>
       <c r="H57" t="n">
-        <v>305.79</v>
+        <v>210.47</v>
       </c>
       <c r="I57" t="n">
-        <v>24544.86</v>
+        <v>24431.13</v>
       </c>
       <c r="J57" t="n">
-        <v>24575.38</v>
+        <v>24813.37</v>
       </c>
       <c r="K57" t="n">
-        <v>24671.25</v>
+        <v>24889.82</v>
       </c>
       <c r="L57" t="n">
-        <v>24767.11</v>
+        <v>24966.26</v>
       </c>
       <c r="M57" t="n">
-        <v>24830.31</v>
+        <v>25195.61</v>
       </c>
       <c r="N57" t="n">
-        <v>24893.5</v>
+        <v>25424.95</v>
       </c>
       <c r="O57" t="n">
-        <v>25022.04</v>
+        <v>25348.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5274,25 +5276,21 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5304,69 +5302,73 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25170.8</v>
+        <v>25064.84</v>
       </c>
       <c r="C58" t="n">
-        <v>25254.11</v>
+        <v>25072.25</v>
       </c>
       <c r="D58" t="n">
-        <v>25043.64</v>
+        <v>24811.85</v>
       </c>
       <c r="E58" t="n">
-        <v>25087.75</v>
+        <v>24834.12</v>
       </c>
       <c r="F58" t="n">
-        <v>45.04</v>
+        <v>-253.63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0018</v>
+        <v>-0.0101</v>
       </c>
       <c r="H58" t="n">
-        <v>210.47</v>
+        <v>260.4</v>
       </c>
       <c r="I58" t="n">
-        <v>24431.13</v>
+        <v>24833.17</v>
       </c>
       <c r="J58" t="n">
-        <v>24813.37</v>
+        <v>24846.72</v>
       </c>
       <c r="K58" t="n">
-        <v>24889.82</v>
+        <v>24982.52</v>
       </c>
       <c r="L58" t="n">
-        <v>24966.26</v>
+        <v>25118.31</v>
       </c>
       <c r="M58" t="n">
-        <v>25195.61</v>
+        <v>25192.98</v>
       </c>
       <c r="N58" t="n">
-        <v>25424.95</v>
+        <v>25267.66</v>
       </c>
       <c r="O58" t="n">
-        <v>25348.5</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+        <v>25464.58</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5374,9 +5376,9 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -5384,67 +5386,63 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25064.84</v>
+        <v>24649.45</v>
       </c>
       <c r="C59" t="n">
-        <v>25072.25</v>
+        <v>24791.2</v>
       </c>
       <c r="D59" t="n">
-        <v>24811.85</v>
+        <v>24648.29</v>
       </c>
       <c r="E59" t="n">
-        <v>24834.12</v>
+        <v>24761.13</v>
       </c>
       <c r="F59" t="n">
-        <v>-253.63</v>
+        <v>-72.98999999999999</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0101</v>
+        <v>-0.0029</v>
       </c>
       <c r="H59" t="n">
-        <v>260.4</v>
+        <v>142.91</v>
       </c>
       <c r="I59" t="n">
-        <v>24833.17</v>
+        <v>24551.45</v>
       </c>
       <c r="J59" t="n">
-        <v>24846.72</v>
+        <v>24519.75</v>
       </c>
       <c r="K59" t="n">
-        <v>24982.52</v>
+        <v>24703.92</v>
       </c>
       <c r="L59" t="n">
-        <v>25118.31</v>
+        <v>24888.08</v>
       </c>
       <c r="M59" t="n">
-        <v>25192.98</v>
+        <v>24964.32</v>
       </c>
       <c r="N59" t="n">
-        <v>25267.66</v>
+        <v>25040.55</v>
       </c>
       <c r="O59" t="n">
-        <v>25464.58</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>25332.65</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5468,63 +5466,67 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24649.45</v>
+        <v>24523.5</v>
       </c>
       <c r="C60" t="n">
-        <v>24791.2</v>
+        <v>24537.14</v>
       </c>
       <c r="D60" t="n">
-        <v>24648.29</v>
+        <v>24275.56</v>
       </c>
       <c r="E60" t="n">
-        <v>24761.13</v>
+        <v>24510.09</v>
       </c>
       <c r="F60" t="n">
-        <v>-72.98999999999999</v>
+        <v>-251.04</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0101</v>
       </c>
       <c r="H60" t="n">
-        <v>142.91</v>
+        <v>261.58</v>
       </c>
       <c r="I60" t="n">
-        <v>24551.45</v>
+        <v>24505.38</v>
       </c>
       <c r="J60" t="n">
-        <v>24519.75</v>
+        <v>24638.91</v>
       </c>
       <c r="K60" t="n">
-        <v>24703.92</v>
+        <v>24689.68</v>
       </c>
       <c r="L60" t="n">
-        <v>24888.08</v>
+        <v>24740.44</v>
       </c>
       <c r="M60" t="n">
-        <v>24964.32</v>
+        <v>24832.59</v>
       </c>
       <c r="N60" t="n">
-        <v>25040.55</v>
+        <v>24924.73</v>
       </c>
       <c r="O60" t="n">
-        <v>25332.65</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>24934.11</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5548,74 +5550,70 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24523.5</v>
+        <v>24554.58</v>
       </c>
       <c r="C61" t="n">
-        <v>24537.14</v>
+        <v>24767.22</v>
       </c>
       <c r="D61" t="n">
-        <v>24275.56</v>
+        <v>24554.58</v>
       </c>
       <c r="E61" t="n">
-        <v>24510.09</v>
+        <v>24642.51</v>
       </c>
       <c r="F61" t="n">
-        <v>-251.04</v>
+        <v>132.42</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0054</v>
       </c>
       <c r="H61" t="n">
-        <v>261.58</v>
+        <v>212.64</v>
       </c>
       <c r="I61" t="n">
-        <v>24505.38</v>
+        <v>24013.98</v>
       </c>
       <c r="J61" t="n">
-        <v>24638.91</v>
+        <v>24300.38</v>
       </c>
       <c r="K61" t="n">
-        <v>24689.68</v>
+        <v>24379.3</v>
       </c>
       <c r="L61" t="n">
-        <v>24740.44</v>
+        <v>24458.22</v>
       </c>
       <c r="M61" t="n">
-        <v>24832.59</v>
+        <v>24640.88</v>
       </c>
       <c r="N61" t="n">
-        <v>24924.73</v>
+        <v>24823.54</v>
       </c>
       <c r="O61" t="n">
-        <v>24934.11</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>24798.72</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5627,55 +5625,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24554.58</v>
+        <v>24648.64</v>
       </c>
       <c r="C62" t="n">
-        <v>24767.22</v>
+        <v>24648.64</v>
       </c>
       <c r="D62" t="n">
-        <v>24554.58</v>
+        <v>24444.15</v>
       </c>
       <c r="E62" t="n">
-        <v>24642.51</v>
+        <v>24523.57</v>
       </c>
       <c r="F62" t="n">
-        <v>132.42</v>
+        <v>-118.94</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0048</v>
       </c>
       <c r="H62" t="n">
-        <v>212.64</v>
+        <v>204.49</v>
       </c>
       <c r="I62" t="n">
-        <v>24013.98</v>
+        <v>24341.94</v>
       </c>
       <c r="J62" t="n">
-        <v>24300.38</v>
+        <v>24420.67</v>
       </c>
       <c r="K62" t="n">
-        <v>24379.3</v>
+        <v>24536.19</v>
       </c>
       <c r="L62" t="n">
-        <v>24458.22</v>
+        <v>24651.71</v>
       </c>
       <c r="M62" t="n">
-        <v>24640.88</v>
+        <v>24748.83</v>
       </c>
       <c r="N62" t="n">
-        <v>24823.54</v>
+        <v>24845.96</v>
       </c>
       <c r="O62" t="n">
-        <v>24798.72</v>
+        <v>24979.86</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5683,18 +5685,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5707,59 +5709,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24648.64</v>
+        <v>24393.88</v>
       </c>
       <c r="C63" t="n">
-        <v>24648.64</v>
+        <v>24637.65</v>
       </c>
       <c r="D63" t="n">
-        <v>24444.15</v>
+        <v>24332.64</v>
       </c>
       <c r="E63" t="n">
-        <v>24523.57</v>
+        <v>24613.27</v>
       </c>
       <c r="F63" t="n">
-        <v>-118.94</v>
+        <v>89.7</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0048</v>
+        <v>0.0037</v>
       </c>
       <c r="H63" t="n">
-        <v>204.49</v>
+        <v>305.01</v>
       </c>
       <c r="I63" t="n">
-        <v>24341.94</v>
+        <v>24239.66</v>
       </c>
       <c r="J63" t="n">
-        <v>24420.67</v>
+        <v>24307.67</v>
       </c>
       <c r="K63" t="n">
-        <v>24536.19</v>
+        <v>24421.33</v>
       </c>
       <c r="L63" t="n">
-        <v>24651.71</v>
+        <v>24534.98</v>
       </c>
       <c r="M63" t="n">
-        <v>24748.83</v>
+        <v>24625.82</v>
       </c>
       <c r="N63" t="n">
-        <v>24845.96</v>
+        <v>24716.65</v>
       </c>
       <c r="O63" t="n">
-        <v>24979.86</v>
+        <v>24853.13</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5769,17 +5767,19 @@
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
@@ -5791,61 +5791,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>24393.88</v>
+        <v>24099.73</v>
       </c>
       <c r="C64" t="n">
-        <v>24637.65</v>
+        <v>24099.73</v>
       </c>
       <c r="D64" t="n">
-        <v>24332.64</v>
+        <v>23865.33</v>
       </c>
       <c r="E64" t="n">
-        <v>24613.27</v>
+        <v>23972.29</v>
       </c>
       <c r="F64" t="n">
-        <v>89.7</v>
+        <v>-640.98</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.026</v>
       </c>
       <c r="H64" t="n">
-        <v>305.01</v>
+        <v>234.4</v>
       </c>
       <c r="I64" t="n">
-        <v>24239.66</v>
+        <v>24027.63</v>
       </c>
       <c r="J64" t="n">
-        <v>24307.67</v>
+        <v>24372.32</v>
       </c>
       <c r="K64" t="n">
-        <v>24421.33</v>
+        <v>24460.76</v>
       </c>
       <c r="L64" t="n">
-        <v>24534.98</v>
+        <v>24549.21</v>
       </c>
       <c r="M64" t="n">
-        <v>24625.82</v>
+        <v>24765.77</v>
       </c>
       <c r="N64" t="n">
-        <v>24716.65</v>
+        <v>24982.34</v>
       </c>
       <c r="O64" t="n">
-        <v>24853.13</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
+        <v>24942.66</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
@@ -5854,13 +5862,11 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5873,11 +5879,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/HSI_daily.xlsx
+++ b/three_gate/analysis/HSI_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,17 +104,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23568.49</v>
+        <v>23541.22</v>
       </c>
       <c r="C2" t="n">
-        <v>23820.92</v>
+        <v>24310.92</v>
       </c>
       <c r="D2" t="n">
-        <v>23398.27</v>
+        <v>23541.22</v>
       </c>
       <c r="E2" t="n">
-        <v>23496.89</v>
+        <v>24199.46</v>
       </c>
       <c r="F2" t="n">
-        <v>-119.43</v>
+        <v>702.5700000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0299</v>
       </c>
       <c r="H2" t="n">
-        <v>422.65</v>
+        <v>769.7</v>
       </c>
       <c r="I2" t="n">
-        <v>22772.2</v>
+        <v>22975.62</v>
       </c>
       <c r="J2" t="n">
-        <v>23238.32</v>
+        <v>23017.89</v>
       </c>
       <c r="K2" t="n">
-        <v>23387.73</v>
+        <v>23285.57</v>
       </c>
       <c r="L2" t="n">
-        <v>23537.15</v>
+        <v>23553.24</v>
       </c>
       <c r="M2" t="n">
-        <v>23844.91</v>
+        <v>23708.22</v>
       </c>
       <c r="N2" t="n">
-        <v>24152.67</v>
+        <v>23863.19</v>
       </c>
       <c r="O2" t="n">
-        <v>24143.74</v>
+        <v>24243.57</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,76 +693,78 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23541.22</v>
+        <v>24181.34</v>
       </c>
       <c r="C3" t="n">
-        <v>24310.92</v>
+        <v>24353.76</v>
       </c>
       <c r="D3" t="n">
-        <v>23541.22</v>
+        <v>23917.32</v>
       </c>
       <c r="E3" t="n">
-        <v>24199.46</v>
+        <v>24030.18</v>
       </c>
       <c r="F3" t="n">
-        <v>702.5700000000001</v>
+        <v>-169.28</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0299</v>
+        <v>-0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>769.7</v>
+        <v>436.44</v>
       </c>
       <c r="I3" t="n">
-        <v>22975.62</v>
+        <v>22771.52</v>
       </c>
       <c r="J3" t="n">
-        <v>23017.89</v>
+        <v>23566.46</v>
       </c>
       <c r="K3" t="n">
-        <v>23285.57</v>
+        <v>23814.61</v>
       </c>
       <c r="L3" t="n">
-        <v>23553.24</v>
+        <v>24062.77</v>
       </c>
       <c r="M3" t="n">
-        <v>23708.22</v>
+        <v>24584.31</v>
       </c>
       <c r="N3" t="n">
-        <v>23863.19</v>
+        <v>25105.86</v>
       </c>
       <c r="O3" t="n">
-        <v>24243.57</v>
+        <v>25080.62</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,78 +777,76 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24181.34</v>
+        <v>24213.44</v>
       </c>
       <c r="C4" t="n">
-        <v>24353.76</v>
+        <v>24499.63</v>
       </c>
       <c r="D4" t="n">
-        <v>23917.32</v>
+        <v>24064.62</v>
       </c>
       <c r="E4" t="n">
-        <v>24030.18</v>
+        <v>24175.12</v>
       </c>
       <c r="F4" t="n">
-        <v>-169.28</v>
+        <v>144.94</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H4" t="n">
-        <v>436.44</v>
+        <v>435.01</v>
       </c>
       <c r="I4" t="n">
-        <v>22771.52</v>
+        <v>23480.88</v>
       </c>
       <c r="J4" t="n">
-        <v>23566.46</v>
+        <v>23541.06</v>
       </c>
       <c r="K4" t="n">
-        <v>23814.61</v>
+        <v>23811.96</v>
       </c>
       <c r="L4" t="n">
-        <v>24062.77</v>
+        <v>24082.86</v>
       </c>
       <c r="M4" t="n">
-        <v>24584.31</v>
+        <v>24248.4</v>
       </c>
       <c r="N4" t="n">
-        <v>25105.86</v>
+        <v>24413.94</v>
       </c>
       <c r="O4" t="n">
-        <v>25080.62</v>
+        <v>24790.2</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -856,14 +859,18 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -873,59 +880,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24213.44</v>
+        <v>24157.65</v>
       </c>
       <c r="C5" t="n">
-        <v>24499.63</v>
+        <v>24449.77</v>
       </c>
       <c r="D5" t="n">
-        <v>24064.62</v>
+        <v>24095.73</v>
       </c>
       <c r="E5" t="n">
-        <v>24175.12</v>
+        <v>24213.72</v>
       </c>
       <c r="F5" t="n">
-        <v>144.94</v>
+        <v>38.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0016</v>
       </c>
       <c r="H5" t="n">
-        <v>435.01</v>
+        <v>354.04</v>
       </c>
       <c r="I5" t="n">
-        <v>23480.88</v>
+        <v>23629.61</v>
       </c>
       <c r="J5" t="n">
-        <v>23541.06</v>
+        <v>23686.6</v>
       </c>
       <c r="K5" t="n">
-        <v>23811.96</v>
+        <v>23957.61</v>
       </c>
       <c r="L5" t="n">
-        <v>24082.86</v>
+        <v>24228.62</v>
       </c>
       <c r="M5" t="n">
-        <v>24248.4</v>
+        <v>24392.62</v>
       </c>
       <c r="N5" t="n">
-        <v>24413.94</v>
+        <v>24556.63</v>
       </c>
       <c r="O5" t="n">
-        <v>24790.2</v>
+        <v>24934.64</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,18 +941,16 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -959,55 +960,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24157.65</v>
+        <v>24181.52</v>
       </c>
       <c r="C6" t="n">
-        <v>24449.77</v>
+        <v>24436.58</v>
       </c>
       <c r="D6" t="n">
-        <v>24095.73</v>
+        <v>23902.05</v>
       </c>
       <c r="E6" t="n">
-        <v>24213.72</v>
+        <v>24340.73</v>
       </c>
       <c r="F6" t="n">
-        <v>38.6</v>
+        <v>127.01</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
       <c r="H6" t="n">
-        <v>354.04</v>
+        <v>534.53</v>
       </c>
       <c r="I6" t="n">
-        <v>23629.61</v>
+        <v>23741.69</v>
       </c>
       <c r="J6" t="n">
-        <v>23686.6</v>
+        <v>23830.17</v>
       </c>
       <c r="K6" t="n">
-        <v>23957.61</v>
+        <v>24036.7</v>
       </c>
       <c r="L6" t="n">
-        <v>24228.62</v>
+        <v>24243.24</v>
       </c>
       <c r="M6" t="n">
-        <v>24392.62</v>
+        <v>24390.74</v>
       </c>
       <c r="N6" t="n">
-        <v>24556.63</v>
+        <v>24538.25</v>
       </c>
       <c r="O6" t="n">
-        <v>24934.64</v>
+        <v>24803.81</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,17 +1020,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1041,57 +1048,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24181.52</v>
+        <v>24551.34</v>
       </c>
       <c r="C7" t="n">
-        <v>24436.58</v>
+        <v>24774.84</v>
       </c>
       <c r="D7" t="n">
-        <v>23902.05</v>
+        <v>24449.53</v>
       </c>
       <c r="E7" t="n">
-        <v>24340.73</v>
+        <v>24681.1</v>
       </c>
       <c r="F7" t="n">
-        <v>127.01</v>
+        <v>340.37</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.014</v>
       </c>
       <c r="H7" t="n">
-        <v>534.53</v>
+        <v>325.31</v>
       </c>
       <c r="I7" t="n">
-        <v>23741.69</v>
+        <v>23367.52</v>
       </c>
       <c r="J7" t="n">
-        <v>23830.17</v>
+        <v>23891.91</v>
       </c>
       <c r="K7" t="n">
-        <v>24036.7</v>
+        <v>24073.47</v>
       </c>
       <c r="L7" t="n">
-        <v>24243.24</v>
+        <v>24255.02</v>
       </c>
       <c r="M7" t="n">
-        <v>24390.74</v>
+        <v>24608</v>
       </c>
       <c r="N7" t="n">
-        <v>24538.25</v>
+        <v>24960.97</v>
       </c>
       <c r="O7" t="n">
-        <v>24803.81</v>
+        <v>24971.11</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,12 +1106,10 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1125,59 +1130,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24551.34</v>
+        <v>24825.02</v>
       </c>
       <c r="C8" t="n">
-        <v>24774.84</v>
+        <v>25221.44</v>
       </c>
       <c r="D8" t="n">
-        <v>24449.53</v>
+        <v>24825.02</v>
       </c>
       <c r="E8" t="n">
-        <v>24681.1</v>
+        <v>25008.6</v>
       </c>
       <c r="F8" t="n">
-        <v>340.37</v>
+        <v>327.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="H8" t="n">
-        <v>325.31</v>
+        <v>396.42</v>
       </c>
       <c r="I8" t="n">
-        <v>23367.52</v>
+        <v>24124.22</v>
       </c>
       <c r="J8" t="n">
-        <v>23891.91</v>
+        <v>24390.25</v>
       </c>
       <c r="K8" t="n">
-        <v>24073.47</v>
+        <v>24518.44</v>
       </c>
       <c r="L8" t="n">
-        <v>24255.02</v>
+        <v>24646.64</v>
       </c>
       <c r="M8" t="n">
-        <v>24608</v>
+        <v>24843.75</v>
       </c>
       <c r="N8" t="n">
-        <v>24960.97</v>
+        <v>25040.87</v>
       </c>
       <c r="O8" t="n">
-        <v>24971.11</v>
+        <v>25100.15</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,21 +1189,25 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1214,83 +1219,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24825.02</v>
+        <v>25022.54</v>
       </c>
       <c r="C9" t="n">
-        <v>25221.44</v>
+        <v>25166.56</v>
       </c>
       <c r="D9" t="n">
-        <v>24825.02</v>
+        <v>24332.51</v>
       </c>
       <c r="E9" t="n">
-        <v>25008.6</v>
+        <v>24562.24</v>
       </c>
       <c r="F9" t="n">
-        <v>327.5</v>
+        <v>-446.36</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0178</v>
       </c>
       <c r="H9" t="n">
-        <v>396.42</v>
+        <v>834.05</v>
       </c>
       <c r="I9" t="n">
-        <v>24124.22</v>
+        <v>24428.6</v>
       </c>
       <c r="J9" t="n">
-        <v>24390.25</v>
+        <v>24604.86</v>
       </c>
       <c r="K9" t="n">
-        <v>24518.44</v>
+        <v>24810.39</v>
       </c>
       <c r="L9" t="n">
-        <v>24646.64</v>
+        <v>25015.91</v>
       </c>
       <c r="M9" t="n">
-        <v>24843.75</v>
+        <v>25206.81</v>
       </c>
       <c r="N9" t="n">
-        <v>25040.87</v>
+        <v>25397.7</v>
       </c>
       <c r="O9" t="n">
-        <v>25100.15</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>25617.86</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1298,77 +1303,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25022.54</v>
+        <v>24835.03</v>
       </c>
       <c r="C10" t="n">
-        <v>25166.56</v>
+        <v>25155.55</v>
       </c>
       <c r="D10" t="n">
-        <v>24332.51</v>
+        <v>24756.36</v>
       </c>
       <c r="E10" t="n">
-        <v>24562.24</v>
+        <v>25143.05</v>
       </c>
       <c r="F10" t="n">
-        <v>-446.36</v>
+        <v>580.8099999999999</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0178</v>
+        <v>0.0236</v>
       </c>
       <c r="H10" t="n">
-        <v>834.05</v>
+        <v>399.19</v>
       </c>
       <c r="I10" t="n">
-        <v>24428.6</v>
+        <v>23498.46</v>
       </c>
       <c r="J10" t="n">
-        <v>24604.86</v>
+        <v>23634.54</v>
       </c>
       <c r="K10" t="n">
-        <v>24810.39</v>
+        <v>24145.21</v>
       </c>
       <c r="L10" t="n">
-        <v>25015.91</v>
+        <v>24655.89</v>
       </c>
       <c r="M10" t="n">
-        <v>25206.81</v>
+        <v>24979.27</v>
       </c>
       <c r="N10" t="n">
-        <v>25397.7</v>
+        <v>25302.64</v>
       </c>
       <c r="O10" t="n">
-        <v>25617.86</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>26000.61</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1377,55 +1380,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24835.03</v>
+        <v>25150.54</v>
       </c>
       <c r="C11" t="n">
-        <v>25155.55</v>
+        <v>25253.65</v>
       </c>
       <c r="D11" t="n">
-        <v>24756.36</v>
+        <v>24991.39</v>
       </c>
       <c r="E11" t="n">
-        <v>25143.05</v>
+        <v>25132.29</v>
       </c>
       <c r="F11" t="n">
-        <v>580.8099999999999</v>
+        <v>-10.76</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0236</v>
+        <v>-0.0004</v>
       </c>
       <c r="H11" t="n">
-        <v>399.19</v>
+        <v>262.26</v>
       </c>
       <c r="I11" t="n">
-        <v>23498.46</v>
+        <v>24357.17</v>
       </c>
       <c r="J11" t="n">
-        <v>23634.54</v>
+        <v>24837.41</v>
       </c>
       <c r="K11" t="n">
-        <v>24145.21</v>
+        <v>24943.46</v>
       </c>
       <c r="L11" t="n">
-        <v>24655.89</v>
+        <v>25049.5</v>
       </c>
       <c r="M11" t="n">
-        <v>24979.27</v>
+        <v>25342.65</v>
       </c>
       <c r="N11" t="n">
-        <v>25302.64</v>
+        <v>25635.79</v>
       </c>
       <c r="O11" t="n">
-        <v>26000.61</v>
+        <v>25554.74</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,20 +1443,16 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1468,63 +1471,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25150.54</v>
+        <v>24978.9</v>
       </c>
       <c r="C12" t="n">
-        <v>25253.65</v>
+        <v>25040.27</v>
       </c>
       <c r="D12" t="n">
-        <v>24991.39</v>
+        <v>24802.06</v>
       </c>
       <c r="E12" t="n">
-        <v>25132.29</v>
+        <v>24892.66</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.76</v>
+        <v>-239.63</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0095</v>
       </c>
       <c r="H12" t="n">
-        <v>262.26</v>
+        <v>238.21</v>
       </c>
       <c r="I12" t="n">
-        <v>24357.17</v>
+        <v>24729.13</v>
       </c>
       <c r="J12" t="n">
-        <v>24837.41</v>
+        <v>24874.91</v>
       </c>
       <c r="K12" t="n">
-        <v>24943.46</v>
+        <v>25001.16</v>
       </c>
       <c r="L12" t="n">
-        <v>25049.5</v>
+        <v>25127.4</v>
       </c>
       <c r="M12" t="n">
-        <v>25342.65</v>
+        <v>25263.42</v>
       </c>
       <c r="N12" t="n">
-        <v>25635.79</v>
+        <v>25399.43</v>
       </c>
       <c r="O12" t="n">
-        <v>25554.74</v>
+        <v>25515.91</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1541,90 +1548,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24978.9</v>
+        <v>24966.53</v>
       </c>
       <c r="C13" t="n">
-        <v>25040.27</v>
+        <v>25267.39</v>
       </c>
       <c r="D13" t="n">
-        <v>24802.06</v>
+        <v>24876.83</v>
       </c>
       <c r="E13" t="n">
-        <v>24892.66</v>
+        <v>25210.81</v>
       </c>
       <c r="F13" t="n">
-        <v>-239.63</v>
+        <v>318.15</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0095</v>
+        <v>0.0128</v>
       </c>
       <c r="H13" t="n">
-        <v>238.21</v>
+        <v>390.56</v>
       </c>
       <c r="I13" t="n">
-        <v>24729.13</v>
+        <v>24563.85</v>
       </c>
       <c r="J13" t="n">
-        <v>24874.91</v>
+        <v>24640.2</v>
       </c>
       <c r="K13" t="n">
-        <v>25001.16</v>
+        <v>24773.56</v>
       </c>
       <c r="L13" t="n">
-        <v>25127.4</v>
+        <v>24906.91</v>
       </c>
       <c r="M13" t="n">
-        <v>25263.42</v>
+        <v>25011.76</v>
       </c>
       <c r="N13" t="n">
-        <v>25399.43</v>
+        <v>25116.62</v>
       </c>
       <c r="O13" t="n">
-        <v>25515.91</v>
+        <v>25278.48</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1632,220 +1637,220 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24966.53</v>
+        <v>24932.5</v>
       </c>
       <c r="C14" t="n">
-        <v>25267.39</v>
+        <v>25031.34</v>
       </c>
       <c r="D14" t="n">
-        <v>24876.83</v>
+        <v>24812.5</v>
       </c>
       <c r="E14" t="n">
-        <v>25210.81</v>
+        <v>24963.23</v>
       </c>
       <c r="F14" t="n">
-        <v>318.15</v>
+        <v>-247.58</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0098</v>
       </c>
       <c r="H14" t="n">
-        <v>390.56</v>
+        <v>218.84</v>
       </c>
       <c r="I14" t="n">
-        <v>24563.85</v>
+        <v>24486.27</v>
       </c>
       <c r="J14" t="n">
-        <v>24640.2</v>
+        <v>24889.6</v>
       </c>
       <c r="K14" t="n">
-        <v>24773.56</v>
+        <v>25015.53</v>
       </c>
       <c r="L14" t="n">
-        <v>24906.91</v>
+        <v>25141.46</v>
       </c>
       <c r="M14" t="n">
-        <v>25011.76</v>
+        <v>25406.09</v>
       </c>
       <c r="N14" t="n">
-        <v>25116.62</v>
+        <v>25670.72</v>
       </c>
       <c r="O14" t="n">
-        <v>25278.48</v>
+        <v>25657.95</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24932.5</v>
+        <v>24993.77</v>
       </c>
       <c r="C15" t="n">
-        <v>25031.34</v>
+        <v>25276.96</v>
       </c>
       <c r="D15" t="n">
-        <v>24812.5</v>
+        <v>24938.34</v>
       </c>
       <c r="E15" t="n">
-        <v>24963.23</v>
+        <v>25207.18</v>
       </c>
       <c r="F15" t="n">
-        <v>-247.58</v>
+        <v>243.95</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0098</v>
+        <v>0.0098</v>
       </c>
       <c r="H15" t="n">
-        <v>218.84</v>
+        <v>338.62</v>
       </c>
       <c r="I15" t="n">
-        <v>24486.27</v>
+        <v>24593.66</v>
       </c>
       <c r="J15" t="n">
-        <v>24889.6</v>
+        <v>24765.05</v>
       </c>
       <c r="K15" t="n">
-        <v>25015.53</v>
+        <v>24853.81</v>
       </c>
       <c r="L15" t="n">
-        <v>25141.46</v>
+        <v>24942.58</v>
       </c>
       <c r="M15" t="n">
-        <v>25406.09</v>
+        <v>25072.65</v>
       </c>
       <c r="N15" t="n">
-        <v>25670.72</v>
+        <v>25202.73</v>
       </c>
       <c r="O15" t="n">
-        <v>25657.95</v>
+        <v>25250.18</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24993.77</v>
+        <v>25271.95</v>
       </c>
       <c r="C16" t="n">
-        <v>25276.96</v>
+        <v>25440.68</v>
       </c>
       <c r="D16" t="n">
-        <v>24938.34</v>
+        <v>25069.85</v>
       </c>
       <c r="E16" t="n">
-        <v>25207.18</v>
+        <v>25310.85</v>
       </c>
       <c r="F16" t="n">
-        <v>243.95</v>
+        <v>103.67</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0041</v>
       </c>
       <c r="H16" t="n">
-        <v>338.62</v>
+        <v>370.83</v>
       </c>
       <c r="I16" t="n">
-        <v>24593.66</v>
+        <v>24599.72</v>
       </c>
       <c r="J16" t="n">
-        <v>24765.05</v>
+        <v>24918.32</v>
       </c>
       <c r="K16" t="n">
-        <v>24853.81</v>
+        <v>25037.87</v>
       </c>
       <c r="L16" t="n">
-        <v>24942.58</v>
+        <v>25157.42</v>
       </c>
       <c r="M16" t="n">
-        <v>25072.65</v>
+        <v>25376.49</v>
       </c>
       <c r="N16" t="n">
-        <v>25202.73</v>
+        <v>25595.57</v>
       </c>
       <c r="O16" t="n">
-        <v>25250.18</v>
+        <v>25615.58</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1856,25 +1861,21 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1886,50 +1887,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25271.95</v>
+        <v>25487.16</v>
       </c>
       <c r="C17" t="n">
-        <v>25440.68</v>
+        <v>25808.93</v>
       </c>
       <c r="D17" t="n">
-        <v>25069.85</v>
+        <v>25487.16</v>
       </c>
       <c r="E17" t="n">
-        <v>25310.85</v>
+        <v>25807.92</v>
       </c>
       <c r="F17" t="n">
-        <v>103.67</v>
+        <v>497.07</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0196</v>
       </c>
       <c r="H17" t="n">
-        <v>370.83</v>
+        <v>321.77</v>
       </c>
       <c r="I17" t="n">
-        <v>24599.72</v>
+        <v>24699.02</v>
       </c>
       <c r="J17" t="n">
-        <v>24918.32</v>
+        <v>24967.81</v>
       </c>
       <c r="K17" t="n">
-        <v>25037.87</v>
+        <v>25125.43</v>
       </c>
       <c r="L17" t="n">
-        <v>25157.42</v>
+        <v>25283.06</v>
       </c>
       <c r="M17" t="n">
-        <v>25376.49</v>
+        <v>25496.26</v>
       </c>
       <c r="N17" t="n">
-        <v>25595.57</v>
+        <v>25709.47</v>
       </c>
       <c r="O17" t="n">
-        <v>25615.58</v>
+        <v>25811.51</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,21 +1941,25 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1966,50 +1971,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25487.16</v>
+        <v>25875.83</v>
       </c>
       <c r="C18" t="n">
-        <v>25808.93</v>
+        <v>25971.63</v>
       </c>
       <c r="D18" t="n">
-        <v>25487.16</v>
+        <v>25657.33</v>
       </c>
       <c r="E18" t="n">
-        <v>25807.92</v>
+        <v>25858.88</v>
       </c>
       <c r="F18" t="n">
-        <v>497.07</v>
+        <v>50.96</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.002</v>
       </c>
       <c r="H18" t="n">
-        <v>321.77</v>
+        <v>314.3</v>
       </c>
       <c r="I18" t="n">
-        <v>24699.02</v>
+        <v>25165.39</v>
       </c>
       <c r="J18" t="n">
-        <v>24967.81</v>
+        <v>25566.09</v>
       </c>
       <c r="K18" t="n">
-        <v>25125.43</v>
+        <v>25647.04</v>
       </c>
       <c r="L18" t="n">
-        <v>25283.06</v>
+        <v>25727.98</v>
       </c>
       <c r="M18" t="n">
-        <v>25496.26</v>
+        <v>25968.8</v>
       </c>
       <c r="N18" t="n">
-        <v>25709.47</v>
+        <v>26209.63</v>
       </c>
       <c r="O18" t="n">
-        <v>25811.51</v>
+        <v>26130.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2020,25 +2025,21 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2050,50 +2051,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25875.83</v>
+        <v>25837.72</v>
       </c>
       <c r="C19" t="n">
-        <v>25971.63</v>
+        <v>25917.2</v>
       </c>
       <c r="D19" t="n">
-        <v>25657.33</v>
+        <v>25622.92</v>
       </c>
       <c r="E19" t="n">
-        <v>25858.88</v>
+        <v>25884.43</v>
       </c>
       <c r="F19" t="n">
-        <v>50.96</v>
+        <v>25.55</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>314.3</v>
+        <v>294.28</v>
       </c>
       <c r="I19" t="n">
-        <v>25165.39</v>
+        <v>25343.03</v>
       </c>
       <c r="J19" t="n">
-        <v>25566.09</v>
+        <v>25566.78</v>
       </c>
       <c r="K19" t="n">
-        <v>25647.04</v>
+        <v>25701.73</v>
       </c>
       <c r="L19" t="n">
-        <v>25727.98</v>
+        <v>25836.68</v>
       </c>
       <c r="M19" t="n">
-        <v>25968.8</v>
+        <v>26016.03</v>
       </c>
       <c r="N19" t="n">
-        <v>26209.63</v>
+        <v>26195.38</v>
       </c>
       <c r="O19" t="n">
-        <v>26130.7</v>
+        <v>26285.93</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,18 +2102,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2125,55 +2126,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25837.72</v>
+        <v>25987.31</v>
       </c>
       <c r="C20" t="n">
-        <v>25917.2</v>
+        <v>26133.88</v>
       </c>
       <c r="D20" t="n">
-        <v>25622.92</v>
+        <v>25811.74</v>
       </c>
       <c r="E20" t="n">
-        <v>25884.43</v>
+        <v>26009.4</v>
       </c>
       <c r="F20" t="n">
-        <v>25.55</v>
+        <v>124.97</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0048</v>
       </c>
       <c r="H20" t="n">
-        <v>294.28</v>
+        <v>322.14</v>
       </c>
       <c r="I20" t="n">
-        <v>25343.03</v>
+        <v>25328.64</v>
       </c>
       <c r="J20" t="n">
-        <v>25566.78</v>
+        <v>25647.34</v>
       </c>
       <c r="K20" t="n">
-        <v>25701.73</v>
+        <v>25737.29</v>
       </c>
       <c r="L20" t="n">
-        <v>25836.68</v>
+        <v>25827.24</v>
       </c>
       <c r="M20" t="n">
-        <v>26016.03</v>
+        <v>26031.57</v>
       </c>
       <c r="N20" t="n">
-        <v>26195.38</v>
+        <v>26235.89</v>
       </c>
       <c r="O20" t="n">
-        <v>26285.93</v>
+        <v>26211.48</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,18 +2186,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2205,59 +2210,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25987.31</v>
+        <v>26090.98</v>
       </c>
       <c r="C21" t="n">
-        <v>26133.88</v>
+        <v>26187.57</v>
       </c>
       <c r="D21" t="n">
-        <v>25811.74</v>
+        <v>25768.04</v>
       </c>
       <c r="E21" t="n">
-        <v>26009.4</v>
+        <v>25852.92</v>
       </c>
       <c r="F21" t="n">
-        <v>124.97</v>
+        <v>-156.48</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0048</v>
+        <v>-0.006</v>
       </c>
       <c r="H21" t="n">
-        <v>322.14</v>
+        <v>419.53</v>
       </c>
       <c r="I21" t="n">
-        <v>25328.64</v>
+        <v>25489.6</v>
       </c>
       <c r="J21" t="n">
-        <v>25647.34</v>
+        <v>25705.55</v>
       </c>
       <c r="K21" t="n">
-        <v>25737.29</v>
+        <v>25848.33</v>
       </c>
       <c r="L21" t="n">
-        <v>25827.24</v>
+        <v>25991.11</v>
       </c>
       <c r="M21" t="n">
-        <v>26031.57</v>
+        <v>26170.47</v>
       </c>
       <c r="N21" t="n">
-        <v>26235.89</v>
+        <v>26349.84</v>
       </c>
       <c r="O21" t="n">
-        <v>26211.48</v>
+        <v>26456.02</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2265,17 +2266,19 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2289,55 +2292,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26090.98</v>
+        <v>25890.99</v>
       </c>
       <c r="C22" t="n">
-        <v>26187.57</v>
+        <v>25973.94</v>
       </c>
       <c r="D22" t="n">
-        <v>25768.04</v>
+        <v>25729.86</v>
       </c>
       <c r="E22" t="n">
-        <v>25852.92</v>
+        <v>25915.82</v>
       </c>
       <c r="F22" t="n">
-        <v>-156.48</v>
+        <v>62.9</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0024</v>
       </c>
       <c r="H22" t="n">
-        <v>419.53</v>
+        <v>244.08</v>
       </c>
       <c r="I22" t="n">
-        <v>25489.6</v>
+        <v>25348.51</v>
       </c>
       <c r="J22" t="n">
-        <v>25705.55</v>
+        <v>25370.95</v>
       </c>
       <c r="K22" t="n">
-        <v>25848.33</v>
+        <v>25643.15</v>
       </c>
       <c r="L22" t="n">
-        <v>25991.11</v>
+        <v>25915.36</v>
       </c>
       <c r="M22" t="n">
-        <v>26170.47</v>
+        <v>26062.69</v>
       </c>
       <c r="N22" t="n">
-        <v>26349.84</v>
+        <v>26210.01</v>
       </c>
       <c r="O22" t="n">
-        <v>26456.02</v>
+        <v>26607.1</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2345,20 +2352,16 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2380,63 +2383,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25890.99</v>
+        <v>25667.14</v>
       </c>
       <c r="C23" t="n">
-        <v>25973.94</v>
+        <v>25667.14</v>
       </c>
       <c r="D23" t="n">
-        <v>25729.86</v>
+        <v>25389.42</v>
       </c>
       <c r="E23" t="n">
-        <v>25915.82</v>
+        <v>25530.28</v>
       </c>
       <c r="F23" t="n">
-        <v>62.9</v>
+        <v>-385.54</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0149</v>
       </c>
       <c r="H23" t="n">
-        <v>244.08</v>
+        <v>277.72</v>
       </c>
       <c r="I23" t="n">
-        <v>25348.51</v>
+        <v>25485.78</v>
       </c>
       <c r="J23" t="n">
-        <v>25370.95</v>
+        <v>25703.7</v>
       </c>
       <c r="K23" t="n">
-        <v>25643.15</v>
+        <v>25793.78</v>
       </c>
       <c r="L23" t="n">
-        <v>25915.36</v>
+        <v>25883.86</v>
       </c>
       <c r="M23" t="n">
-        <v>26062.69</v>
+        <v>26037.86</v>
       </c>
       <c r="N23" t="n">
-        <v>26210.01</v>
+        <v>26191.86</v>
       </c>
       <c r="O23" t="n">
-        <v>26607.1</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>26218.02</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2448,88 +2457,80 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25667.14</v>
+        <v>25526.65</v>
       </c>
       <c r="C24" t="n">
-        <v>25667.14</v>
+        <v>25669.52</v>
       </c>
       <c r="D24" t="n">
-        <v>25389.42</v>
+        <v>25393.13</v>
       </c>
       <c r="E24" t="n">
-        <v>25530.28</v>
+        <v>25668.03</v>
       </c>
       <c r="F24" t="n">
-        <v>-385.54</v>
+        <v>137.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0149</v>
+        <v>0.0054</v>
       </c>
       <c r="H24" t="n">
-        <v>277.72</v>
+        <v>276.39</v>
       </c>
       <c r="I24" t="n">
-        <v>25485.78</v>
+        <v>25111.7</v>
       </c>
       <c r="J24" t="n">
-        <v>25703.7</v>
+        <v>25253.56</v>
       </c>
       <c r="K24" t="n">
-        <v>25793.78</v>
+        <v>25391.42</v>
       </c>
       <c r="L24" t="n">
-        <v>25883.86</v>
+        <v>25529.28</v>
       </c>
       <c r="M24" t="n">
-        <v>26037.86</v>
+        <v>25669.14</v>
       </c>
       <c r="N24" t="n">
-        <v>26191.86</v>
+        <v>25809</v>
       </c>
       <c r="O24" t="n">
-        <v>26218.02</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>25944.86</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2541,55 +2542,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25526.65</v>
+        <v>25805.18</v>
       </c>
       <c r="C25" t="n">
-        <v>25669.52</v>
+        <v>25957.75</v>
       </c>
       <c r="D25" t="n">
-        <v>25393.13</v>
+        <v>25720.46</v>
       </c>
       <c r="E25" t="n">
-        <v>25668.03</v>
+        <v>25937.49</v>
       </c>
       <c r="F25" t="n">
-        <v>137.75</v>
+        <v>269.46</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0105</v>
       </c>
       <c r="H25" t="n">
-        <v>276.39</v>
+        <v>237.29</v>
       </c>
       <c r="I25" t="n">
-        <v>25111.7</v>
+        <v>25116.74</v>
       </c>
       <c r="J25" t="n">
-        <v>25253.56</v>
+        <v>25459.99</v>
       </c>
       <c r="K25" t="n">
-        <v>25391.42</v>
+        <v>25529.83</v>
       </c>
       <c r="L25" t="n">
-        <v>25529.28</v>
+        <v>25599.68</v>
       </c>
       <c r="M25" t="n">
-        <v>25669.14</v>
+        <v>25806.22</v>
       </c>
       <c r="N25" t="n">
-        <v>25809</v>
+        <v>26012.77</v>
       </c>
       <c r="O25" t="n">
-        <v>25944.86</v>
+        <v>25945.91</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,21 +2605,23 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
@@ -2630,63 +2637,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25805.18</v>
+        <v>25998.59</v>
       </c>
       <c r="C26" t="n">
-        <v>25957.75</v>
+        <v>26060.32</v>
       </c>
       <c r="D26" t="n">
-        <v>25720.46</v>
+        <v>25647.66</v>
       </c>
       <c r="E26" t="n">
-        <v>25937.49</v>
+        <v>25652.82</v>
       </c>
       <c r="F26" t="n">
-        <v>269.46</v>
+        <v>-284.67</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0105</v>
+        <v>-0.011</v>
       </c>
       <c r="H26" t="n">
-        <v>237.29</v>
+        <v>412.66</v>
       </c>
       <c r="I26" t="n">
-        <v>25116.74</v>
+        <v>25483.17</v>
       </c>
       <c r="J26" t="n">
-        <v>25459.99</v>
+        <v>25749.39</v>
       </c>
       <c r="K26" t="n">
-        <v>25529.83</v>
+        <v>25818.85</v>
       </c>
       <c r="L26" t="n">
-        <v>25599.68</v>
+        <v>25888.3</v>
       </c>
       <c r="M26" t="n">
-        <v>25806.22</v>
+        <v>26056.13</v>
       </c>
       <c r="N26" t="n">
-        <v>26012.77</v>
+        <v>26223.97</v>
       </c>
       <c r="O26" t="n">
-        <v>25945.91</v>
+        <v>26195.04</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2697,10 +2708,8 @@
       <c r="U26" s="8" t="n">
         <v/>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
@@ -2709,80 +2718,76 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25998.59</v>
+        <v>25498.39</v>
       </c>
       <c r="C27" t="n">
-        <v>26060.32</v>
+        <v>25498.39</v>
       </c>
       <c r="D27" t="n">
-        <v>25647.66</v>
+        <v>25323.33</v>
       </c>
       <c r="E27" t="n">
-        <v>25652.82</v>
+        <v>25440.17</v>
       </c>
       <c r="F27" t="n">
-        <v>-284.67</v>
+        <v>-212.65</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0083</v>
       </c>
       <c r="H27" t="n">
-        <v>412.66</v>
+        <v>175.06</v>
       </c>
       <c r="I27" t="n">
-        <v>25483.17</v>
+        <v>25235</v>
       </c>
       <c r="J27" t="n">
-        <v>25749.39</v>
+        <v>25139.58</v>
       </c>
       <c r="K27" t="n">
-        <v>25818.85</v>
+        <v>25446.49</v>
       </c>
       <c r="L27" t="n">
-        <v>25888.3</v>
+        <v>25753.41</v>
       </c>
       <c r="M27" t="n">
-        <v>26056.13</v>
+        <v>25859.15</v>
       </c>
       <c r="N27" t="n">
-        <v>26223.97</v>
+        <v>25964.9</v>
       </c>
       <c r="O27" t="n">
-        <v>26195.04</v>
+        <v>26472.98</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2795,59 +2800,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25498.39</v>
+        <v>25288.07</v>
       </c>
       <c r="C28" t="n">
-        <v>25498.39</v>
+        <v>25519.39</v>
       </c>
       <c r="D28" t="n">
-        <v>25323.33</v>
+        <v>25288.07</v>
       </c>
       <c r="E28" t="n">
-        <v>25440.17</v>
+        <v>25396.51</v>
       </c>
       <c r="F28" t="n">
-        <v>-212.65</v>
+        <v>-43.66</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0017</v>
       </c>
       <c r="H28" t="n">
-        <v>175.06</v>
+        <v>231.32</v>
       </c>
       <c r="I28" t="n">
-        <v>25235</v>
+        <v>25148.27</v>
       </c>
       <c r="J28" t="n">
-        <v>25139.58</v>
+        <v>25279.76</v>
       </c>
       <c r="K28" t="n">
-        <v>25446.49</v>
+        <v>25352.64</v>
       </c>
       <c r="L28" t="n">
-        <v>25753.41</v>
+        <v>25425.52</v>
       </c>
       <c r="M28" t="n">
-        <v>25859.15</v>
+        <v>25527.7</v>
       </c>
       <c r="N28" t="n">
-        <v>25964.9</v>
+        <v>25629.89</v>
       </c>
       <c r="O28" t="n">
-        <v>26472.98</v>
+        <v>25673.45</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,12 +2858,12 @@
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2879,70 +2880,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25288.07</v>
+        <v>25219.15</v>
       </c>
       <c r="C29" t="n">
-        <v>25519.39</v>
+        <v>25311.86</v>
       </c>
       <c r="D29" t="n">
-        <v>25288.07</v>
+        <v>25089.14</v>
       </c>
       <c r="E29" t="n">
-        <v>25396.51</v>
+        <v>25116.85</v>
       </c>
       <c r="F29" t="n">
-        <v>-43.66</v>
+        <v>-279.66</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.011</v>
       </c>
       <c r="H29" t="n">
-        <v>231.32</v>
+        <v>222.72</v>
       </c>
       <c r="I29" t="n">
-        <v>25148.27</v>
+        <v>25056.75</v>
       </c>
       <c r="J29" t="n">
-        <v>25279.76</v>
+        <v>25161.58</v>
       </c>
       <c r="K29" t="n">
-        <v>25352.64</v>
+        <v>25280.85</v>
       </c>
       <c r="L29" t="n">
-        <v>25425.52</v>
+        <v>25400.12</v>
       </c>
       <c r="M29" t="n">
-        <v>25527.7</v>
+        <v>25512.17</v>
       </c>
       <c r="N29" t="n">
-        <v>25629.89</v>
+        <v>25624.22</v>
       </c>
       <c r="O29" t="n">
-        <v>25673.45</v>
+        <v>25750.71</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2959,90 +2966,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>25219.15</v>
+        <v>25303.41</v>
       </c>
       <c r="C30" t="n">
-        <v>25311.86</v>
+        <v>25578.27</v>
       </c>
       <c r="D30" t="n">
-        <v>25089.14</v>
+        <v>25303.41</v>
       </c>
       <c r="E30" t="n">
-        <v>25116.85</v>
+        <v>25453.23</v>
       </c>
       <c r="F30" t="n">
-        <v>-279.66</v>
+        <v>336.38</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0134</v>
       </c>
       <c r="H30" t="n">
-        <v>222.72</v>
+        <v>274.86</v>
       </c>
       <c r="I30" t="n">
-        <v>25056.75</v>
+        <v>24866.42</v>
       </c>
       <c r="J30" t="n">
-        <v>25161.58</v>
+        <v>24852.31</v>
       </c>
       <c r="K30" t="n">
-        <v>25280.85</v>
+        <v>25005.49</v>
       </c>
       <c r="L30" t="n">
-        <v>25400.12</v>
+        <v>25158.67</v>
       </c>
       <c r="M30" t="n">
-        <v>25512.17</v>
+        <v>25228.21</v>
       </c>
       <c r="N30" t="n">
-        <v>25624.22</v>
+        <v>25297.74</v>
       </c>
       <c r="O30" t="n">
-        <v>25750.71</v>
+        <v>25534.58</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3050,50 +3055,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>25303.41</v>
+        <v>25368.87</v>
       </c>
       <c r="C31" t="n">
-        <v>25578.27</v>
+        <v>25518.03</v>
       </c>
       <c r="D31" t="n">
-        <v>25303.41</v>
+        <v>25240.62</v>
       </c>
       <c r="E31" t="n">
-        <v>25453.23</v>
+        <v>25471.15</v>
       </c>
       <c r="F31" t="n">
-        <v>336.38</v>
+        <v>17.92</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0007</v>
       </c>
       <c r="H31" t="n">
-        <v>274.86</v>
+        <v>277.41</v>
       </c>
       <c r="I31" t="n">
-        <v>24866.42</v>
+        <v>25028.55</v>
       </c>
       <c r="J31" t="n">
-        <v>24852.31</v>
+        <v>25184.57</v>
       </c>
       <c r="K31" t="n">
-        <v>25005.49</v>
+        <v>25315.8</v>
       </c>
       <c r="L31" t="n">
-        <v>25158.67</v>
+        <v>25447.04</v>
       </c>
       <c r="M31" t="n">
-        <v>25228.21</v>
+        <v>25590.66</v>
       </c>
       <c r="N31" t="n">
-        <v>25297.74</v>
+        <v>25734.29</v>
       </c>
       <c r="O31" t="n">
-        <v>25534.58</v>
+        <v>25853.13</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3101,83 +3106,83 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25368.87</v>
+        <v>25346.9</v>
       </c>
       <c r="C32" t="n">
-        <v>25518.03</v>
+        <v>25537.19</v>
       </c>
       <c r="D32" t="n">
-        <v>25240.62</v>
+        <v>25315.32</v>
       </c>
       <c r="E32" t="n">
-        <v>25471.15</v>
+        <v>25495.07</v>
       </c>
       <c r="F32" t="n">
-        <v>17.92</v>
+        <v>23.92</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0009</v>
       </c>
       <c r="H32" t="n">
-        <v>277.41</v>
+        <v>221.87</v>
       </c>
       <c r="I32" t="n">
-        <v>25028.55</v>
+        <v>24963.21</v>
       </c>
       <c r="J32" t="n">
-        <v>25184.57</v>
+        <v>25239.65</v>
       </c>
       <c r="K32" t="n">
-        <v>25315.8</v>
+        <v>25332.45</v>
       </c>
       <c r="L32" t="n">
-        <v>25447.04</v>
+        <v>25425.24</v>
       </c>
       <c r="M32" t="n">
-        <v>25590.66</v>
+        <v>25609.86</v>
       </c>
       <c r="N32" t="n">
-        <v>25734.29</v>
+        <v>25794.47</v>
       </c>
       <c r="O32" t="n">
-        <v>25853.13</v>
+        <v>25795.44</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3190,7 +3195,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3209,59 +3214,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>25346.9</v>
+        <v>25779.08</v>
       </c>
       <c r="C33" t="n">
-        <v>25537.19</v>
+        <v>25842.91</v>
       </c>
       <c r="D33" t="n">
-        <v>25315.32</v>
+        <v>25632.39</v>
       </c>
       <c r="E33" t="n">
-        <v>25495.07</v>
+        <v>25698.49</v>
       </c>
       <c r="F33" t="n">
-        <v>23.92</v>
+        <v>203.42</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.008</v>
       </c>
       <c r="H33" t="n">
-        <v>221.87</v>
+        <v>210.52</v>
       </c>
       <c r="I33" t="n">
-        <v>24963.21</v>
+        <v>25093.45</v>
       </c>
       <c r="J33" t="n">
-        <v>25239.65</v>
+        <v>25307.61</v>
       </c>
       <c r="K33" t="n">
-        <v>25332.45</v>
+        <v>25384.14</v>
       </c>
       <c r="L33" t="n">
-        <v>25425.24</v>
+        <v>25460.66</v>
       </c>
       <c r="M33" t="n">
-        <v>25609.86</v>
+        <v>25606</v>
       </c>
       <c r="N33" t="n">
-        <v>25794.47</v>
+        <v>25751.35</v>
       </c>
       <c r="O33" t="n">
-        <v>25795.44</v>
+        <v>25759.06</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3269,24 +3270,28 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3298,50 +3303,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25779.08</v>
+        <v>25807.61</v>
       </c>
       <c r="C34" t="n">
-        <v>25842.91</v>
+        <v>26009.46</v>
       </c>
       <c r="D34" t="n">
-        <v>25632.39</v>
+        <v>25807.61</v>
       </c>
       <c r="E34" t="n">
-        <v>25698.49</v>
+        <v>26009.46</v>
       </c>
       <c r="F34" t="n">
-        <v>203.42</v>
+        <v>310.97</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0121</v>
       </c>
       <c r="H34" t="n">
-        <v>210.52</v>
+        <v>201.85</v>
       </c>
       <c r="I34" t="n">
-        <v>25093.45</v>
+        <v>25421.87</v>
       </c>
       <c r="J34" t="n">
-        <v>25307.61</v>
+        <v>25468.39</v>
       </c>
       <c r="K34" t="n">
-        <v>25384.14</v>
+        <v>25593.23</v>
       </c>
       <c r="L34" t="n">
-        <v>25460.66</v>
+        <v>25718.07</v>
       </c>
       <c r="M34" t="n">
-        <v>25606</v>
+        <v>25803.75</v>
       </c>
       <c r="N34" t="n">
-        <v>25751.35</v>
+        <v>25889.43</v>
       </c>
       <c r="O34" t="n">
-        <v>25759.06</v>
+        <v>26053.43</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3352,7 +3357,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3364,12 +3369,12 @@
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
@@ -3382,83 +3387,83 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25807.61</v>
+        <v>25780.12</v>
       </c>
       <c r="C35" t="n">
-        <v>26009.46</v>
+        <v>25780.12</v>
       </c>
       <c r="D35" t="n">
-        <v>25807.61</v>
+        <v>25430.94</v>
       </c>
       <c r="E35" t="n">
-        <v>26009.46</v>
+        <v>25517.33</v>
       </c>
       <c r="F35" t="n">
-        <v>310.97</v>
+        <v>-492.13</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0121</v>
+        <v>-0.0189</v>
       </c>
       <c r="H35" t="n">
-        <v>201.85</v>
+        <v>349.18</v>
       </c>
       <c r="I35" t="n">
-        <v>25421.87</v>
+        <v>25605.76</v>
       </c>
       <c r="J35" t="n">
-        <v>25468.39</v>
+        <v>25858.07</v>
       </c>
       <c r="K35" t="n">
-        <v>25593.23</v>
+        <v>25908.54</v>
       </c>
       <c r="L35" t="n">
-        <v>25718.07</v>
+        <v>25959</v>
       </c>
       <c r="M35" t="n">
-        <v>25803.75</v>
+        <v>26110.39</v>
       </c>
       <c r="N35" t="n">
-        <v>25889.43</v>
+        <v>26261.78</v>
       </c>
       <c r="O35" t="n">
-        <v>26053.43</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+        <v>26211.31</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3466,69 +3471,63 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>25780.12</v>
+        <v>25634.22</v>
       </c>
       <c r="C36" t="n">
-        <v>25780.12</v>
+        <v>25676.77</v>
       </c>
       <c r="D36" t="n">
-        <v>25430.94</v>
+        <v>25403.44</v>
       </c>
       <c r="E36" t="n">
-        <v>25517.33</v>
+        <v>25511.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-492.13</v>
+        <v>-6.23</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0002</v>
       </c>
       <c r="H36" t="n">
-        <v>349.18</v>
+        <v>273.33</v>
       </c>
       <c r="I36" t="n">
-        <v>25605.76</v>
+        <v>25081.76</v>
       </c>
       <c r="J36" t="n">
-        <v>25858.07</v>
+        <v>25124.05</v>
       </c>
       <c r="K36" t="n">
-        <v>25908.54</v>
+        <v>25342.74</v>
       </c>
       <c r="L36" t="n">
-        <v>25959</v>
+        <v>25561.43</v>
       </c>
       <c r="M36" t="n">
-        <v>26110.39</v>
+        <v>25691.92</v>
       </c>
       <c r="N36" t="n">
-        <v>26261.78</v>
+        <v>25822.41</v>
       </c>
       <c r="O36" t="n">
-        <v>26211.31</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>26129.3</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3550,50 +3549,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>25634.22</v>
+        <v>25635.24</v>
       </c>
       <c r="C37" t="n">
-        <v>25676.77</v>
+        <v>25800.22</v>
       </c>
       <c r="D37" t="n">
-        <v>25403.44</v>
+        <v>25615.94</v>
       </c>
       <c r="E37" t="n">
-        <v>25511.1</v>
+        <v>25652.97</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.23</v>
+        <v>141.87</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0056</v>
       </c>
       <c r="H37" t="n">
-        <v>273.33</v>
+        <v>184.28</v>
       </c>
       <c r="I37" t="n">
-        <v>25081.76</v>
+        <v>25130.11</v>
       </c>
       <c r="J37" t="n">
-        <v>25124.05</v>
+        <v>25223.27</v>
       </c>
       <c r="K37" t="n">
-        <v>25342.74</v>
+        <v>25374.43</v>
       </c>
       <c r="L37" t="n">
-        <v>25561.43</v>
+        <v>25525.6</v>
       </c>
       <c r="M37" t="n">
-        <v>25691.92</v>
+        <v>25647.76</v>
       </c>
       <c r="N37" t="n">
-        <v>25822.41</v>
+        <v>25769.93</v>
       </c>
       <c r="O37" t="n">
-        <v>26129.3</v>
+        <v>25950.1</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3606,14 +3605,18 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3623,55 +3626,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>25635.24</v>
+        <v>25774.87</v>
       </c>
       <c r="C38" t="n">
-        <v>25800.22</v>
+        <v>25792.01</v>
       </c>
       <c r="D38" t="n">
-        <v>25615.94</v>
+        <v>25500.96</v>
       </c>
       <c r="E38" t="n">
-        <v>25652.97</v>
+        <v>25565.74</v>
       </c>
       <c r="F38" t="n">
-        <v>141.87</v>
+        <v>-87.23</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0056</v>
+        <v>-0.0034</v>
       </c>
       <c r="H38" t="n">
-        <v>184.28</v>
+        <v>291.05</v>
       </c>
       <c r="I38" t="n">
-        <v>25130.11</v>
+        <v>25431.66</v>
       </c>
       <c r="J38" t="n">
-        <v>25223.27</v>
+        <v>25441.13</v>
       </c>
       <c r="K38" t="n">
-        <v>25374.43</v>
+        <v>25560.83</v>
       </c>
       <c r="L38" t="n">
-        <v>25525.6</v>
+        <v>25680.53</v>
       </c>
       <c r="M38" t="n">
-        <v>25647.76</v>
+        <v>25745.11</v>
       </c>
       <c r="N38" t="n">
-        <v>25769.93</v>
+        <v>25809.7</v>
       </c>
       <c r="O38" t="n">
-        <v>25950.1</v>
+        <v>25984.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3679,23 +3686,23 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3705,59 +3712,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>25774.87</v>
+        <v>25410.46</v>
       </c>
       <c r="C39" t="n">
-        <v>25792.01</v>
+        <v>25699.09</v>
       </c>
       <c r="D39" t="n">
-        <v>25500.96</v>
+        <v>25410.46</v>
       </c>
       <c r="E39" t="n">
-        <v>25565.74</v>
+        <v>25584.79</v>
       </c>
       <c r="F39" t="n">
-        <v>-87.23</v>
+        <v>19.05</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0007</v>
       </c>
       <c r="H39" t="n">
-        <v>291.05</v>
+        <v>288.63</v>
       </c>
       <c r="I39" t="n">
-        <v>25431.66</v>
+        <v>25209.91</v>
       </c>
       <c r="J39" t="n">
-        <v>25441.13</v>
+        <v>25234.32</v>
       </c>
       <c r="K39" t="n">
-        <v>25560.83</v>
+        <v>25420.22</v>
       </c>
       <c r="L39" t="n">
-        <v>25680.53</v>
+        <v>25606.11</v>
       </c>
       <c r="M39" t="n">
-        <v>25745.11</v>
+        <v>25711.26</v>
       </c>
       <c r="N39" t="n">
-        <v>25809.7</v>
+        <v>25816.42</v>
       </c>
       <c r="O39" t="n">
-        <v>25984.5</v>
+        <v>26083.06</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3767,18 +3770,16 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3791,68 +3792,74 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25410.46</v>
+        <v>25420.63</v>
       </c>
       <c r="C40" t="n">
-        <v>25699.09</v>
+        <v>25566.99</v>
       </c>
       <c r="D40" t="n">
-        <v>25410.46</v>
+        <v>25290.69</v>
       </c>
       <c r="E40" t="n">
-        <v>25584.79</v>
+        <v>25566.99</v>
       </c>
       <c r="F40" t="n">
-        <v>19.05</v>
+        <v>-17.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>288.63</v>
+        <v>276.3</v>
       </c>
       <c r="I40" t="n">
-        <v>25209.91</v>
+        <v>25121.83</v>
       </c>
       <c r="J40" t="n">
-        <v>25234.32</v>
+        <v>25311.17</v>
       </c>
       <c r="K40" t="n">
-        <v>25420.22</v>
+        <v>25440.47</v>
       </c>
       <c r="L40" t="n">
-        <v>25606.11</v>
+        <v>25569.78</v>
       </c>
       <c r="M40" t="n">
-        <v>25711.26</v>
+        <v>25729.1</v>
       </c>
       <c r="N40" t="n">
-        <v>25816.42</v>
+        <v>25888.42</v>
       </c>
       <c r="O40" t="n">
-        <v>26083.06</v>
+        <v>25987.72</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3871,66 +3878,62 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>25420.63</v>
+        <v>25415.72</v>
       </c>
       <c r="C41" t="n">
-        <v>25566.99</v>
+        <v>25478.98</v>
       </c>
       <c r="D41" t="n">
-        <v>25290.69</v>
+        <v>25240.2</v>
       </c>
       <c r="E41" t="n">
-        <v>25566.99</v>
+        <v>25329.73</v>
       </c>
       <c r="F41" t="n">
-        <v>-17.8</v>
+        <v>-237.26</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>276.3</v>
+        <v>238.78</v>
       </c>
       <c r="I41" t="n">
-        <v>25121.83</v>
+        <v>25014.39</v>
       </c>
       <c r="J41" t="n">
-        <v>25311.17</v>
+        <v>25359.76</v>
       </c>
       <c r="K41" t="n">
-        <v>25440.47</v>
+        <v>25428.84</v>
       </c>
       <c r="L41" t="n">
-        <v>25569.78</v>
+        <v>25497.92</v>
       </c>
       <c r="M41" t="n">
-        <v>25729.1</v>
+        <v>25705.14</v>
       </c>
       <c r="N41" t="n">
-        <v>25888.42</v>
+        <v>25912.37</v>
       </c>
       <c r="O41" t="n">
-        <v>25987.72</v>
+        <v>25843.29</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -3938,9 +3941,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3962,57 +3965,57 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25415.72</v>
+        <v>25280.82</v>
       </c>
       <c r="C42" t="n">
-        <v>25478.98</v>
+        <v>25311.21</v>
       </c>
       <c r="D42" t="n">
-        <v>25240.2</v>
+        <v>25008.87</v>
       </c>
       <c r="E42" t="n">
-        <v>25329.73</v>
+        <v>25311.21</v>
       </c>
       <c r="F42" t="n">
-        <v>-237.26</v>
+        <v>-18.52</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>238.78</v>
+        <v>302.34</v>
       </c>
       <c r="I42" t="n">
-        <v>25014.39</v>
+        <v>25001.42</v>
       </c>
       <c r="J42" t="n">
-        <v>25359.76</v>
+        <v>25076.02</v>
       </c>
       <c r="K42" t="n">
-        <v>25428.84</v>
+        <v>25210.34</v>
       </c>
       <c r="L42" t="n">
-        <v>25497.92</v>
+        <v>25344.66</v>
       </c>
       <c r="M42" t="n">
-        <v>25705.14</v>
+        <v>25449.12</v>
       </c>
       <c r="N42" t="n">
-        <v>25912.37</v>
+        <v>25553.58</v>
       </c>
       <c r="O42" t="n">
-        <v>25843.29</v>
+        <v>25717.76</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -4020,9 +4023,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4044,71 +4047,69 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25280.82</v>
+        <v>25482.56</v>
       </c>
       <c r="C43" t="n">
-        <v>25311.21</v>
+        <v>25538.15</v>
       </c>
       <c r="D43" t="n">
-        <v>25008.87</v>
+        <v>25160.38</v>
       </c>
       <c r="E43" t="n">
-        <v>25311.21</v>
+        <v>25213.31</v>
       </c>
       <c r="F43" t="n">
-        <v>-18.52</v>
+        <v>-97.90000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0039</v>
       </c>
       <c r="H43" t="n">
-        <v>302.34</v>
+        <v>377.77</v>
       </c>
       <c r="I43" t="n">
-        <v>25001.42</v>
+        <v>24706.53</v>
       </c>
       <c r="J43" t="n">
-        <v>25076.02</v>
+        <v>25084.45</v>
       </c>
       <c r="K43" t="n">
-        <v>25210.34</v>
+        <v>25160.04</v>
       </c>
       <c r="L43" t="n">
-        <v>25344.66</v>
+        <v>25235.63</v>
       </c>
       <c r="M43" t="n">
-        <v>25449.12</v>
+        <v>25462.38</v>
       </c>
       <c r="N43" t="n">
-        <v>25553.58</v>
+        <v>25689.14</v>
       </c>
       <c r="O43" t="n">
-        <v>25717.76</v>
+        <v>25613.55</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4121,55 +4122,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>25482.56</v>
+        <v>25515.74</v>
       </c>
       <c r="C44" t="n">
-        <v>25538.15</v>
+        <v>25791.38</v>
       </c>
       <c r="D44" t="n">
-        <v>25160.38</v>
+        <v>25515.74</v>
       </c>
       <c r="E44" t="n">
-        <v>25213.31</v>
+        <v>25650.87</v>
       </c>
       <c r="F44" t="n">
-        <v>-97.90000000000001</v>
+        <v>437.56</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0174</v>
       </c>
       <c r="H44" t="n">
-        <v>377.77</v>
+        <v>275.64</v>
       </c>
       <c r="I44" t="n">
-        <v>24706.53</v>
+        <v>24782.61</v>
       </c>
       <c r="J44" t="n">
-        <v>25084.45</v>
+        <v>24767.56</v>
       </c>
       <c r="K44" t="n">
-        <v>25160.04</v>
+        <v>25024.43</v>
       </c>
       <c r="L44" t="n">
-        <v>25235.63</v>
+        <v>25281.29</v>
       </c>
       <c r="M44" t="n">
-        <v>25462.38</v>
+        <v>25402.2</v>
       </c>
       <c r="N44" t="n">
-        <v>25689.14</v>
+        <v>25523.1</v>
       </c>
       <c r="O44" t="n">
-        <v>25613.55</v>
+        <v>25915.92</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4182,7 +4187,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4190,94 +4195,92 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>25515.74</v>
+        <v>25652.97</v>
       </c>
       <c r="C45" t="n">
-        <v>25791.38</v>
+        <v>25664.98</v>
       </c>
       <c r="D45" t="n">
-        <v>25515.74</v>
+        <v>25362.98</v>
       </c>
       <c r="E45" t="n">
-        <v>25650.87</v>
+        <v>25413.12</v>
       </c>
       <c r="F45" t="n">
-        <v>437.56</v>
+        <v>-237.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0174</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>275.64</v>
+        <v>302</v>
       </c>
       <c r="I45" t="n">
-        <v>24782.61</v>
+        <v>25240.1</v>
       </c>
       <c r="J45" t="n">
-        <v>24767.56</v>
+        <v>25373.88</v>
       </c>
       <c r="K45" t="n">
-        <v>25024.43</v>
+        <v>25513.05</v>
       </c>
       <c r="L45" t="n">
-        <v>25281.29</v>
+        <v>25652.21</v>
       </c>
       <c r="M45" t="n">
-        <v>25402.2</v>
+        <v>25788.69</v>
       </c>
       <c r="N45" t="n">
-        <v>25523.1</v>
+        <v>25925.16</v>
       </c>
       <c r="O45" t="n">
-        <v>25915.92</v>
+        <v>26067.02</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4287,70 +4290,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25652.97</v>
+        <v>25252.07</v>
       </c>
       <c r="C46" t="n">
-        <v>25664.98</v>
+        <v>25394.6</v>
       </c>
       <c r="D46" t="n">
-        <v>25362.98</v>
+        <v>25225.69</v>
       </c>
       <c r="E46" t="n">
-        <v>25413.12</v>
+        <v>25317.18</v>
       </c>
       <c r="F46" t="n">
-        <v>-237.75</v>
+        <v>-95.94</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="H46" t="n">
-        <v>302</v>
+        <v>168.91</v>
       </c>
       <c r="I46" t="n">
-        <v>25240.1</v>
+        <v>25060.98</v>
       </c>
       <c r="J46" t="n">
-        <v>25373.88</v>
+        <v>25060.69</v>
       </c>
       <c r="K46" t="n">
-        <v>25513.05</v>
+        <v>25262.12</v>
       </c>
       <c r="L46" t="n">
-        <v>25652.21</v>
+        <v>25463.55</v>
       </c>
       <c r="M46" t="n">
-        <v>25788.69</v>
+        <v>25564.12</v>
       </c>
       <c r="N46" t="n">
-        <v>25925.16</v>
+        <v>25664.69</v>
       </c>
       <c r="O46" t="n">
-        <v>26067.02</v>
+        <v>25966.98</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4378,50 +4383,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25252.07</v>
+        <v>25328.13</v>
       </c>
       <c r="C47" t="n">
-        <v>25394.6</v>
+        <v>25335.52</v>
       </c>
       <c r="D47" t="n">
-        <v>25225.69</v>
+        <v>25161.67</v>
       </c>
       <c r="E47" t="n">
-        <v>25317.18</v>
+        <v>25274.96</v>
       </c>
       <c r="F47" t="n">
-        <v>-95.94</v>
+        <v>-42.22</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0017</v>
       </c>
       <c r="H47" t="n">
-        <v>168.91</v>
+        <v>173.85</v>
       </c>
       <c r="I47" t="n">
-        <v>25060.98</v>
+        <v>25056.78</v>
       </c>
       <c r="J47" t="n">
-        <v>25060.69</v>
+        <v>25151.79</v>
       </c>
       <c r="K47" t="n">
-        <v>25262.12</v>
+        <v>25232.72</v>
       </c>
       <c r="L47" t="n">
-        <v>25463.55</v>
+        <v>25313.66</v>
       </c>
       <c r="M47" t="n">
-        <v>25564.12</v>
+        <v>25401.63</v>
       </c>
       <c r="N47" t="n">
-        <v>25664.69</v>
+        <v>25489.61</v>
       </c>
       <c r="O47" t="n">
-        <v>25966.98</v>
+        <v>25563.51</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4431,12 +4436,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4462,65 +4467,69 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25328.13</v>
+        <v>24985.18</v>
       </c>
       <c r="C48" t="n">
-        <v>25335.52</v>
+        <v>25021.81</v>
       </c>
       <c r="D48" t="n">
-        <v>25161.67</v>
+        <v>24889.64</v>
       </c>
       <c r="E48" t="n">
-        <v>25274.96</v>
+        <v>24954.47</v>
       </c>
       <c r="F48" t="n">
-        <v>-42.22</v>
+        <v>-320.49</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0127</v>
       </c>
       <c r="H48" t="n">
-        <v>173.85</v>
+        <v>132.17</v>
       </c>
       <c r="I48" t="n">
-        <v>25056.78</v>
+        <v>24987.82</v>
       </c>
       <c r="J48" t="n">
-        <v>25151.79</v>
+        <v>25114.29</v>
       </c>
       <c r="K48" t="n">
-        <v>25232.72</v>
+        <v>25188.04</v>
       </c>
       <c r="L48" t="n">
-        <v>25313.66</v>
+        <v>25261.78</v>
       </c>
       <c r="M48" t="n">
-        <v>25401.63</v>
+        <v>25361.89</v>
       </c>
       <c r="N48" t="n">
-        <v>25489.61</v>
+        <v>25461.99</v>
       </c>
       <c r="O48" t="n">
-        <v>25563.51</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>25509.37</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4532,81 +4541,77 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24985.18</v>
+        <v>24718.15</v>
       </c>
       <c r="C49" t="n">
-        <v>25021.81</v>
+        <v>24851.18</v>
       </c>
       <c r="D49" t="n">
-        <v>24889.64</v>
+        <v>24570.24</v>
       </c>
       <c r="E49" t="n">
-        <v>24954.47</v>
+        <v>24805.63</v>
       </c>
       <c r="F49" t="n">
-        <v>-320.49</v>
+        <v>-148.84</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.006</v>
       </c>
       <c r="H49" t="n">
-        <v>132.17</v>
+        <v>280.94</v>
       </c>
       <c r="I49" t="n">
-        <v>24987.82</v>
+        <v>24757.47</v>
       </c>
       <c r="J49" t="n">
-        <v>25114.29</v>
+        <v>24821.67</v>
       </c>
       <c r="K49" t="n">
-        <v>25188.04</v>
+        <v>24888.39</v>
       </c>
       <c r="L49" t="n">
-        <v>25261.78</v>
+        <v>24955.1</v>
       </c>
       <c r="M49" t="n">
-        <v>25361.89</v>
+        <v>25020.56</v>
       </c>
       <c r="N49" t="n">
-        <v>25461.99</v>
+        <v>25086.01</v>
       </c>
       <c r="O49" t="n">
-        <v>25509.37</v>
+        <v>25153.98</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4630,74 +4635,72 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24718.15</v>
+        <v>24701.18</v>
       </c>
       <c r="C50" t="n">
-        <v>24851.18</v>
+        <v>24926.24</v>
       </c>
       <c r="D50" t="n">
-        <v>24570.24</v>
+        <v>24662.11</v>
       </c>
       <c r="E50" t="n">
-        <v>24805.63</v>
+        <v>24917.6</v>
       </c>
       <c r="F50" t="n">
-        <v>-148.84</v>
+        <v>111.97</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0045</v>
       </c>
       <c r="H50" t="n">
-        <v>280.94</v>
+        <v>264.13</v>
       </c>
       <c r="I50" t="n">
-        <v>24757.47</v>
+        <v>24289.3</v>
       </c>
       <c r="J50" t="n">
-        <v>24821.67</v>
+        <v>24572.15</v>
       </c>
       <c r="K50" t="n">
-        <v>24888.39</v>
+        <v>24665.16</v>
       </c>
       <c r="L50" t="n">
-        <v>24955.1</v>
+        <v>24758.17</v>
       </c>
       <c r="M50" t="n">
-        <v>25020.56</v>
+        <v>24946.1</v>
       </c>
       <c r="N50" t="n">
-        <v>25086.01</v>
+        <v>25134.03</v>
       </c>
       <c r="O50" t="n">
-        <v>25153.98</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
+        <v>25132.12</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5